--- a/doc/금융감독원 홈페이지_UIUX_퍼블_컴포넌트리스트 .xlsx
+++ b/doc/금융감독원 홈페이지_UIUX_퍼블_컴포넌트리스트 .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\03.Publishing\fss\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF53CDC7-A656-40CE-AE57-924D56712664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93260AC-0D20-45ED-99CC-47945DC6DC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-5100" windowWidth="29040" windowHeight="15720" tabRatio="499" activeTab="1" xr2:uid="{BA3ED54C-CC85-4CD0-8ADB-46ECF631616A}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="204">
   <si>
     <t>대분류</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -620,42 +620,174 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>css (basic)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>css (plugin)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swiper-bundle.min.css</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>krds.min.css 로 대체 사용(이미지 경로를 상대경로 수정함)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>code/prism.css</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pattern/p_layout.scss</t>
+  </si>
+  <si>
+    <t>pattern/p_content.scss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pattern/p_common.scss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>common.css</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>component.css</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>output.css</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>krds_tokens.css</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>css (additional)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>css (guide additional)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>css 정리 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3-2. Layout</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3-3. main page</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3-4. sub page</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>krds-side-navigation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모바일 메뉴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좌측 메뉴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gnb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>checked</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>logo 및 direct menu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>checking 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>header utility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>subpage gnb</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>js</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>css (basic)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>css (plugin)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>swiper-bundle.min.css</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>krds.min.css 로 대체 사용(이미지 경로를 상대경로 수정함)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>code/prism.css</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pattern/p_layout.scss</t>
-  </si>
-  <si>
-    <t>pattern/p_content.scss</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pattern/p_common.scss</t>
+    <t>header branding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>header-actions 내 icon 가로모드는 class 'btn-navi' 뒤에 navi-row 추가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항목</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>languge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>direct menu, drop menu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>글자화면 설정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>checked</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>디자인만 적용, 항목 선택시 적용하는 js 는 미적용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02.19.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-1-3. 헤더</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-1-4. 푸터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>font.css 생성(local path)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>content.css</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -663,95 +795,41 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>component.css</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>output.css</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>krds_tokens.css</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>css (additional)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>css (guide additional)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>O</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>p_common.css</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>p_content.css</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fss content custom</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
+    <t>style.css</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>fss common custom 작업 중</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>css 정리 완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3-2. Layout</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3-3. main page</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3-4. sub page</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>krds-side-navigation</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>모바일 메뉴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>좌측 메뉴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gnb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>checked</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>logo 및 direct menu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>etc direct menu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>checking 필요</t>
+  </si>
+  <si>
+    <t>font.css</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pretendard GOV file</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fss content custom 미작업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ia_style.css</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> :: guide css link 통합파일 ::
+style.css (front css)
+guide.css</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> :: front css link 통합파일 ::
+krds.min.css (design token)
+plugin/swiper-bundle.min.css
+font.css
+common.css
+content.css</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -759,7 +837,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1033,6 +1111,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1051,13 +1144,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1069,26 +1162,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1428,7 +1506,7 @@
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:H170"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="21.25" customWidth="1"/>
     <col min="2" max="2" width="18.58203125" customWidth="1"/>
@@ -1440,20 +1518,20 @@
     <col min="8" max="8" width="7.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="D1"/>
     </row>
-    <row r="2" spans="1:6" s="4" customFormat="1" ht="30" customHeight="1">
+    <row r="2" spans="1:6" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E2" s="22"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="8.25" customHeight="1">
+    <row r="3" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="D3"/>
     </row>
-    <row r="4" spans="1:6" ht="26.25" customHeight="1">
+    <row r="4" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1473,11 +1551,11 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="33" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="35" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="13"/>
@@ -1489,9 +1567,9 @@
       </c>
       <c r="F5" s="16"/>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="34"/>
-      <c r="B6" s="31"/>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" s="39"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="13" t="s">
         <v>130</v>
       </c>
@@ -1499,10 +1577,10 @@
       <c r="E6" s="23"/>
       <c r="F6" s="16"/>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="34"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="30" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="39"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="35" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="15" t="s">
@@ -1511,20 +1589,20 @@
       <c r="E7" s="23"/>
       <c r="F7" s="16"/>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="34"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="32"/>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="39"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="37"/>
       <c r="D8" s="15" t="s">
         <v>95</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="16"/>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="34"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="30" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" s="39"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="35" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="17" t="s">
@@ -1535,18 +1613,18 @@
       </c>
       <c r="F9" s="16"/>
     </row>
-    <row r="10" spans="1:6" hidden="1">
-      <c r="A10" s="34"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="39"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
       <c r="F10" s="16"/>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="34"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="30" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11" s="39"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="35" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="15" t="s">
@@ -1557,20 +1635,20 @@
       </c>
       <c r="F11" s="16"/>
     </row>
-    <row r="12" spans="1:6" hidden="1">
-      <c r="A12" s="34"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="39"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
       <c r="F12" s="16"/>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="34"/>
-      <c r="B13" s="30" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" s="39"/>
+      <c r="B13" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="35" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="18" t="s">
@@ -1581,26 +1659,26 @@
       </c>
       <c r="F13" s="16"/>
     </row>
-    <row r="14" spans="1:6" hidden="1">
-      <c r="A14" s="34"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="39"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
       <c r="D14" s="18"/>
       <c r="E14" s="18"/>
       <c r="F14" s="16"/>
     </row>
-    <row r="15" spans="1:6" hidden="1">
-      <c r="A15" s="34"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="32"/>
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="39"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="37"/>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
       <c r="F15" s="16"/>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="34"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="30" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16" s="39"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="35" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="18" t="s">
@@ -1611,10 +1689,10 @@
       </c>
       <c r="F16" s="16"/>
     </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="34"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A17" s="39"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
       <c r="D17" s="18" t="s">
         <v>60</v>
       </c>
@@ -1623,34 +1701,34 @@
       </c>
       <c r="F17" s="16"/>
     </row>
-    <row r="18" spans="1:6" hidden="1">
-      <c r="A18" s="34"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="39"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
       <c r="D18" s="18"/>
       <c r="E18" s="18"/>
       <c r="F18" s="16"/>
     </row>
-    <row r="19" spans="1:6" hidden="1">
-      <c r="A19" s="34"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="39"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
       <c r="D19" s="18"/>
       <c r="E19" s="18"/>
       <c r="F19" s="16"/>
     </row>
-    <row r="20" spans="1:6" hidden="1">
-      <c r="A20" s="34"/>
-      <c r="B20" s="31"/>
-      <c r="C20" s="32"/>
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="39"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="37"/>
       <c r="D20" s="18"/>
       <c r="E20" s="18"/>
       <c r="F20" s="16"/>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="34"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="30" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" s="39"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="35" t="s">
         <v>12</v>
       </c>
       <c r="D21" s="18" t="s">
@@ -1661,25 +1739,25 @@
       </c>
       <c r="F21" s="16"/>
     </row>
-    <row r="22" spans="1:6" hidden="1">
-      <c r="A22" s="34"/>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="39"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
       <c r="D22" s="18"/>
       <c r="E22" s="18"/>
       <c r="F22" s="16"/>
     </row>
-    <row r="23" spans="1:6" hidden="1">
-      <c r="A23" s="34"/>
-      <c r="B23" s="31"/>
-      <c r="C23" s="32"/>
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="39"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="37"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="16"/>
     </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="34"/>
-      <c r="B24" s="31"/>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A24" s="39"/>
+      <c r="B24" s="36"/>
       <c r="C24" s="13" t="s">
         <v>13</v>
       </c>
@@ -1691,44 +1769,44 @@
       </c>
       <c r="F24" s="16"/>
     </row>
-    <row r="25" spans="1:6" hidden="1">
-      <c r="A25" s="34"/>
-      <c r="B25" s="31"/>
-      <c r="C25" s="30" t="s">
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="39"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="35" t="s">
         <v>14</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
       <c r="F25" s="16"/>
     </row>
-    <row r="26" spans="1:6" hidden="1">
-      <c r="A26" s="34"/>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="39"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="36"/>
       <c r="D26" s="15"/>
       <c r="E26" s="15"/>
       <c r="F26" s="16"/>
     </row>
-    <row r="27" spans="1:6" hidden="1">
-      <c r="A27" s="34"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="31"/>
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="39"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
       <c r="D27" s="15"/>
       <c r="E27" s="15"/>
       <c r="F27" s="16"/>
     </row>
-    <row r="28" spans="1:6" hidden="1">
-      <c r="A28" s="34"/>
-      <c r="B28" s="31"/>
-      <c r="C28" s="32"/>
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="39"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="37"/>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
       <c r="F28" s="16"/>
     </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="34"/>
-      <c r="B29" s="31"/>
-      <c r="C29" s="30" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A29" s="39"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="35" t="s">
         <v>15</v>
       </c>
       <c r="D29" s="19" t="s">
@@ -1739,78 +1817,78 @@
       </c>
       <c r="F29" s="16"/>
     </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="34"/>
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A30" s="39"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="36"/>
       <c r="D30" s="20" t="s">
         <v>98</v>
       </c>
       <c r="E30" s="14"/>
       <c r="F30" s="16"/>
     </row>
-    <row r="31" spans="1:6" hidden="1">
-      <c r="A31" s="34"/>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="39"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="36"/>
       <c r="D31" s="21"/>
       <c r="E31" s="21"/>
       <c r="F31" s="16"/>
     </row>
-    <row r="32" spans="1:6" hidden="1">
-      <c r="A32" s="34"/>
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="39"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="36"/>
       <c r="D32" s="21"/>
       <c r="E32" s="21"/>
       <c r="F32" s="16"/>
     </row>
-    <row r="33" spans="1:6" hidden="1">
-      <c r="A33" s="34"/>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="39"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="36"/>
       <c r="D33" s="21"/>
       <c r="E33" s="21"/>
       <c r="F33" s="16"/>
     </row>
-    <row r="34" spans="1:6" hidden="1">
-      <c r="A34" s="34"/>
-      <c r="B34" s="31"/>
-      <c r="C34" s="31"/>
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="39"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
       <c r="D34" s="21"/>
       <c r="E34" s="21"/>
       <c r="F34" s="16"/>
     </row>
-    <row r="35" spans="1:6" hidden="1">
-      <c r="A35" s="34"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="39"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="36"/>
       <c r="D35" s="21"/>
       <c r="E35" s="21"/>
       <c r="F35" s="16"/>
     </row>
-    <row r="36" spans="1:6" hidden="1">
-      <c r="A36" s="34"/>
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="39"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="36"/>
       <c r="D36" s="21"/>
       <c r="E36" s="21"/>
       <c r="F36" s="16"/>
     </row>
-    <row r="37" spans="1:6" hidden="1">
-      <c r="A37" s="34"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="39"/>
+      <c r="B37" s="37"/>
+      <c r="C37" s="37"/>
       <c r="D37" s="21"/>
       <c r="E37" s="21"/>
       <c r="F37" s="16"/>
     </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="34"/>
-      <c r="B38" s="30" t="s">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A38" s="39"/>
+      <c r="B38" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C38" s="30" t="s">
+      <c r="C38" s="35" t="s">
         <v>24</v>
       </c>
       <c r="D38" s="21" t="s">
@@ -1819,28 +1897,28 @@
       <c r="E38" s="26"/>
       <c r="F38" s="16"/>
     </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="34"/>
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A39" s="39"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="36"/>
       <c r="D39" s="21" t="s">
         <v>111</v>
       </c>
       <c r="E39" s="26"/>
       <c r="F39" s="16"/>
     </row>
-    <row r="40" spans="1:6" hidden="1">
-      <c r="A40" s="34"/>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="39"/>
+      <c r="B40" s="36"/>
+      <c r="C40" s="36"/>
       <c r="D40" s="21"/>
       <c r="E40" s="21"/>
       <c r="F40" s="16"/>
     </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="34"/>
-      <c r="B41" s="31"/>
-      <c r="C41" s="30" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A41" s="39"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="35" t="s">
         <v>25</v>
       </c>
       <c r="D41" s="21" t="s">
@@ -1849,60 +1927,60 @@
       <c r="E41" s="26"/>
       <c r="F41" s="16"/>
     </row>
-    <row r="42" spans="1:6" hidden="1">
-      <c r="A42" s="34"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="39"/>
+      <c r="B42" s="36"/>
+      <c r="C42" s="36"/>
       <c r="D42" s="21"/>
       <c r="E42" s="21"/>
       <c r="F42" s="16"/>
     </row>
-    <row r="43" spans="1:6" hidden="1">
-      <c r="A43" s="34"/>
-      <c r="B43" s="31"/>
-      <c r="C43" s="32"/>
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="39"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="37"/>
       <c r="D43" s="21"/>
       <c r="E43" s="21"/>
       <c r="F43" s="16"/>
     </row>
-    <row r="44" spans="1:6" hidden="1">
-      <c r="A44" s="34"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="30" t="s">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="39"/>
+      <c r="B44" s="36"/>
+      <c r="C44" s="35" t="s">
         <v>26</v>
       </c>
       <c r="D44" s="21"/>
       <c r="E44" s="21"/>
       <c r="F44" s="16"/>
     </row>
-    <row r="45" spans="1:6" hidden="1">
-      <c r="A45" s="34"/>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="39"/>
+      <c r="B45" s="36"/>
+      <c r="C45" s="36"/>
       <c r="D45" s="21"/>
       <c r="E45" s="21"/>
       <c r="F45" s="16"/>
     </row>
-    <row r="46" spans="1:6" hidden="1">
-      <c r="A46" s="34"/>
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="39"/>
+      <c r="B46" s="36"/>
+      <c r="C46" s="36"/>
       <c r="D46" s="21"/>
       <c r="E46" s="21"/>
       <c r="F46" s="16"/>
     </row>
-    <row r="47" spans="1:6" hidden="1">
-      <c r="A47" s="34"/>
-      <c r="B47" s="31"/>
-      <c r="C47" s="32"/>
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="39"/>
+      <c r="B47" s="36"/>
+      <c r="C47" s="37"/>
       <c r="D47" s="21"/>
       <c r="E47" s="21"/>
       <c r="F47" s="16"/>
     </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="34"/>
-      <c r="B48" s="31"/>
-      <c r="C48" s="30" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A48" s="39"/>
+      <c r="B48" s="36"/>
+      <c r="C48" s="35" t="s">
         <v>27</v>
       </c>
       <c r="D48" s="21" t="s">
@@ -1911,18 +1989,18 @@
       <c r="E48" s="26"/>
       <c r="F48" s="16"/>
     </row>
-    <row r="49" spans="1:6" hidden="1">
-      <c r="A49" s="34"/>
-      <c r="B49" s="31"/>
-      <c r="C49" s="32"/>
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A49" s="39"/>
+      <c r="B49" s="36"/>
+      <c r="C49" s="37"/>
       <c r="D49" s="21"/>
       <c r="E49" s="21"/>
       <c r="F49" s="16"/>
     </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="34"/>
-      <c r="B50" s="31"/>
-      <c r="C50" s="30" t="s">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A50" s="39"/>
+      <c r="B50" s="36"/>
+      <c r="C50" s="35" t="s">
         <v>28</v>
       </c>
       <c r="D50" s="21" t="s">
@@ -1931,20 +2009,20 @@
       <c r="E50" s="26"/>
       <c r="F50" s="16"/>
     </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="34"/>
-      <c r="B51" s="31"/>
-      <c r="C51" s="31"/>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A51" s="39"/>
+      <c r="B51" s="36"/>
+      <c r="C51" s="36"/>
       <c r="D51" s="21" t="s">
         <v>97</v>
       </c>
       <c r="E51" s="26"/>
       <c r="F51" s="16"/>
     </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="34"/>
-      <c r="B52" s="31"/>
-      <c r="C52" s="30" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A52" s="39"/>
+      <c r="B52" s="36"/>
+      <c r="C52" s="35" t="s">
         <v>29</v>
       </c>
       <c r="D52" s="21" t="s">
@@ -1953,30 +2031,30 @@
       <c r="E52" s="26"/>
       <c r="F52" s="16"/>
     </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="34"/>
-      <c r="B53" s="31"/>
-      <c r="C53" s="31"/>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A53" s="39"/>
+      <c r="B53" s="36"/>
+      <c r="C53" s="36"/>
       <c r="D53" s="21" t="s">
         <v>81</v>
       </c>
       <c r="E53" s="26"/>
       <c r="F53" s="16"/>
     </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="34"/>
-      <c r="B54" s="31"/>
-      <c r="C54" s="32"/>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A54" s="39"/>
+      <c r="B54" s="36"/>
+      <c r="C54" s="37"/>
       <c r="D54" s="21" t="s">
         <v>82</v>
       </c>
       <c r="E54" s="26"/>
       <c r="F54" s="16"/>
     </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="34"/>
-      <c r="B55" s="31"/>
-      <c r="C55" s="30" t="s">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A55" s="39"/>
+      <c r="B55" s="36"/>
+      <c r="C55" s="35" t="s">
         <v>30</v>
       </c>
       <c r="D55" s="21" t="s">
@@ -1985,46 +2063,46 @@
       <c r="E55" s="26"/>
       <c r="F55" s="16"/>
     </row>
-    <row r="56" spans="1:6">
-      <c r="A56" s="34"/>
-      <c r="B56" s="31"/>
-      <c r="C56" s="31"/>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A56" s="39"/>
+      <c r="B56" s="36"/>
+      <c r="C56" s="36"/>
       <c r="D56" s="21" t="s">
         <v>62</v>
       </c>
       <c r="E56" s="26"/>
       <c r="F56" s="16"/>
     </row>
-    <row r="57" spans="1:6" hidden="1">
-      <c r="A57" s="34"/>
-      <c r="B57" s="31"/>
-      <c r="C57" s="32"/>
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="39"/>
+      <c r="B57" s="36"/>
+      <c r="C57" s="37"/>
       <c r="D57" s="21"/>
       <c r="E57" s="21"/>
       <c r="F57" s="16"/>
     </row>
-    <row r="58" spans="1:6" hidden="1">
-      <c r="A58" s="34"/>
-      <c r="B58" s="31"/>
-      <c r="C58" s="30" t="s">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="39"/>
+      <c r="B58" s="36"/>
+      <c r="C58" s="35" t="s">
         <v>31</v>
       </c>
       <c r="D58" s="21"/>
       <c r="E58" s="21"/>
       <c r="F58" s="16"/>
     </row>
-    <row r="59" spans="1:6" hidden="1">
-      <c r="A59" s="34"/>
-      <c r="B59" s="31"/>
-      <c r="C59" s="31"/>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A59" s="39"/>
+      <c r="B59" s="36"/>
+      <c r="C59" s="36"/>
       <c r="D59" s="21"/>
       <c r="E59" s="21"/>
       <c r="F59" s="16"/>
     </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="34"/>
-      <c r="B60" s="31"/>
-      <c r="C60" s="30" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A60" s="39"/>
+      <c r="B60" s="36"/>
+      <c r="C60" s="35" t="s">
         <v>32</v>
       </c>
       <c r="D60" s="21" t="s">
@@ -2033,44 +2111,44 @@
       <c r="E60" s="26"/>
       <c r="F60" s="16"/>
     </row>
-    <row r="61" spans="1:6">
-      <c r="A61" s="34"/>
-      <c r="B61" s="31"/>
-      <c r="C61" s="31"/>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A61" s="39"/>
+      <c r="B61" s="36"/>
+      <c r="C61" s="36"/>
       <c r="D61" s="21" t="s">
         <v>73</v>
       </c>
       <c r="E61" s="26"/>
       <c r="F61" s="16"/>
     </row>
-    <row r="62" spans="1:6" hidden="1">
-      <c r="A62" s="34"/>
-      <c r="B62" s="31"/>
-      <c r="C62" s="31"/>
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="39"/>
+      <c r="B62" s="36"/>
+      <c r="C62" s="36"/>
       <c r="D62" s="21"/>
       <c r="E62" s="21"/>
       <c r="F62" s="16"/>
     </row>
-    <row r="63" spans="1:6" hidden="1">
-      <c r="A63" s="34"/>
-      <c r="B63" s="31"/>
-      <c r="C63" s="31"/>
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="39"/>
+      <c r="B63" s="36"/>
+      <c r="C63" s="36"/>
       <c r="D63" s="21"/>
       <c r="E63" s="21"/>
       <c r="F63" s="16"/>
     </row>
-    <row r="64" spans="1:6" hidden="1">
-      <c r="A64" s="34"/>
-      <c r="B64" s="31"/>
-      <c r="C64" s="32"/>
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A64" s="39"/>
+      <c r="B64" s="36"/>
+      <c r="C64" s="37"/>
       <c r="D64" s="21"/>
       <c r="E64" s="21"/>
       <c r="F64" s="16"/>
     </row>
-    <row r="65" spans="1:6">
-      <c r="A65" s="34"/>
-      <c r="B65" s="31"/>
-      <c r="C65" s="30" t="s">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A65" s="39"/>
+      <c r="B65" s="36"/>
+      <c r="C65" s="35" t="s">
         <v>33</v>
       </c>
       <c r="D65" s="21" t="s">
@@ -2079,42 +2157,42 @@
       <c r="E65" s="26"/>
       <c r="F65" s="16"/>
     </row>
-    <row r="66" spans="1:6" hidden="1">
-      <c r="A66" s="34"/>
-      <c r="B66" s="31"/>
-      <c r="C66" s="31"/>
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A66" s="39"/>
+      <c r="B66" s="36"/>
+      <c r="C66" s="36"/>
       <c r="D66" s="21"/>
       <c r="E66" s="21"/>
       <c r="F66" s="16"/>
     </row>
-    <row r="67" spans="1:6" hidden="1">
-      <c r="A67" s="34"/>
-      <c r="B67" s="31"/>
-      <c r="C67" s="31"/>
+    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A67" s="39"/>
+      <c r="B67" s="36"/>
+      <c r="C67" s="36"/>
       <c r="D67" s="21"/>
       <c r="E67" s="21"/>
       <c r="F67" s="16"/>
     </row>
-    <row r="68" spans="1:6" hidden="1">
-      <c r="A68" s="34"/>
-      <c r="B68" s="31"/>
-      <c r="C68" s="31"/>
+    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A68" s="39"/>
+      <c r="B68" s="36"/>
+      <c r="C68" s="36"/>
       <c r="D68" s="21"/>
       <c r="E68" s="21"/>
       <c r="F68" s="16"/>
     </row>
-    <row r="69" spans="1:6" hidden="1">
-      <c r="A69" s="34"/>
-      <c r="B69" s="31"/>
-      <c r="C69" s="31"/>
+    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A69" s="39"/>
+      <c r="B69" s="36"/>
+      <c r="C69" s="36"/>
       <c r="D69" s="21"/>
       <c r="E69" s="21"/>
       <c r="F69" s="16"/>
     </row>
-    <row r="70" spans="1:6">
-      <c r="A70" s="34"/>
-      <c r="B70" s="31"/>
-      <c r="C70" s="30" t="s">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A70" s="39"/>
+      <c r="B70" s="36"/>
+      <c r="C70" s="35" t="s">
         <v>34</v>
       </c>
       <c r="D70" s="21" t="s">
@@ -2123,18 +2201,18 @@
       <c r="E70" s="26"/>
       <c r="F70" s="16"/>
     </row>
-    <row r="71" spans="1:6" hidden="1">
-      <c r="A71" s="34"/>
-      <c r="B71" s="31"/>
-      <c r="C71" s="32"/>
+    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A71" s="39"/>
+      <c r="B71" s="36"/>
+      <c r="C71" s="37"/>
       <c r="D71" s="21"/>
       <c r="E71" s="21"/>
       <c r="F71" s="16"/>
     </row>
-    <row r="72" spans="1:6">
-      <c r="A72" s="34"/>
-      <c r="B72" s="31"/>
-      <c r="C72" s="30" t="s">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A72" s="39"/>
+      <c r="B72" s="36"/>
+      <c r="C72" s="35" t="s">
         <v>35</v>
       </c>
       <c r="D72" s="21" t="s">
@@ -2143,22 +2221,22 @@
       <c r="E72" s="26"/>
       <c r="F72" s="16"/>
     </row>
-    <row r="73" spans="1:6">
-      <c r="A73" s="34"/>
-      <c r="B73" s="32"/>
-      <c r="C73" s="31"/>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A73" s="39"/>
+      <c r="B73" s="37"/>
+      <c r="C73" s="36"/>
       <c r="D73" s="21" t="s">
         <v>121</v>
       </c>
       <c r="E73" s="26"/>
       <c r="F73" s="16"/>
     </row>
-    <row r="74" spans="1:6">
-      <c r="A74" s="34"/>
-      <c r="B74" s="30" t="s">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A74" s="39"/>
+      <c r="B74" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C74" s="30" t="s">
+      <c r="C74" s="35" t="s">
         <v>36</v>
       </c>
       <c r="D74" s="15" t="s">
@@ -2167,42 +2245,42 @@
       <c r="E74" s="23"/>
       <c r="F74" s="16"/>
     </row>
-    <row r="75" spans="1:6" hidden="1">
-      <c r="A75" s="34"/>
-      <c r="B75" s="31"/>
-      <c r="C75" s="31"/>
+    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A75" s="39"/>
+      <c r="B75" s="36"/>
+      <c r="C75" s="36"/>
       <c r="D75" s="15"/>
       <c r="E75" s="15"/>
       <c r="F75" s="16"/>
     </row>
-    <row r="76" spans="1:6" hidden="1">
-      <c r="A76" s="34"/>
-      <c r="B76" s="31"/>
-      <c r="C76" s="31"/>
+    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A76" s="39"/>
+      <c r="B76" s="36"/>
+      <c r="C76" s="36"/>
       <c r="D76" s="15"/>
       <c r="E76" s="15"/>
       <c r="F76" s="16"/>
     </row>
-    <row r="77" spans="1:6" hidden="1">
-      <c r="A77" s="34"/>
-      <c r="B77" s="31"/>
-      <c r="C77" s="31"/>
+    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A77" s="39"/>
+      <c r="B77" s="36"/>
+      <c r="C77" s="36"/>
       <c r="D77" s="15"/>
       <c r="E77" s="15"/>
       <c r="F77" s="16"/>
     </row>
-    <row r="78" spans="1:6" hidden="1">
-      <c r="A78" s="34"/>
-      <c r="B78" s="31"/>
-      <c r="C78" s="31"/>
+    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A78" s="39"/>
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
       <c r="D78" s="15"/>
       <c r="E78" s="15"/>
       <c r="F78" s="16"/>
     </row>
-    <row r="79" spans="1:6">
-      <c r="A79" s="34"/>
-      <c r="B79" s="31"/>
-      <c r="C79" s="30" t="s">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A79" s="39"/>
+      <c r="B79" s="36"/>
+      <c r="C79" s="35" t="s">
         <v>37</v>
       </c>
       <c r="D79" s="15" t="s">
@@ -2211,70 +2289,70 @@
       <c r="E79" s="23"/>
       <c r="F79" s="16"/>
     </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="34"/>
-      <c r="B80" s="31"/>
-      <c r="C80" s="31"/>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A80" s="39"/>
+      <c r="B80" s="36"/>
+      <c r="C80" s="36"/>
       <c r="D80" s="15" t="s">
         <v>65</v>
       </c>
       <c r="E80" s="23"/>
       <c r="F80" s="16"/>
     </row>
-    <row r="81" spans="1:6">
-      <c r="A81" s="34"/>
-      <c r="B81" s="31"/>
-      <c r="C81" s="31"/>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A81" s="39"/>
+      <c r="B81" s="36"/>
+      <c r="C81" s="36"/>
       <c r="D81" s="15" t="s">
         <v>66</v>
       </c>
       <c r="E81" s="23"/>
       <c r="F81" s="16"/>
     </row>
-    <row r="82" spans="1:6">
-      <c r="A82" s="34"/>
-      <c r="B82" s="31"/>
-      <c r="C82" s="31"/>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A82" s="39"/>
+      <c r="B82" s="36"/>
+      <c r="C82" s="36"/>
       <c r="D82" s="15" t="s">
         <v>67</v>
       </c>
       <c r="E82" s="23"/>
       <c r="F82" s="16"/>
     </row>
-    <row r="83" spans="1:6">
-      <c r="A83" s="34"/>
-      <c r="B83" s="31"/>
-      <c r="C83" s="31"/>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A83" s="39"/>
+      <c r="B83" s="36"/>
+      <c r="C83" s="36"/>
       <c r="D83" s="15" t="s">
         <v>68</v>
       </c>
       <c r="E83" s="23"/>
       <c r="F83" s="16"/>
     </row>
-    <row r="84" spans="1:6">
-      <c r="A84" s="34"/>
-      <c r="B84" s="31"/>
-      <c r="C84" s="31"/>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A84" s="39"/>
+      <c r="B84" s="36"/>
+      <c r="C84" s="36"/>
       <c r="D84" s="15" t="s">
         <v>69</v>
       </c>
       <c r="E84" s="23"/>
       <c r="F84" s="16"/>
     </row>
-    <row r="85" spans="1:6" hidden="1">
-      <c r="A85" s="34"/>
-      <c r="B85" s="31"/>
-      <c r="C85" s="31"/>
+    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A85" s="39"/>
+      <c r="B85" s="36"/>
+      <c r="C85" s="36"/>
       <c r="D85" s="15"/>
       <c r="E85" s="15"/>
       <c r="F85" s="16"/>
     </row>
-    <row r="86" spans="1:6">
-      <c r="A86" s="34"/>
-      <c r="B86" s="30" t="s">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A86" s="39"/>
+      <c r="B86" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="C86" s="30" t="s">
+      <c r="C86" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D86" s="15" t="s">
@@ -2283,54 +2361,54 @@
       <c r="E86" s="23"/>
       <c r="F86" s="16"/>
     </row>
-    <row r="87" spans="1:6">
-      <c r="A87" s="34"/>
-      <c r="B87" s="31"/>
-      <c r="C87" s="31"/>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A87" s="39"/>
+      <c r="B87" s="36"/>
+      <c r="C87" s="36"/>
       <c r="D87" s="15" t="s">
         <v>100</v>
       </c>
       <c r="E87" s="23"/>
       <c r="F87" s="16"/>
     </row>
-    <row r="88" spans="1:6">
-      <c r="A88" s="34"/>
-      <c r="B88" s="31"/>
-      <c r="C88" s="31"/>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A88" s="39"/>
+      <c r="B88" s="36"/>
+      <c r="C88" s="36"/>
       <c r="D88" s="15" t="s">
         <v>101</v>
       </c>
       <c r="E88" s="23"/>
       <c r="F88" s="16"/>
     </row>
-    <row r="89" spans="1:6" hidden="1">
-      <c r="A89" s="34"/>
-      <c r="B89" s="31"/>
-      <c r="C89" s="31"/>
+    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A89" s="39"/>
+      <c r="B89" s="36"/>
+      <c r="C89" s="36"/>
       <c r="D89" s="15"/>
       <c r="E89" s="15"/>
       <c r="F89" s="16"/>
     </row>
-    <row r="90" spans="1:6" hidden="1">
-      <c r="A90" s="34"/>
-      <c r="B90" s="31"/>
-      <c r="C90" s="31"/>
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A90" s="39"/>
+      <c r="B90" s="36"/>
+      <c r="C90" s="36"/>
       <c r="D90" s="15"/>
       <c r="E90" s="15"/>
       <c r="F90" s="16"/>
     </row>
-    <row r="91" spans="1:6" hidden="1">
-      <c r="A91" s="34"/>
-      <c r="B91" s="31"/>
-      <c r="C91" s="32"/>
+    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A91" s="39"/>
+      <c r="B91" s="36"/>
+      <c r="C91" s="37"/>
       <c r="D91" s="15"/>
       <c r="E91" s="15"/>
       <c r="F91" s="16"/>
     </row>
-    <row r="92" spans="1:6">
-      <c r="A92" s="34"/>
-      <c r="B92" s="31"/>
-      <c r="C92" s="30" t="s">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A92" s="39"/>
+      <c r="B92" s="36"/>
+      <c r="C92" s="35" t="s">
         <v>39</v>
       </c>
       <c r="D92" s="15" t="s">
@@ -2339,54 +2417,54 @@
       <c r="E92" s="23"/>
       <c r="F92" s="16"/>
     </row>
-    <row r="93" spans="1:6">
-      <c r="A93" s="34"/>
-      <c r="B93" s="31"/>
-      <c r="C93" s="31"/>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A93" s="39"/>
+      <c r="B93" s="36"/>
+      <c r="C93" s="36"/>
       <c r="D93" s="15" t="s">
         <v>75</v>
       </c>
       <c r="E93" s="23"/>
       <c r="F93" s="16"/>
     </row>
-    <row r="94" spans="1:6">
-      <c r="A94" s="34"/>
-      <c r="B94" s="31"/>
-      <c r="C94" s="31"/>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A94" s="39"/>
+      <c r="B94" s="36"/>
+      <c r="C94" s="36"/>
       <c r="D94" s="15" t="s">
         <v>76</v>
       </c>
       <c r="E94" s="23"/>
       <c r="F94" s="16"/>
     </row>
-    <row r="95" spans="1:6" hidden="1">
-      <c r="A95" s="34"/>
-      <c r="B95" s="31"/>
-      <c r="C95" s="31"/>
+    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A95" s="39"/>
+      <c r="B95" s="36"/>
+      <c r="C95" s="36"/>
       <c r="D95" s="15"/>
       <c r="E95" s="15"/>
       <c r="F95" s="16"/>
     </row>
-    <row r="96" spans="1:6" hidden="1">
-      <c r="A96" s="34"/>
-      <c r="B96" s="31"/>
-      <c r="C96" s="31"/>
+    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A96" s="39"/>
+      <c r="B96" s="36"/>
+      <c r="C96" s="36"/>
       <c r="D96" s="15"/>
       <c r="E96" s="15"/>
       <c r="F96" s="16"/>
     </row>
-    <row r="97" spans="1:6" hidden="1">
-      <c r="A97" s="34"/>
-      <c r="B97" s="31"/>
-      <c r="C97" s="32"/>
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A97" s="39"/>
+      <c r="B97" s="36"/>
+      <c r="C97" s="37"/>
       <c r="D97" s="15"/>
       <c r="E97" s="15"/>
       <c r="F97" s="16"/>
     </row>
-    <row r="98" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A98" s="34"/>
-      <c r="B98" s="31"/>
-      <c r="C98" s="30" t="s">
+    <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A98" s="39"/>
+      <c r="B98" s="36"/>
+      <c r="C98" s="35" t="s">
         <v>40</v>
       </c>
       <c r="D98" s="15" t="s">
@@ -2395,48 +2473,48 @@
       <c r="E98" s="23"/>
       <c r="F98" s="16"/>
     </row>
-    <row r="99" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A99" s="34"/>
-      <c r="B99" s="31"/>
-      <c r="C99" s="31"/>
+    <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A99" s="39"/>
+      <c r="B99" s="36"/>
+      <c r="C99" s="36"/>
       <c r="D99" s="15" t="s">
         <v>104</v>
       </c>
       <c r="E99" s="23"/>
       <c r="F99" s="16"/>
     </row>
-    <row r="100" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A100" s="34"/>
-      <c r="B100" s="31"/>
-      <c r="C100" s="31"/>
+    <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A100" s="39"/>
+      <c r="B100" s="36"/>
+      <c r="C100" s="36"/>
       <c r="D100" s="15" t="s">
         <v>105</v>
       </c>
       <c r="E100" s="23"/>
       <c r="F100" s="16"/>
     </row>
-    <row r="101" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A101" s="34"/>
-      <c r="B101" s="31"/>
-      <c r="C101" s="31"/>
+    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A101" s="39"/>
+      <c r="B101" s="36"/>
+      <c r="C101" s="36"/>
       <c r="D101" s="15" t="s">
         <v>106</v>
       </c>
       <c r="E101" s="23"/>
       <c r="F101" s="16"/>
     </row>
-    <row r="102" spans="1:6" ht="15.5" hidden="1" customHeight="1">
-      <c r="A102" s="34"/>
-      <c r="B102" s="31"/>
-      <c r="C102" s="32"/>
+    <row r="102" spans="1:6" ht="15.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A102" s="39"/>
+      <c r="B102" s="36"/>
+      <c r="C102" s="37"/>
       <c r="D102" s="15"/>
       <c r="E102" s="15"/>
       <c r="F102" s="16"/>
     </row>
-    <row r="103" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A103" s="34"/>
-      <c r="B103" s="31"/>
-      <c r="C103" s="30" t="s">
+    <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A103" s="39"/>
+      <c r="B103" s="36"/>
+      <c r="C103" s="35" t="s">
         <v>41</v>
       </c>
       <c r="D103" s="15" t="s">
@@ -2445,36 +2523,36 @@
       <c r="E103" s="23"/>
       <c r="F103" s="16"/>
     </row>
-    <row r="104" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A104" s="34"/>
-      <c r="B104" s="31"/>
-      <c r="C104" s="31"/>
+    <row r="104" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A104" s="39"/>
+      <c r="B104" s="36"/>
+      <c r="C104" s="36"/>
       <c r="D104" s="15" t="s">
         <v>115</v>
       </c>
       <c r="E104" s="23"/>
       <c r="F104" s="16"/>
     </row>
-    <row r="105" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A105" s="34"/>
-      <c r="B105" s="31"/>
-      <c r="C105" s="31"/>
+    <row r="105" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A105" s="39"/>
+      <c r="B105" s="36"/>
+      <c r="C105" s="36"/>
       <c r="D105" s="15"/>
       <c r="E105" s="15"/>
       <c r="F105" s="16"/>
     </row>
-    <row r="106" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A106" s="34"/>
-      <c r="B106" s="31"/>
-      <c r="C106" s="32"/>
+    <row r="106" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A106" s="39"/>
+      <c r="B106" s="36"/>
+      <c r="C106" s="37"/>
       <c r="D106" s="15"/>
       <c r="E106" s="15"/>
       <c r="F106" s="16"/>
     </row>
-    <row r="107" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A107" s="34"/>
-      <c r="B107" s="31"/>
-      <c r="C107" s="30" t="s">
+    <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A107" s="39"/>
+      <c r="B107" s="36"/>
+      <c r="C107" s="35" t="s">
         <v>42</v>
       </c>
       <c r="D107" s="15" t="s">
@@ -2483,46 +2561,46 @@
       <c r="E107" s="23"/>
       <c r="F107" s="16"/>
     </row>
-    <row r="108" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A108" s="34"/>
-      <c r="B108" s="31"/>
-      <c r="C108" s="31"/>
+    <row r="108" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A108" s="39"/>
+      <c r="B108" s="36"/>
+      <c r="C108" s="36"/>
       <c r="D108" s="15" t="s">
         <v>124</v>
       </c>
       <c r="E108" s="23"/>
       <c r="F108" s="16"/>
     </row>
-    <row r="109" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A109" s="34"/>
-      <c r="B109" s="31"/>
-      <c r="C109" s="31"/>
+    <row r="109" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A109" s="39"/>
+      <c r="B109" s="36"/>
+      <c r="C109" s="36"/>
       <c r="D109" s="15"/>
       <c r="E109" s="15"/>
       <c r="F109" s="16"/>
     </row>
-    <row r="110" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A110" s="34"/>
-      <c r="B110" s="31"/>
-      <c r="C110" s="31"/>
+    <row r="110" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A110" s="39"/>
+      <c r="B110" s="36"/>
+      <c r="C110" s="36"/>
       <c r="D110" s="15"/>
       <c r="E110" s="15"/>
       <c r="F110" s="16"/>
     </row>
-    <row r="111" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A111" s="34"/>
-      <c r="B111" s="32"/>
-      <c r="C111" s="32"/>
+    <row r="111" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A111" s="39"/>
+      <c r="B111" s="37"/>
+      <c r="C111" s="37"/>
       <c r="D111" s="15"/>
       <c r="E111" s="15"/>
       <c r="F111" s="16"/>
     </row>
-    <row r="112" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A112" s="34"/>
-      <c r="B112" s="30" t="s">
+    <row r="112" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A112" s="39"/>
+      <c r="B112" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="C112" s="30" t="s">
+      <c r="C112" s="35" t="s">
         <v>43</v>
       </c>
       <c r="D112" s="21" t="s">
@@ -2531,26 +2609,26 @@
       <c r="E112" s="26"/>
       <c r="F112" s="16"/>
     </row>
-    <row r="113" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A113" s="34"/>
-      <c r="B113" s="31"/>
-      <c r="C113" s="31"/>
+    <row r="113" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A113" s="39"/>
+      <c r="B113" s="36"/>
+      <c r="C113" s="36"/>
       <c r="D113" s="15"/>
       <c r="E113" s="15"/>
       <c r="F113" s="16"/>
     </row>
-    <row r="114" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A114" s="34"/>
-      <c r="B114" s="31"/>
-      <c r="C114" s="32"/>
+    <row r="114" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A114" s="39"/>
+      <c r="B114" s="36"/>
+      <c r="C114" s="37"/>
       <c r="D114" s="15"/>
       <c r="E114" s="15"/>
       <c r="F114" s="16"/>
     </row>
-    <row r="115" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A115" s="34"/>
-      <c r="B115" s="31"/>
-      <c r="C115" s="30" t="s">
+    <row r="115" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A115" s="39"/>
+      <c r="B115" s="36"/>
+      <c r="C115" s="35" t="s">
         <v>44</v>
       </c>
       <c r="D115" s="15" t="s">
@@ -2559,20 +2637,20 @@
       <c r="E115" s="23"/>
       <c r="F115" s="16"/>
     </row>
-    <row r="116" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A116" s="34"/>
-      <c r="B116" s="32"/>
-      <c r="C116" s="32"/>
+    <row r="116" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A116" s="39"/>
+      <c r="B116" s="37"/>
+      <c r="C116" s="37"/>
       <c r="D116" s="15"/>
       <c r="E116" s="15"/>
       <c r="F116" s="16"/>
     </row>
-    <row r="117" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A117" s="34"/>
-      <c r="B117" s="30" t="s">
+    <row r="117" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A117" s="39"/>
+      <c r="B117" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="C117" s="30" t="s">
+      <c r="C117" s="35" t="s">
         <v>45</v>
       </c>
       <c r="D117" s="15" t="s">
@@ -2581,50 +2659,50 @@
       <c r="E117" s="23"/>
       <c r="F117" s="16"/>
     </row>
-    <row r="118" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A118" s="34"/>
-      <c r="B118" s="31"/>
-      <c r="C118" s="31"/>
+    <row r="118" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A118" s="39"/>
+      <c r="B118" s="36"/>
+      <c r="C118" s="36"/>
       <c r="D118" s="15"/>
       <c r="E118" s="15"/>
       <c r="F118" s="16"/>
     </row>
-    <row r="119" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A119" s="34"/>
-      <c r="B119" s="31"/>
-      <c r="C119" s="31"/>
+    <row r="119" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A119" s="39"/>
+      <c r="B119" s="36"/>
+      <c r="C119" s="36"/>
       <c r="D119" s="15"/>
       <c r="E119" s="15"/>
       <c r="F119" s="16"/>
     </row>
-    <row r="120" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A120" s="34"/>
-      <c r="B120" s="31"/>
-      <c r="C120" s="31"/>
+    <row r="120" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A120" s="39"/>
+      <c r="B120" s="36"/>
+      <c r="C120" s="36"/>
       <c r="D120" s="15"/>
       <c r="E120" s="15"/>
       <c r="F120" s="16"/>
     </row>
-    <row r="121" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A121" s="34"/>
-      <c r="B121" s="31"/>
-      <c r="C121" s="31"/>
+    <row r="121" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A121" s="39"/>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
       <c r="D121" s="15"/>
       <c r="E121" s="15"/>
       <c r="F121" s="16"/>
     </row>
-    <row r="122" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A122" s="34"/>
-      <c r="B122" s="31"/>
-      <c r="C122" s="32"/>
+    <row r="122" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A122" s="39"/>
+      <c r="B122" s="36"/>
+      <c r="C122" s="37"/>
       <c r="D122" s="15"/>
       <c r="E122" s="15"/>
       <c r="F122" s="16"/>
     </row>
-    <row r="123" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A123" s="34"/>
-      <c r="B123" s="31"/>
-      <c r="C123" s="30" t="s">
+    <row r="123" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A123" s="39"/>
+      <c r="B123" s="36"/>
+      <c r="C123" s="35" t="s">
         <v>46</v>
       </c>
       <c r="D123" s="15" t="s">
@@ -2633,18 +2711,18 @@
       <c r="E123" s="23"/>
       <c r="F123" s="16"/>
     </row>
-    <row r="124" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A124" s="34"/>
-      <c r="B124" s="31"/>
-      <c r="C124" s="31"/>
+    <row r="124" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A124" s="39"/>
+      <c r="B124" s="36"/>
+      <c r="C124" s="36"/>
       <c r="D124" s="15"/>
       <c r="E124" s="15"/>
       <c r="F124" s="16"/>
     </row>
-    <row r="125" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A125" s="34"/>
-      <c r="B125" s="31"/>
-      <c r="C125" s="30" t="s">
+    <row r="125" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A125" s="39"/>
+      <c r="B125" s="36"/>
+      <c r="C125" s="35" t="s">
         <v>47</v>
       </c>
       <c r="D125" s="15" t="s">
@@ -2653,58 +2731,58 @@
       <c r="E125" s="23"/>
       <c r="F125" s="16"/>
     </row>
-    <row r="126" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A126" s="34"/>
-      <c r="B126" s="31"/>
-      <c r="C126" s="31"/>
+    <row r="126" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A126" s="39"/>
+      <c r="B126" s="36"/>
+      <c r="C126" s="36"/>
       <c r="D126" s="15"/>
       <c r="E126" s="15"/>
       <c r="F126" s="16"/>
     </row>
-    <row r="127" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A127" s="34"/>
-      <c r="B127" s="31"/>
-      <c r="C127" s="31"/>
+    <row r="127" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A127" s="39"/>
+      <c r="B127" s="36"/>
+      <c r="C127" s="36"/>
       <c r="D127" s="15"/>
       <c r="E127" s="15"/>
       <c r="F127" s="16"/>
     </row>
-    <row r="128" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A128" s="34"/>
-      <c r="B128" s="31"/>
-      <c r="C128" s="31"/>
+    <row r="128" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A128" s="39"/>
+      <c r="B128" s="36"/>
+      <c r="C128" s="36"/>
       <c r="D128" s="15"/>
       <c r="E128" s="15"/>
       <c r="F128" s="16"/>
     </row>
-    <row r="129" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A129" s="34"/>
-      <c r="B129" s="31"/>
-      <c r="C129" s="31"/>
+    <row r="129" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A129" s="39"/>
+      <c r="B129" s="36"/>
+      <c r="C129" s="36"/>
       <c r="D129" s="15"/>
       <c r="E129" s="15"/>
       <c r="F129" s="16"/>
     </row>
-    <row r="130" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A130" s="34"/>
-      <c r="B130" s="31"/>
-      <c r="C130" s="31"/>
+    <row r="130" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A130" s="39"/>
+      <c r="B130" s="36"/>
+      <c r="C130" s="36"/>
       <c r="D130" s="15"/>
       <c r="E130" s="15"/>
       <c r="F130" s="16"/>
     </row>
-    <row r="131" spans="1:6" ht="15" hidden="1" customHeight="1">
-      <c r="A131" s="34"/>
-      <c r="B131" s="31"/>
-      <c r="C131" s="32"/>
+    <row r="131" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A131" s="39"/>
+      <c r="B131" s="36"/>
+      <c r="C131" s="37"/>
       <c r="D131" s="15"/>
       <c r="E131" s="15"/>
       <c r="F131" s="16"/>
     </row>
-    <row r="132" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A132" s="34"/>
-      <c r="B132" s="31"/>
-      <c r="C132" s="30" t="s">
+    <row r="132" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A132" s="39"/>
+      <c r="B132" s="36"/>
+      <c r="C132" s="35" t="s">
         <v>48</v>
       </c>
       <c r="D132" s="15" t="s">
@@ -2713,26 +2791,26 @@
       <c r="E132" s="23"/>
       <c r="F132" s="16"/>
     </row>
-    <row r="133" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A133" s="34"/>
-      <c r="B133" s="31"/>
-      <c r="C133" s="31"/>
+    <row r="133" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A133" s="39"/>
+      <c r="B133" s="36"/>
+      <c r="C133" s="36"/>
       <c r="D133" s="15"/>
       <c r="E133" s="15"/>
       <c r="F133" s="16"/>
     </row>
-    <row r="134" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A134" s="34"/>
-      <c r="B134" s="31"/>
-      <c r="C134" s="32"/>
+    <row r="134" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A134" s="39"/>
+      <c r="B134" s="36"/>
+      <c r="C134" s="37"/>
       <c r="D134" s="15"/>
       <c r="E134" s="15"/>
       <c r="F134" s="16"/>
     </row>
-    <row r="135" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A135" s="34"/>
-      <c r="B135" s="31"/>
-      <c r="C135" s="30" t="s">
+    <row r="135" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A135" s="39"/>
+      <c r="B135" s="36"/>
+      <c r="C135" s="35" t="s">
         <v>49</v>
       </c>
       <c r="D135" s="15" t="s">
@@ -2741,48 +2819,48 @@
       <c r="E135" s="23"/>
       <c r="F135" s="16"/>
     </row>
-    <row r="136" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A136" s="34"/>
-      <c r="B136" s="31"/>
-      <c r="C136" s="31"/>
+    <row r="136" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A136" s="39"/>
+      <c r="B136" s="36"/>
+      <c r="C136" s="36"/>
       <c r="D136" s="15" t="s">
         <v>126</v>
       </c>
       <c r="E136" s="23"/>
       <c r="F136" s="16"/>
     </row>
-    <row r="137" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A137" s="34"/>
-      <c r="B137" s="31"/>
-      <c r="C137" s="31"/>
+    <row r="137" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A137" s="39"/>
+      <c r="B137" s="36"/>
+      <c r="C137" s="36"/>
       <c r="D137" s="15" t="s">
         <v>127</v>
       </c>
       <c r="E137" s="23"/>
       <c r="F137" s="16"/>
     </row>
-    <row r="138" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A138" s="34"/>
-      <c r="B138" s="31"/>
-      <c r="C138" s="31"/>
+    <row r="138" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A138" s="39"/>
+      <c r="B138" s="36"/>
+      <c r="C138" s="36"/>
       <c r="D138" s="15"/>
       <c r="E138" s="15"/>
       <c r="F138" s="16"/>
     </row>
-    <row r="139" spans="1:6" ht="15.75" hidden="1" customHeight="1">
-      <c r="A139" s="34"/>
-      <c r="B139" s="31"/>
-      <c r="C139" s="31"/>
+    <row r="139" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A139" s="39"/>
+      <c r="B139" s="36"/>
+      <c r="C139" s="36"/>
       <c r="D139" s="15"/>
       <c r="E139" s="15"/>
       <c r="F139" s="16"/>
     </row>
-    <row r="140" spans="1:6">
-      <c r="A140" s="34"/>
-      <c r="B140" s="30" t="s">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A140" s="39"/>
+      <c r="B140" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="C140" s="30" t="s">
+      <c r="C140" s="35" t="s">
         <v>50</v>
       </c>
       <c r="D140" s="15" t="s">
@@ -2791,30 +2869,30 @@
       <c r="E140" s="23"/>
       <c r="F140" s="16"/>
     </row>
-    <row r="141" spans="1:6">
-      <c r="A141" s="34"/>
-      <c r="B141" s="31"/>
-      <c r="C141" s="31"/>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A141" s="39"/>
+      <c r="B141" s="36"/>
+      <c r="C141" s="36"/>
       <c r="D141" s="15" t="s">
         <v>71</v>
       </c>
       <c r="E141" s="23"/>
       <c r="F141" s="16"/>
     </row>
-    <row r="142" spans="1:6">
-      <c r="A142" s="34"/>
-      <c r="B142" s="31"/>
-      <c r="C142" s="31"/>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A142" s="39"/>
+      <c r="B142" s="36"/>
+      <c r="C142" s="36"/>
       <c r="D142" s="15" t="s">
         <v>83</v>
       </c>
       <c r="E142" s="23"/>
       <c r="F142" s="16"/>
     </row>
-    <row r="143" spans="1:6">
-      <c r="A143" s="34"/>
-      <c r="B143" s="31"/>
-      <c r="C143" s="30" t="s">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A143" s="39"/>
+      <c r="B143" s="36"/>
+      <c r="C143" s="35" t="s">
         <v>51</v>
       </c>
       <c r="D143" s="15" t="s">
@@ -2823,40 +2901,40 @@
       <c r="E143" s="23"/>
       <c r="F143" s="16"/>
     </row>
-    <row r="144" spans="1:6">
-      <c r="A144" s="34"/>
-      <c r="B144" s="31"/>
-      <c r="C144" s="31"/>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A144" s="39"/>
+      <c r="B144" s="36"/>
+      <c r="C144" s="36"/>
       <c r="D144" s="15" t="s">
         <v>117</v>
       </c>
       <c r="E144" s="23"/>
       <c r="F144" s="16"/>
     </row>
-    <row r="145" spans="1:6">
-      <c r="A145" s="34"/>
-      <c r="B145" s="31"/>
-      <c r="C145" s="31"/>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A145" s="39"/>
+      <c r="B145" s="36"/>
+      <c r="C145" s="36"/>
       <c r="D145" s="15" t="s">
         <v>118</v>
       </c>
       <c r="E145" s="23"/>
       <c r="F145" s="16"/>
     </row>
-    <row r="146" spans="1:6">
-      <c r="A146" s="34"/>
-      <c r="B146" s="31"/>
-      <c r="C146" s="31"/>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A146" s="39"/>
+      <c r="B146" s="36"/>
+      <c r="C146" s="36"/>
       <c r="D146" s="15" t="s">
         <v>119</v>
       </c>
       <c r="E146" s="23"/>
       <c r="F146" s="16"/>
     </row>
-    <row r="147" spans="1:6">
-      <c r="A147" s="34"/>
-      <c r="B147" s="31"/>
-      <c r="C147" s="30" t="s">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A147" s="39"/>
+      <c r="B147" s="36"/>
+      <c r="C147" s="35" t="s">
         <v>52</v>
       </c>
       <c r="D147" s="15" t="s">
@@ -2865,34 +2943,34 @@
       <c r="E147" s="23"/>
       <c r="F147" s="16"/>
     </row>
-    <row r="148" spans="1:6" hidden="1">
-      <c r="A148" s="34"/>
-      <c r="B148" s="31"/>
-      <c r="C148" s="31"/>
+    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A148" s="39"/>
+      <c r="B148" s="36"/>
+      <c r="C148" s="36"/>
       <c r="D148" s="15"/>
       <c r="E148" s="15"/>
       <c r="F148" s="16"/>
     </row>
-    <row r="149" spans="1:6" hidden="1">
-      <c r="A149" s="34"/>
-      <c r="B149" s="31"/>
-      <c r="C149" s="31"/>
+    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A149" s="39"/>
+      <c r="B149" s="36"/>
+      <c r="C149" s="36"/>
       <c r="D149" s="15"/>
       <c r="E149" s="15"/>
       <c r="F149" s="16"/>
     </row>
-    <row r="150" spans="1:6" hidden="1">
-      <c r="A150" s="34"/>
-      <c r="B150" s="31"/>
-      <c r="C150" s="31"/>
+    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A150" s="39"/>
+      <c r="B150" s="36"/>
+      <c r="C150" s="36"/>
       <c r="D150" s="15"/>
       <c r="E150" s="15"/>
       <c r="F150" s="16"/>
     </row>
-    <row r="151" spans="1:6">
-      <c r="A151" s="34"/>
-      <c r="B151" s="31"/>
-      <c r="C151" s="30" t="s">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A151" s="39"/>
+      <c r="B151" s="36"/>
+      <c r="C151" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D151" s="15" t="s">
@@ -2901,44 +2979,44 @@
       <c r="E151" s="23"/>
       <c r="F151" s="16"/>
     </row>
-    <row r="152" spans="1:6" hidden="1">
-      <c r="A152" s="34"/>
-      <c r="B152" s="31"/>
-      <c r="C152" s="31"/>
+    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A152" s="39"/>
+      <c r="B152" s="36"/>
+      <c r="C152" s="36"/>
       <c r="D152" s="15"/>
       <c r="E152" s="15"/>
       <c r="F152" s="16"/>
     </row>
-    <row r="153" spans="1:6" hidden="1">
-      <c r="A153" s="34"/>
-      <c r="B153" s="31"/>
-      <c r="C153" s="31"/>
+    <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A153" s="39"/>
+      <c r="B153" s="36"/>
+      <c r="C153" s="36"/>
       <c r="D153" s="15"/>
       <c r="E153" s="15"/>
       <c r="F153" s="16"/>
     </row>
-    <row r="154" spans="1:6" hidden="1">
-      <c r="A154" s="34"/>
-      <c r="B154" s="31"/>
-      <c r="C154" s="31"/>
+    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A154" s="39"/>
+      <c r="B154" s="36"/>
+      <c r="C154" s="36"/>
       <c r="D154" s="15"/>
       <c r="E154" s="15"/>
       <c r="F154" s="16"/>
     </row>
-    <row r="155" spans="1:6" hidden="1">
-      <c r="A155" s="34"/>
-      <c r="B155" s="31"/>
-      <c r="C155" s="31"/>
+    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A155" s="39"/>
+      <c r="B155" s="36"/>
+      <c r="C155" s="36"/>
       <c r="D155" s="15"/>
       <c r="E155" s="15"/>
       <c r="F155" s="16"/>
     </row>
-    <row r="156" spans="1:6">
-      <c r="A156" s="34"/>
-      <c r="B156" s="30" t="s">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A156" s="39"/>
+      <c r="B156" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C156" s="30" t="s">
+      <c r="C156" s="35" t="s">
         <v>54</v>
       </c>
       <c r="D156" s="15" t="s">
@@ -2947,20 +3025,20 @@
       <c r="E156" s="23"/>
       <c r="F156" s="16"/>
     </row>
-    <row r="157" spans="1:6">
-      <c r="A157" s="34"/>
-      <c r="B157" s="31"/>
-      <c r="C157" s="32"/>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A157" s="39"/>
+      <c r="B157" s="36"/>
+      <c r="C157" s="37"/>
       <c r="D157" s="15" t="s">
         <v>93</v>
       </c>
       <c r="E157" s="23"/>
       <c r="F157" s="16"/>
     </row>
-    <row r="158" spans="1:6">
-      <c r="A158" s="34"/>
-      <c r="B158" s="31"/>
-      <c r="C158" s="30" t="s">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A158" s="39"/>
+      <c r="B158" s="36"/>
+      <c r="C158" s="35" t="s">
         <v>55</v>
       </c>
       <c r="D158" s="15" t="s">
@@ -2969,16 +3047,16 @@
       <c r="E158" s="23"/>
       <c r="F158" s="16"/>
     </row>
-    <row r="159" spans="1:6" hidden="1">
-      <c r="A159" s="34"/>
-      <c r="B159" s="32"/>
-      <c r="C159" s="32"/>
+    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A159" s="39"/>
+      <c r="B159" s="37"/>
+      <c r="C159" s="37"/>
       <c r="D159" s="15"/>
       <c r="E159" s="15"/>
       <c r="F159" s="16"/>
     </row>
-    <row r="160" spans="1:6" hidden="1">
-      <c r="A160" s="34"/>
+    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A160" s="39"/>
       <c r="B160" s="10" t="s">
         <v>23</v>
       </c>
@@ -2987,51 +3065,51 @@
       <c r="E160" s="15"/>
       <c r="F160" s="16"/>
     </row>
-    <row r="161" spans="1:8" hidden="1">
-      <c r="A161" s="34"/>
+    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A161" s="39"/>
       <c r="B161" s="11"/>
       <c r="C161" s="11"/>
       <c r="D161" s="15"/>
       <c r="E161" s="15"/>
       <c r="F161" s="16"/>
     </row>
-    <row r="162" spans="1:8" hidden="1">
-      <c r="A162" s="34"/>
+    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A162" s="39"/>
       <c r="B162" s="11"/>
       <c r="C162" s="11"/>
       <c r="D162" s="15"/>
       <c r="E162" s="15"/>
       <c r="F162" s="16"/>
     </row>
-    <row r="163" spans="1:8" hidden="1">
-      <c r="A163" s="35"/>
+    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A163" s="40"/>
       <c r="B163" s="12"/>
       <c r="C163" s="12"/>
       <c r="D163" s="15"/>
       <c r="E163" s="15"/>
       <c r="F163" s="16"/>
     </row>
-    <row r="164" spans="1:8" hidden="1">
+    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="E164" s="3"/>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.45">
       <c r="G165" s="9"/>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.45">
       <c r="G166" s="9"/>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.45">
       <c r="G167" s="9"/>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.45">
       <c r="G168" s="9"/>
       <c r="H168" s="7"/>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.45">
       <c r="G169" s="9"/>
       <c r="H169" s="8"/>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.45">
       <c r="H170" s="8"/>
     </row>
   </sheetData>
@@ -3105,8 +3183,8 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:I157"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <dimension ref="A1:I165"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="21.25" customWidth="1"/>
     <col min="2" max="2" width="18.58203125" customWidth="1"/>
@@ -3118,22 +3196,22 @@
     <col min="9" max="9" width="7.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="D1"/>
     </row>
-    <row r="2" spans="1:8" s="4" customFormat="1" ht="30" customHeight="1">
+    <row r="2" spans="1:8" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="27"/>
-      <c r="H2" s="48"/>
-    </row>
-    <row r="3" spans="1:8" ht="8.25" customHeight="1">
+      <c r="H2" s="34"/>
+    </row>
+    <row r="3" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="D3"/>
     </row>
-    <row r="4" spans="1:8" ht="26.25" customHeight="1">
+    <row r="4" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -3144,7 +3222,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>3</v>
+        <v>184</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>129</v>
@@ -3156,11 +3234,11 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="33" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="35" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="13"/>
@@ -3174,9 +3252,9 @@
         <v>138</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="34"/>
-      <c r="B6" s="31"/>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" s="39"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="13" t="s">
         <v>130</v>
       </c>
@@ -3185,10 +3263,10 @@
       <c r="F6" s="23"/>
       <c r="G6" s="19"/>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="34"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="30" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" s="39"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="35" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="15" t="s">
@@ -3198,10 +3276,10 @@
       <c r="F7" s="23"/>
       <c r="G7" s="19"/>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="34"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="32"/>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A8" s="39"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="37"/>
       <c r="D8" s="15" t="s">
         <v>95</v>
       </c>
@@ -3209,58 +3287,58 @@
       <c r="F8" s="23"/>
       <c r="G8" s="19"/>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="34"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>87</v>
+    <row r="9" spans="1:8" ht="34" x14ac:dyDescent="0.45">
+      <c r="A9" s="39"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>88</v>
       </c>
       <c r="E9" s="24"/>
       <c r="F9" s="24"/>
-      <c r="G9" s="19"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="34"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="G9" s="17" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A10" s="39"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
       <c r="G10" s="19"/>
     </row>
-    <row r="11" spans="1:8" ht="34">
-      <c r="A11" s="34"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>88</v>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A11" s="39"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>87</v>
       </c>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
-      <c r="G11" s="17" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="34"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
+      <c r="G11" s="19"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A12" s="39"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
       <c r="G12" s="19"/>
     </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="34"/>
-      <c r="B13" s="30" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A13" s="39"/>
+      <c r="B13" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="35" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="18" t="s">
@@ -3270,28 +3348,28 @@
       <c r="F13" s="25"/>
       <c r="G13" s="19"/>
     </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="34"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A14" s="39"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
       <c r="D14" s="18"/>
       <c r="E14" s="18"/>
       <c r="F14" s="18"/>
       <c r="G14" s="19"/>
     </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="34"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="32"/>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A15" s="39"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="37"/>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
       <c r="F15" s="18"/>
       <c r="G15" s="19"/>
     </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="34"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="30" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A16" s="39"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="35" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="18" t="s">
@@ -3301,10 +3379,10 @@
       <c r="F16" s="25"/>
       <c r="G16" s="19"/>
     </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="34"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A17" s="39"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
       <c r="D17" s="18" t="s">
         <v>60</v>
       </c>
@@ -3312,18 +3390,18 @@
       <c r="F17" s="25"/>
       <c r="G17" s="19"/>
     </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="34"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="32"/>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A18" s="39"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="37"/>
       <c r="D18" s="18"/>
       <c r="E18" s="18"/>
       <c r="F18" s="18"/>
       <c r="G18" s="19"/>
     </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="34"/>
-      <c r="B19" s="31"/>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A19" s="39"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="13" t="s">
         <v>12</v>
       </c>
@@ -3334,9 +3412,9 @@
       <c r="F19" s="25"/>
       <c r="G19" s="19"/>
     </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="34"/>
-      <c r="B20" s="31"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A20" s="39"/>
+      <c r="B20" s="36"/>
       <c r="C20" s="13" t="s">
         <v>13</v>
       </c>
@@ -3349,10 +3427,10 @@
       <c r="F20" s="23"/>
       <c r="G20" s="19"/>
     </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="34"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="30" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A21" s="39"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="35" t="s">
         <v>14</v>
       </c>
       <c r="D21" s="15"/>
@@ -3360,37 +3438,37 @@
       <c r="F21" s="15"/>
       <c r="G21" s="19"/>
     </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="34"/>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A22" s="39"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="15"/>
       <c r="G22" s="19"/>
     </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="34"/>
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A23" s="39"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
       <c r="F23" s="15"/>
       <c r="G23" s="19"/>
     </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="34"/>
-      <c r="B24" s="31"/>
-      <c r="C24" s="32"/>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A24" s="39"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="37"/>
       <c r="D24" s="19"/>
       <c r="E24" s="19"/>
       <c r="F24" s="19"/>
       <c r="G24" s="19"/>
     </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="34"/>
-      <c r="B25" s="31"/>
-      <c r="C25" s="30" t="s">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A25" s="39"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="35" t="s">
         <v>15</v>
       </c>
       <c r="D25" s="19" t="s">
@@ -3402,10 +3480,10 @@
       <c r="F25" s="16"/>
       <c r="G25" s="19"/>
     </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="34"/>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A26" s="39"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="36"/>
       <c r="D26" s="20" t="s">
         <v>98</v>
       </c>
@@ -3413,30 +3491,30 @@
       <c r="F26" s="14"/>
       <c r="G26" s="19"/>
     </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="34"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="31"/>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A27" s="39"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
       <c r="D27" s="21"/>
       <c r="E27" s="21"/>
       <c r="F27" s="21"/>
       <c r="G27" s="19"/>
     </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="34"/>
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A28" s="39"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
       <c r="D28" s="21"/>
       <c r="E28" s="21"/>
       <c r="F28" s="21"/>
       <c r="G28" s="19"/>
     </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="34"/>
-      <c r="B29" s="30" t="s">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A29" s="39"/>
+      <c r="B29" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="30" t="s">
+      <c r="C29" s="35" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="21" t="s">
@@ -3446,10 +3524,10 @@
       <c r="F29" s="26"/>
       <c r="G29" s="19"/>
     </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="34"/>
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A30" s="39"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="36"/>
       <c r="D30" s="21" t="s">
         <v>111</v>
       </c>
@@ -3457,19 +3535,19 @@
       <c r="F30" s="26"/>
       <c r="G30" s="19"/>
     </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="34"/>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A31" s="39"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="36"/>
       <c r="D31" s="21"/>
       <c r="E31" s="21"/>
       <c r="F31" s="21"/>
       <c r="G31" s="19"/>
     </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="34"/>
-      <c r="B32" s="31"/>
-      <c r="C32" s="30" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A32" s="39"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="35" t="s">
         <v>25</v>
       </c>
       <c r="D32" s="21" t="s">
@@ -3479,28 +3557,28 @@
       <c r="F32" s="26"/>
       <c r="G32" s="19"/>
     </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="34"/>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A33" s="39"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="36"/>
       <c r="D33" s="21"/>
       <c r="E33" s="21"/>
       <c r="F33" s="21"/>
       <c r="G33" s="19"/>
     </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="34"/>
-      <c r="B34" s="31"/>
-      <c r="C34" s="32"/>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A34" s="39"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="37"/>
       <c r="D34" s="21"/>
       <c r="E34" s="21"/>
       <c r="F34" s="21"/>
       <c r="G34" s="19"/>
     </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="34"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="30" t="s">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A35" s="39"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="35" t="s">
         <v>26</v>
       </c>
       <c r="D35" s="21"/>
@@ -3508,37 +3586,37 @@
       <c r="F35" s="21"/>
       <c r="G35" s="19"/>
     </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="34"/>
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A36" s="39"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="36"/>
       <c r="D36" s="21"/>
       <c r="E36" s="21"/>
       <c r="F36" s="21"/>
       <c r="G36" s="19"/>
     </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="34"/>
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A37" s="39"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="36"/>
       <c r="D37" s="21"/>
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
       <c r="G37" s="19"/>
     </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="34"/>
-      <c r="B38" s="31"/>
-      <c r="C38" s="32"/>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A38" s="39"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="37"/>
       <c r="D38" s="21"/>
       <c r="E38" s="21"/>
       <c r="F38" s="21"/>
       <c r="G38" s="19"/>
     </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="34"/>
-      <c r="B39" s="31"/>
-      <c r="C39" s="30" t="s">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A39" s="39"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="35" t="s">
         <v>27</v>
       </c>
       <c r="D39" s="21" t="s">
@@ -3548,19 +3626,19 @@
       <c r="F39" s="26"/>
       <c r="G39" s="19"/>
     </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="34"/>
-      <c r="B40" s="31"/>
-      <c r="C40" s="32"/>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A40" s="39"/>
+      <c r="B40" s="36"/>
+      <c r="C40" s="37"/>
       <c r="D40" s="21"/>
       <c r="E40" s="21"/>
       <c r="F40" s="21"/>
       <c r="G40" s="19"/>
     </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="34"/>
-      <c r="B41" s="31"/>
-      <c r="C41" s="30" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A41" s="39"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="35" t="s">
         <v>28</v>
       </c>
       <c r="D41" s="21" t="s">
@@ -3570,10 +3648,10 @@
       <c r="F41" s="26"/>
       <c r="G41" s="19"/>
     </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="34"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A42" s="39"/>
+      <c r="B42" s="36"/>
+      <c r="C42" s="36"/>
       <c r="D42" s="21" t="s">
         <v>97</v>
       </c>
@@ -3581,10 +3659,10 @@
       <c r="F42" s="26"/>
       <c r="G42" s="19"/>
     </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="34"/>
-      <c r="B43" s="31"/>
-      <c r="C43" s="30" t="s">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A43" s="39"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="35" t="s">
         <v>29</v>
       </c>
       <c r="D43" s="21" t="s">
@@ -3594,10 +3672,10 @@
       <c r="F43" s="26"/>
       <c r="G43" s="19"/>
     </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="34"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="31"/>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A44" s="39"/>
+      <c r="B44" s="36"/>
+      <c r="C44" s="36"/>
       <c r="D44" s="21" t="s">
         <v>81</v>
       </c>
@@ -3605,10 +3683,10 @@
       <c r="F44" s="26"/>
       <c r="G44" s="19"/>
     </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="34"/>
-      <c r="B45" s="31"/>
-      <c r="C45" s="32"/>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A45" s="39"/>
+      <c r="B45" s="36"/>
+      <c r="C45" s="37"/>
       <c r="D45" s="21" t="s">
         <v>82</v>
       </c>
@@ -3616,10 +3694,10 @@
       <c r="F45" s="26"/>
       <c r="G45" s="19"/>
     </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="34"/>
-      <c r="B46" s="31"/>
-      <c r="C46" s="30" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A46" s="39"/>
+      <c r="B46" s="36"/>
+      <c r="C46" s="35" t="s">
         <v>30</v>
       </c>
       <c r="D46" s="21" t="s">
@@ -3629,10 +3707,10 @@
       <c r="F46" s="26"/>
       <c r="G46" s="19"/>
     </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="34"/>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A47" s="39"/>
+      <c r="B47" s="36"/>
+      <c r="C47" s="36"/>
       <c r="D47" s="21" t="s">
         <v>62</v>
       </c>
@@ -3640,19 +3718,19 @@
       <c r="F47" s="26"/>
       <c r="G47" s="19"/>
     </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="34"/>
-      <c r="B48" s="31"/>
-      <c r="C48" s="32"/>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A48" s="39"/>
+      <c r="B48" s="36"/>
+      <c r="C48" s="37"/>
       <c r="D48" s="21"/>
       <c r="E48" s="21"/>
       <c r="F48" s="21"/>
       <c r="G48" s="19"/>
     </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="34"/>
-      <c r="B49" s="31"/>
-      <c r="C49" s="30" t="s">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A49" s="39"/>
+      <c r="B49" s="36"/>
+      <c r="C49" s="35" t="s">
         <v>31</v>
       </c>
       <c r="D49" s="21"/>
@@ -3660,19 +3738,19 @@
       <c r="F49" s="21"/>
       <c r="G49" s="19"/>
     </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="34"/>
-      <c r="B50" s="31"/>
-      <c r="C50" s="31"/>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A50" s="39"/>
+      <c r="B50" s="36"/>
+      <c r="C50" s="36"/>
       <c r="D50" s="21"/>
       <c r="E50" s="21"/>
       <c r="F50" s="21"/>
       <c r="G50" s="19"/>
     </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="34"/>
-      <c r="B51" s="31"/>
-      <c r="C51" s="30" t="s">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A51" s="39"/>
+      <c r="B51" s="36"/>
+      <c r="C51" s="35" t="s">
         <v>32</v>
       </c>
       <c r="D51" s="21" t="s">
@@ -3682,10 +3760,10 @@
       <c r="F51" s="26"/>
       <c r="G51" s="19"/>
     </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="34"/>
-      <c r="B52" s="31"/>
-      <c r="C52" s="31"/>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A52" s="39"/>
+      <c r="B52" s="36"/>
+      <c r="C52" s="36"/>
       <c r="D52" s="21" t="s">
         <v>73</v>
       </c>
@@ -3693,19 +3771,19 @@
       <c r="F52" s="26"/>
       <c r="G52" s="19"/>
     </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="34"/>
-      <c r="B53" s="31"/>
-      <c r="C53" s="31"/>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A53" s="39"/>
+      <c r="B53" s="36"/>
+      <c r="C53" s="36"/>
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
       <c r="F53" s="21"/>
       <c r="G53" s="19"/>
     </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="34"/>
-      <c r="B54" s="31"/>
-      <c r="C54" s="30" t="s">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A54" s="39"/>
+      <c r="B54" s="36"/>
+      <c r="C54" s="35" t="s">
         <v>33</v>
       </c>
       <c r="D54" s="21" t="s">
@@ -3715,28 +3793,28 @@
       <c r="F54" s="26"/>
       <c r="G54" s="19"/>
     </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="34"/>
-      <c r="B55" s="31"/>
-      <c r="C55" s="31"/>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A55" s="39"/>
+      <c r="B55" s="36"/>
+      <c r="C55" s="36"/>
       <c r="D55" s="21"/>
       <c r="E55" s="21"/>
       <c r="F55" s="21"/>
       <c r="G55" s="19"/>
     </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="34"/>
-      <c r="B56" s="31"/>
-      <c r="C56" s="31"/>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A56" s="39"/>
+      <c r="B56" s="36"/>
+      <c r="C56" s="36"/>
       <c r="D56" s="21"/>
       <c r="E56" s="21"/>
       <c r="F56" s="21"/>
       <c r="G56" s="19"/>
     </row>
-    <row r="57" spans="1:7">
-      <c r="A57" s="34"/>
-      <c r="B57" s="31"/>
-      <c r="C57" s="30" t="s">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A57" s="39"/>
+      <c r="B57" s="36"/>
+      <c r="C57" s="35" t="s">
         <v>34</v>
       </c>
       <c r="D57" s="21" t="s">
@@ -3746,19 +3824,19 @@
       <c r="F57" s="26"/>
       <c r="G57" s="19"/>
     </row>
-    <row r="58" spans="1:7">
-      <c r="A58" s="34"/>
-      <c r="B58" s="31"/>
-      <c r="C58" s="32"/>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A58" s="39"/>
+      <c r="B58" s="36"/>
+      <c r="C58" s="37"/>
       <c r="D58" s="21"/>
       <c r="E58" s="21"/>
       <c r="F58" s="21"/>
       <c r="G58" s="19"/>
     </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="34"/>
-      <c r="B59" s="31"/>
-      <c r="C59" s="30" t="s">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A59" s="39"/>
+      <c r="B59" s="36"/>
+      <c r="C59" s="35" t="s">
         <v>35</v>
       </c>
       <c r="D59" s="21" t="s">
@@ -3768,10 +3846,10 @@
       <c r="F59" s="26"/>
       <c r="G59" s="19"/>
     </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="34"/>
-      <c r="B60" s="32"/>
-      <c r="C60" s="31"/>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A60" s="39"/>
+      <c r="B60" s="37"/>
+      <c r="C60" s="36"/>
       <c r="D60" s="21" t="s">
         <v>121</v>
       </c>
@@ -3779,12 +3857,12 @@
       <c r="F60" s="26"/>
       <c r="G60" s="19"/>
     </row>
-    <row r="61" spans="1:7">
-      <c r="A61" s="34"/>
-      <c r="B61" s="30" t="s">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A61" s="39"/>
+      <c r="B61" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C61" s="30" t="s">
+      <c r="C61" s="35" t="s">
         <v>36</v>
       </c>
       <c r="D61" s="15" t="s">
@@ -3796,19 +3874,19 @@
       </c>
       <c r="G61" s="19"/>
     </row>
-    <row r="62" spans="1:7">
-      <c r="A62" s="34"/>
-      <c r="B62" s="31"/>
-      <c r="C62" s="31"/>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A62" s="39"/>
+      <c r="B62" s="36"/>
+      <c r="C62" s="36"/>
       <c r="D62" s="15"/>
       <c r="E62" s="15"/>
       <c r="F62" s="16"/>
       <c r="G62" s="19"/>
     </row>
-    <row r="63" spans="1:7">
-      <c r="A63" s="34"/>
-      <c r="B63" s="31"/>
-      <c r="C63" s="30" t="s">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A63" s="39"/>
+      <c r="B63" s="36"/>
+      <c r="C63" s="35" t="s">
         <v>37</v>
       </c>
       <c r="D63" s="15" t="s">
@@ -3820,10 +3898,10 @@
       </c>
       <c r="G63" s="19"/>
     </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="34"/>
-      <c r="B64" s="31"/>
-      <c r="C64" s="31"/>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A64" s="39"/>
+      <c r="B64" s="36"/>
+      <c r="C64" s="36"/>
       <c r="D64" s="15" t="s">
         <v>65</v>
       </c>
@@ -3833,10 +3911,10 @@
       </c>
       <c r="G64" s="19"/>
     </row>
-    <row r="65" spans="1:7">
-      <c r="A65" s="34"/>
-      <c r="B65" s="31"/>
-      <c r="C65" s="31"/>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A65" s="39"/>
+      <c r="B65" s="36"/>
+      <c r="C65" s="36"/>
       <c r="D65" s="15" t="s">
         <v>66</v>
       </c>
@@ -3846,10 +3924,10 @@
       </c>
       <c r="G65" s="19"/>
     </row>
-    <row r="66" spans="1:7">
-      <c r="A66" s="34"/>
-      <c r="B66" s="31"/>
-      <c r="C66" s="31"/>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A66" s="39"/>
+      <c r="B66" s="36"/>
+      <c r="C66" s="36"/>
       <c r="D66" s="15" t="s">
         <v>67</v>
       </c>
@@ -3859,10 +3937,10 @@
       </c>
       <c r="G66" s="19"/>
     </row>
-    <row r="67" spans="1:7">
-      <c r="A67" s="34"/>
-      <c r="B67" s="31"/>
-      <c r="C67" s="31"/>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A67" s="39"/>
+      <c r="B67" s="36"/>
+      <c r="C67" s="36"/>
       <c r="D67" s="15" t="s">
         <v>68</v>
       </c>
@@ -3872,10 +3950,10 @@
       </c>
       <c r="G67" s="19"/>
     </row>
-    <row r="68" spans="1:7">
-      <c r="A68" s="34"/>
-      <c r="B68" s="31"/>
-      <c r="C68" s="31"/>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A68" s="39"/>
+      <c r="B68" s="36"/>
+      <c r="C68" s="36"/>
       <c r="D68" s="15" t="s">
         <v>69</v>
       </c>
@@ -3885,12 +3963,12 @@
       </c>
       <c r="G68" s="19"/>
     </row>
-    <row r="69" spans="1:7">
-      <c r="A69" s="34"/>
-      <c r="B69" s="30" t="s">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A69" s="39"/>
+      <c r="B69" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="C69" s="30" t="s">
+      <c r="C69" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D69" s="15" t="s">
@@ -3902,10 +3980,10 @@
       </c>
       <c r="G69" s="19"/>
     </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="34"/>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A70" s="39"/>
+      <c r="B70" s="36"/>
+      <c r="C70" s="36"/>
       <c r="D70" s="15" t="s">
         <v>100</v>
       </c>
@@ -3915,10 +3993,10 @@
       </c>
       <c r="G70" s="19"/>
     </row>
-    <row r="71" spans="1:7">
-      <c r="A71" s="34"/>
-      <c r="B71" s="31"/>
-      <c r="C71" s="31"/>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A71" s="39"/>
+      <c r="B71" s="36"/>
+      <c r="C71" s="36"/>
       <c r="D71" s="15" t="s">
         <v>101</v>
       </c>
@@ -3928,10 +4006,10 @@
       </c>
       <c r="G71" s="19"/>
     </row>
-    <row r="72" spans="1:7">
-      <c r="A72" s="34"/>
-      <c r="B72" s="31"/>
-      <c r="C72" s="30" t="s">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A72" s="39"/>
+      <c r="B72" s="36"/>
+      <c r="C72" s="35" t="s">
         <v>39</v>
       </c>
       <c r="D72" s="15" t="s">
@@ -3943,10 +4021,10 @@
       </c>
       <c r="G72" s="19"/>
     </row>
-    <row r="73" spans="1:7">
-      <c r="A73" s="34"/>
-      <c r="B73" s="31"/>
-      <c r="C73" s="31"/>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A73" s="39"/>
+      <c r="B73" s="36"/>
+      <c r="C73" s="36"/>
       <c r="D73" s="15" t="s">
         <v>75</v>
       </c>
@@ -3956,10 +4034,10 @@
       </c>
       <c r="G73" s="19"/>
     </row>
-    <row r="74" spans="1:7">
-      <c r="A74" s="34"/>
-      <c r="B74" s="31"/>
-      <c r="C74" s="31"/>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A74" s="39"/>
+      <c r="B74" s="36"/>
+      <c r="C74" s="36"/>
       <c r="D74" s="15" t="s">
         <v>76</v>
       </c>
@@ -3969,10 +4047,10 @@
       </c>
       <c r="G74" s="19"/>
     </row>
-    <row r="75" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A75" s="34"/>
-      <c r="B75" s="31"/>
-      <c r="C75" s="30" t="s">
+    <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A75" s="39"/>
+      <c r="B75" s="36"/>
+      <c r="C75" s="35" t="s">
         <v>40</v>
       </c>
       <c r="D75" s="15" t="s">
@@ -3984,10 +4062,10 @@
       </c>
       <c r="G75" s="19"/>
     </row>
-    <row r="76" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A76" s="34"/>
-      <c r="B76" s="31"/>
-      <c r="C76" s="31"/>
+    <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A76" s="39"/>
+      <c r="B76" s="36"/>
+      <c r="C76" s="36"/>
       <c r="D76" s="15" t="s">
         <v>104</v>
       </c>
@@ -3997,10 +4075,10 @@
       </c>
       <c r="G76" s="19"/>
     </row>
-    <row r="77" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A77" s="34"/>
-      <c r="B77" s="31"/>
-      <c r="C77" s="31"/>
+    <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A77" s="39"/>
+      <c r="B77" s="36"/>
+      <c r="C77" s="36"/>
       <c r="D77" s="15" t="s">
         <v>105</v>
       </c>
@@ -4010,10 +4088,10 @@
       </c>
       <c r="G77" s="19"/>
     </row>
-    <row r="78" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A78" s="34"/>
-      <c r="B78" s="31"/>
-      <c r="C78" s="31"/>
+    <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A78" s="39"/>
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
       <c r="D78" s="15" t="s">
         <v>106</v>
       </c>
@@ -4023,10 +4101,10 @@
       </c>
       <c r="G78" s="19"/>
     </row>
-    <row r="79" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A79" s="34"/>
-      <c r="B79" s="31"/>
-      <c r="C79" s="30" t="s">
+    <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A79" s="39"/>
+      <c r="B79" s="36"/>
+      <c r="C79" s="35" t="s">
         <v>41</v>
       </c>
       <c r="D79" s="15" t="s">
@@ -4038,10 +4116,10 @@
       </c>
       <c r="G79" s="19"/>
     </row>
-    <row r="80" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A80" s="34"/>
-      <c r="B80" s="31"/>
-      <c r="C80" s="31"/>
+    <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A80" s="39"/>
+      <c r="B80" s="36"/>
+      <c r="C80" s="36"/>
       <c r="D80" s="15" t="s">
         <v>115</v>
       </c>
@@ -4051,10 +4129,10 @@
       </c>
       <c r="G80" s="19"/>
     </row>
-    <row r="81" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A81" s="34"/>
-      <c r="B81" s="31"/>
-      <c r="C81" s="30" t="s">
+    <row r="81" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A81" s="39"/>
+      <c r="B81" s="36"/>
+      <c r="C81" s="35" t="s">
         <v>42</v>
       </c>
       <c r="D81" s="15" t="s">
@@ -4066,10 +4144,10 @@
       </c>
       <c r="G81" s="19"/>
     </row>
-    <row r="82" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A82" s="34"/>
-      <c r="B82" s="31"/>
-      <c r="C82" s="31"/>
+    <row r="82" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A82" s="39"/>
+      <c r="B82" s="36"/>
+      <c r="C82" s="36"/>
       <c r="D82" s="15" t="s">
         <v>124</v>
       </c>
@@ -4079,12 +4157,12 @@
       </c>
       <c r="G82" s="19"/>
     </row>
-    <row r="83" spans="1:7" ht="15.5" customHeight="1">
-      <c r="A83" s="34"/>
-      <c r="B83" s="30" t="s">
+    <row r="83" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A83" s="39"/>
+      <c r="B83" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="C83" s="30" t="s">
+      <c r="C83" s="35" t="s">
         <v>43</v>
       </c>
       <c r="D83" s="21" t="s">
@@ -4094,19 +4172,19 @@
       <c r="F83" s="26"/>
       <c r="G83" s="19"/>
     </row>
-    <row r="84" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A84" s="34"/>
-      <c r="B84" s="31"/>
-      <c r="C84" s="32"/>
+    <row r="84" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A84" s="39"/>
+      <c r="B84" s="36"/>
+      <c r="C84" s="37"/>
       <c r="D84" s="15"/>
       <c r="E84" s="15"/>
       <c r="F84" s="15"/>
       <c r="G84" s="19"/>
     </row>
-    <row r="85" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A85" s="34"/>
-      <c r="B85" s="31"/>
-      <c r="C85" s="30" t="s">
+    <row r="85" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A85" s="39"/>
+      <c r="B85" s="36"/>
+      <c r="C85" s="35" t="s">
         <v>44</v>
       </c>
       <c r="D85" s="15" t="s">
@@ -4116,21 +4194,21 @@
       <c r="F85" s="23"/>
       <c r="G85" s="19"/>
     </row>
-    <row r="86" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A86" s="34"/>
-      <c r="B86" s="32"/>
-      <c r="C86" s="32"/>
+    <row r="86" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A86" s="39"/>
+      <c r="B86" s="37"/>
+      <c r="C86" s="37"/>
       <c r="D86" s="15"/>
       <c r="E86" s="15"/>
       <c r="F86" s="15"/>
       <c r="G86" s="19"/>
     </row>
-    <row r="87" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A87" s="34"/>
-      <c r="B87" s="30" t="s">
+    <row r="87" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A87" s="39"/>
+      <c r="B87" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="C87" s="30" t="s">
+      <c r="C87" s="35" t="s">
         <v>45</v>
       </c>
       <c r="D87" s="15" t="s">
@@ -4140,28 +4218,28 @@
       <c r="F87" s="23"/>
       <c r="G87" s="19"/>
     </row>
-    <row r="88" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A88" s="34"/>
-      <c r="B88" s="31"/>
-      <c r="C88" s="31"/>
+    <row r="88" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A88" s="39"/>
+      <c r="B88" s="36"/>
+      <c r="C88" s="36"/>
       <c r="D88" s="15"/>
       <c r="E88" s="15"/>
       <c r="F88" s="15"/>
       <c r="G88" s="19"/>
     </row>
-    <row r="89" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A89" s="34"/>
-      <c r="B89" s="31"/>
-      <c r="C89" s="32"/>
+    <row r="89" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A89" s="39"/>
+      <c r="B89" s="36"/>
+      <c r="C89" s="37"/>
       <c r="D89" s="15"/>
       <c r="E89" s="15"/>
       <c r="F89" s="15"/>
       <c r="G89" s="19"/>
     </row>
-    <row r="90" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A90" s="34"/>
-      <c r="B90" s="31"/>
-      <c r="C90" s="30" t="s">
+    <row r="90" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A90" s="39"/>
+      <c r="B90" s="36"/>
+      <c r="C90" s="35" t="s">
         <v>46</v>
       </c>
       <c r="D90" s="15" t="s">
@@ -4171,19 +4249,19 @@
       <c r="F90" s="23"/>
       <c r="G90" s="19"/>
     </row>
-    <row r="91" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A91" s="34"/>
-      <c r="B91" s="31"/>
-      <c r="C91" s="31"/>
+    <row r="91" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A91" s="39"/>
+      <c r="B91" s="36"/>
+      <c r="C91" s="36"/>
       <c r="D91" s="15"/>
       <c r="E91" s="15"/>
       <c r="F91" s="15"/>
       <c r="G91" s="19"/>
     </row>
-    <row r="92" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A92" s="34"/>
-      <c r="B92" s="31"/>
-      <c r="C92" s="30" t="s">
+    <row r="92" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A92" s="39"/>
+      <c r="B92" s="36"/>
+      <c r="C92" s="35" t="s">
         <v>47</v>
       </c>
       <c r="D92" s="15" t="s">
@@ -4193,19 +4271,19 @@
       <c r="F92" s="23"/>
       <c r="G92" s="19"/>
     </row>
-    <row r="93" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A93" s="34"/>
-      <c r="B93" s="31"/>
-      <c r="C93" s="31"/>
+    <row r="93" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A93" s="39"/>
+      <c r="B93" s="36"/>
+      <c r="C93" s="36"/>
       <c r="D93" s="15"/>
       <c r="E93" s="15"/>
       <c r="F93" s="15"/>
       <c r="G93" s="19"/>
     </row>
-    <row r="94" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A94" s="34"/>
-      <c r="B94" s="31"/>
-      <c r="C94" s="30" t="s">
+    <row r="94" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A94" s="39"/>
+      <c r="B94" s="36"/>
+      <c r="C94" s="35" t="s">
         <v>48</v>
       </c>
       <c r="D94" s="15" t="s">
@@ -4215,19 +4293,19 @@
       <c r="F94" s="23"/>
       <c r="G94" s="19"/>
     </row>
-    <row r="95" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A95" s="34"/>
-      <c r="B95" s="31"/>
-      <c r="C95" s="31"/>
+    <row r="95" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A95" s="39"/>
+      <c r="B95" s="36"/>
+      <c r="C95" s="36"/>
       <c r="D95" s="15"/>
       <c r="E95" s="15"/>
       <c r="F95" s="15"/>
       <c r="G95" s="19"/>
     </row>
-    <row r="96" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A96" s="34"/>
-      <c r="B96" s="31"/>
-      <c r="C96" s="30" t="s">
+    <row r="96" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A96" s="39"/>
+      <c r="B96" s="36"/>
+      <c r="C96" s="35" t="s">
         <v>49</v>
       </c>
       <c r="D96" s="15" t="s">
@@ -4237,10 +4315,10 @@
       <c r="F96" s="23"/>
       <c r="G96" s="19"/>
     </row>
-    <row r="97" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A97" s="34"/>
-      <c r="B97" s="31"/>
-      <c r="C97" s="31"/>
+    <row r="97" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A97" s="39"/>
+      <c r="B97" s="36"/>
+      <c r="C97" s="36"/>
       <c r="D97" s="15" t="s">
         <v>126</v>
       </c>
@@ -4248,10 +4326,10 @@
       <c r="F97" s="23"/>
       <c r="G97" s="19"/>
     </row>
-    <row r="98" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A98" s="34"/>
-      <c r="B98" s="31"/>
-      <c r="C98" s="31"/>
+    <row r="98" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A98" s="39"/>
+      <c r="B98" s="36"/>
+      <c r="C98" s="36"/>
       <c r="D98" s="15" t="s">
         <v>127</v>
       </c>
@@ -4259,30 +4337,30 @@
       <c r="F98" s="23"/>
       <c r="G98" s="19"/>
     </row>
-    <row r="99" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A99" s="34"/>
-      <c r="B99" s="31"/>
-      <c r="C99" s="31"/>
+    <row r="99" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A99" s="39"/>
+      <c r="B99" s="36"/>
+      <c r="C99" s="36"/>
       <c r="D99" s="15"/>
       <c r="E99" s="15"/>
       <c r="F99" s="15"/>
       <c r="G99" s="19"/>
     </row>
-    <row r="100" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A100" s="34"/>
-      <c r="B100" s="31"/>
-      <c r="C100" s="31"/>
+    <row r="100" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A100" s="39"/>
+      <c r="B100" s="36"/>
+      <c r="C100" s="36"/>
       <c r="D100" s="15"/>
       <c r="E100" s="15"/>
       <c r="F100" s="15"/>
       <c r="G100" s="19"/>
     </row>
-    <row r="101" spans="1:7">
-      <c r="A101" s="34"/>
-      <c r="B101" s="30" t="s">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A101" s="39"/>
+      <c r="B101" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="C101" s="30" t="s">
+      <c r="C101" s="35" t="s">
         <v>50</v>
       </c>
       <c r="D101" s="15" t="s">
@@ -4292,10 +4370,10 @@
       <c r="F101" s="23"/>
       <c r="G101" s="19"/>
     </row>
-    <row r="102" spans="1:7">
-      <c r="A102" s="34"/>
-      <c r="B102" s="31"/>
-      <c r="C102" s="31"/>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A102" s="39"/>
+      <c r="B102" s="36"/>
+      <c r="C102" s="36"/>
       <c r="D102" s="15" t="s">
         <v>71</v>
       </c>
@@ -4303,10 +4381,10 @@
       <c r="F102" s="23"/>
       <c r="G102" s="19"/>
     </row>
-    <row r="103" spans="1:7">
-      <c r="A103" s="34"/>
-      <c r="B103" s="31"/>
-      <c r="C103" s="31"/>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A103" s="39"/>
+      <c r="B103" s="36"/>
+      <c r="C103" s="36"/>
       <c r="D103" s="15" t="s">
         <v>83</v>
       </c>
@@ -4314,10 +4392,10 @@
       <c r="F103" s="23"/>
       <c r="G103" s="19"/>
     </row>
-    <row r="104" spans="1:7">
-      <c r="A104" s="34"/>
-      <c r="B104" s="31"/>
-      <c r="C104" s="30" t="s">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A104" s="39"/>
+      <c r="B104" s="36"/>
+      <c r="C104" s="35" t="s">
         <v>51</v>
       </c>
       <c r="D104" s="15" t="s">
@@ -4327,10 +4405,10 @@
       <c r="F104" s="23"/>
       <c r="G104" s="19"/>
     </row>
-    <row r="105" spans="1:7">
-      <c r="A105" s="34"/>
-      <c r="B105" s="31"/>
-      <c r="C105" s="31"/>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A105" s="39"/>
+      <c r="B105" s="36"/>
+      <c r="C105" s="36"/>
       <c r="D105" s="15" t="s">
         <v>117</v>
       </c>
@@ -4338,10 +4416,10 @@
       <c r="F105" s="23"/>
       <c r="G105" s="19"/>
     </row>
-    <row r="106" spans="1:7">
-      <c r="A106" s="34"/>
-      <c r="B106" s="31"/>
-      <c r="C106" s="31"/>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A106" s="39"/>
+      <c r="B106" s="36"/>
+      <c r="C106" s="36"/>
       <c r="D106" s="15" t="s">
         <v>118</v>
       </c>
@@ -4349,10 +4427,10 @@
       <c r="F106" s="23"/>
       <c r="G106" s="19"/>
     </row>
-    <row r="107" spans="1:7">
-      <c r="A107" s="34"/>
-      <c r="B107" s="31"/>
-      <c r="C107" s="31"/>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A107" s="39"/>
+      <c r="B107" s="36"/>
+      <c r="C107" s="36"/>
       <c r="D107" s="15" t="s">
         <v>119</v>
       </c>
@@ -4360,10 +4438,10 @@
       <c r="F107" s="23"/>
       <c r="G107" s="19"/>
     </row>
-    <row r="108" spans="1:7">
-      <c r="A108" s="34"/>
-      <c r="B108" s="31"/>
-      <c r="C108" s="30" t="s">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A108" s="39"/>
+      <c r="B108" s="36"/>
+      <c r="C108" s="35" t="s">
         <v>52</v>
       </c>
       <c r="D108" s="15" t="s">
@@ -4373,18 +4451,18 @@
       <c r="F108" s="23"/>
       <c r="G108" s="19"/>
     </row>
-    <row r="109" spans="1:7">
-      <c r="A109" s="34"/>
-      <c r="B109" s="31"/>
-      <c r="C109" s="31"/>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A109" s="39"/>
+      <c r="B109" s="36"/>
+      <c r="C109" s="36"/>
       <c r="D109" s="15"/>
       <c r="E109" s="15"/>
       <c r="F109" s="15"/>
       <c r="G109" s="19"/>
     </row>
-    <row r="110" spans="1:7">
-      <c r="A110" s="34"/>
-      <c r="B110" s="31"/>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A110" s="39"/>
+      <c r="B110" s="36"/>
       <c r="C110" s="13" t="s">
         <v>53</v>
       </c>
@@ -4395,12 +4473,12 @@
       <c r="F110" s="23"/>
       <c r="G110" s="19"/>
     </row>
-    <row r="111" spans="1:7">
-      <c r="A111" s="34"/>
-      <c r="B111" s="30" t="s">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A111" s="39"/>
+      <c r="B111" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C111" s="30" t="s">
+      <c r="C111" s="35" t="s">
         <v>54</v>
       </c>
       <c r="D111" s="15" t="s">
@@ -4410,10 +4488,10 @@
       <c r="F111" s="23"/>
       <c r="G111" s="19"/>
     </row>
-    <row r="112" spans="1:7">
-      <c r="A112" s="34"/>
-      <c r="B112" s="31"/>
-      <c r="C112" s="32"/>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A112" s="39"/>
+      <c r="B112" s="36"/>
+      <c r="C112" s="37"/>
       <c r="D112" s="15" t="s">
         <v>93</v>
       </c>
@@ -4421,10 +4499,10 @@
       <c r="F112" s="23"/>
       <c r="G112" s="19"/>
     </row>
-    <row r="113" spans="1:8">
-      <c r="A113" s="34"/>
-      <c r="B113" s="31"/>
-      <c r="C113" s="30" t="s">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A113" s="39"/>
+      <c r="B113" s="36"/>
+      <c r="C113" s="35" t="s">
         <v>55</v>
       </c>
       <c r="D113" s="15" t="s">
@@ -4434,17 +4512,17 @@
       <c r="F113" s="23"/>
       <c r="G113" s="19"/>
     </row>
-    <row r="114" spans="1:8">
-      <c r="A114" s="34"/>
-      <c r="B114" s="32"/>
-      <c r="C114" s="32"/>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A114" s="39"/>
+      <c r="B114" s="37"/>
+      <c r="C114" s="37"/>
       <c r="D114" s="15"/>
       <c r="E114" s="15"/>
       <c r="F114" s="15"/>
       <c r="G114" s="19"/>
     </row>
-    <row r="115" spans="1:8">
-      <c r="A115" s="34"/>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A115" s="39"/>
       <c r="B115" s="10" t="s">
         <v>23</v>
       </c>
@@ -4454,8 +4532,8 @@
       <c r="F115" s="15"/>
       <c r="G115" s="19"/>
     </row>
-    <row r="116" spans="1:8">
-      <c r="A116" s="34"/>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A116" s="39"/>
       <c r="B116" s="11"/>
       <c r="C116" s="11"/>
       <c r="D116" s="15"/>
@@ -4463,8 +4541,8 @@
       <c r="F116" s="15"/>
       <c r="G116" s="19"/>
     </row>
-    <row r="117" spans="1:8">
-      <c r="A117" s="34"/>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A117" s="39"/>
       <c r="B117" s="11"/>
       <c r="C117" s="11"/>
       <c r="D117" s="15"/>
@@ -4472,8 +4550,8 @@
       <c r="F117" s="15"/>
       <c r="G117" s="19"/>
     </row>
-    <row r="118" spans="1:8">
-      <c r="A118" s="35"/>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A118" s="40"/>
       <c r="B118" s="12"/>
       <c r="C118" s="12"/>
       <c r="D118" s="15"/>
@@ -4481,11 +4559,11 @@
       <c r="F118" s="15"/>
       <c r="G118" s="19"/>
     </row>
-    <row r="119" spans="1:8">
-      <c r="A119" s="33" t="s">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A119" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="B119" s="36" t="s">
+      <c r="B119" s="43" t="s">
         <v>141</v>
       </c>
       <c r="C119" s="28"/>
@@ -4494,27 +4572,27 @@
       <c r="F119" s="19"/>
       <c r="G119" s="19"/>
     </row>
-    <row r="120" spans="1:8">
-      <c r="A120" s="34"/>
-      <c r="B120" s="37"/>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A120" s="39"/>
+      <c r="B120" s="41"/>
       <c r="C120" s="28"/>
       <c r="D120" s="19"/>
       <c r="E120" s="19"/>
       <c r="F120" s="19"/>
       <c r="G120" s="19"/>
     </row>
-    <row r="121" spans="1:8">
-      <c r="A121" s="34"/>
-      <c r="B121" s="38"/>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A121" s="39"/>
+      <c r="B121" s="42"/>
       <c r="C121" s="28"/>
       <c r="D121" s="19"/>
       <c r="E121" s="19"/>
       <c r="F121" s="19"/>
       <c r="G121" s="19"/>
     </row>
-    <row r="122" spans="1:8">
-      <c r="A122" s="34"/>
-      <c r="B122" s="36" t="s">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A122" s="39"/>
+      <c r="B122" s="43" t="s">
         <v>142</v>
       </c>
       <c r="C122" s="28" t="s">
@@ -4525,424 +4603,532 @@
       <c r="F122" s="19"/>
       <c r="G122" s="19"/>
       <c r="H122" s="9" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8">
-      <c r="A123" s="34"/>
-      <c r="B123" s="37"/>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A123" s="39"/>
+      <c r="B123" s="41"/>
       <c r="C123" s="28" t="s">
         <v>145</v>
       </c>
       <c r="D123" s="19" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E123" s="19"/>
-      <c r="F123" s="19"/>
-      <c r="G123" s="19"/>
-    </row>
-    <row r="124" spans="1:8">
-      <c r="A124" s="34"/>
-      <c r="B124" s="37"/>
-      <c r="C124" s="28" t="s">
+      <c r="F123" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="G123" s="19" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A124" s="39"/>
+      <c r="B124" s="41"/>
+      <c r="C124" s="28"/>
+      <c r="D124" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="E124" s="19"/>
+      <c r="F124" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="G124" s="19" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A125" s="39"/>
+      <c r="B125" s="41"/>
+      <c r="C125" s="28"/>
+      <c r="D125" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="E125" s="19"/>
+      <c r="F125" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="G125" s="19" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A126" s="39"/>
+      <c r="B126" s="41"/>
+      <c r="C126" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="D124" s="19" t="s">
+      <c r="D126" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="E126" s="19"/>
+      <c r="F126" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="G126" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="E124" s="19"/>
-      <c r="F124" s="19"/>
-      <c r="G124" s="19"/>
-    </row>
-    <row r="125" spans="1:8">
-      <c r="A125" s="34"/>
-      <c r="B125" s="37"/>
-      <c r="C125" s="28" t="s">
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A127" s="39"/>
+      <c r="B127" s="41"/>
+      <c r="C127" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="D125" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="E125" s="19"/>
-      <c r="F125" s="19"/>
-      <c r="G125" s="19" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8">
-      <c r="A126" s="34"/>
-      <c r="B126" s="37"/>
-      <c r="C126" s="28" t="s">
-        <v>149</v>
-      </c>
-      <c r="D126" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="E126" s="19"/>
-      <c r="F126" s="19"/>
-      <c r="G126" s="19"/>
-    </row>
-    <row r="127" spans="1:8">
-      <c r="A127" s="34"/>
-      <c r="B127" s="37"/>
-      <c r="C127" s="28" t="s">
-        <v>178</v>
-      </c>
       <c r="D127" s="19" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E127" s="19"/>
       <c r="F127" s="19"/>
-      <c r="G127" s="19"/>
-    </row>
-    <row r="128" spans="1:8">
-      <c r="A128" s="34"/>
-      <c r="B128" s="37"/>
-      <c r="C128" s="28"/>
-      <c r="D128" s="19"/>
+      <c r="G127" s="19" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A128" s="39"/>
+      <c r="B128" s="41"/>
+      <c r="C128" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="D128" s="19" t="s">
+        <v>174</v>
+      </c>
       <c r="E128" s="19"/>
-      <c r="F128" s="19"/>
-      <c r="G128" s="19"/>
-    </row>
-    <row r="129" spans="1:8">
-      <c r="A129" s="34"/>
-      <c r="B129" s="37"/>
-      <c r="C129" s="28"/>
-      <c r="D129" s="19"/>
+      <c r="F128" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="G128" s="19" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A129" s="39"/>
+      <c r="B129" s="41"/>
+      <c r="C129" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="D129" s="19" t="s">
+        <v>175</v>
+      </c>
       <c r="E129" s="19"/>
       <c r="F129" s="19"/>
       <c r="G129" s="19"/>
     </row>
-    <row r="130" spans="1:8">
-      <c r="A130" s="34"/>
-      <c r="B130" s="37"/>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A130" s="39"/>
+      <c r="B130" s="41"/>
       <c r="C130" s="28"/>
       <c r="D130" s="19"/>
       <c r="E130" s="19"/>
       <c r="F130" s="19"/>
       <c r="G130" s="19"/>
     </row>
-    <row r="131" spans="1:8" ht="17.5" thickBot="1">
-      <c r="A131" s="43"/>
-      <c r="B131" s="44"/>
-      <c r="C131" s="45"/>
-      <c r="D131" s="46"/>
-      <c r="E131" s="47"/>
-      <c r="F131" s="47"/>
-      <c r="G131" s="46"/>
-    </row>
-    <row r="132" spans="1:8">
-      <c r="A132" s="34" t="s">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A131" s="39"/>
+      <c r="B131" s="41"/>
+      <c r="C131" s="28"/>
+      <c r="D131" s="19"/>
+      <c r="E131" s="19"/>
+      <c r="F131" s="19"/>
+      <c r="G131" s="19"/>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A132" s="39"/>
+      <c r="B132" s="41"/>
+      <c r="C132" s="28"/>
+      <c r="D132" s="19"/>
+      <c r="E132" s="19"/>
+      <c r="F132" s="19"/>
+      <c r="G132" s="19"/>
+    </row>
+    <row r="133" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A133" s="47"/>
+      <c r="B133" s="48"/>
+      <c r="C133" s="31"/>
+      <c r="D133" s="32"/>
+      <c r="E133" s="33"/>
+      <c r="F133" s="33"/>
+      <c r="G133" s="32"/>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A134" s="39" t="s">
         <v>150</v>
       </c>
-      <c r="B132" s="37" t="s">
+      <c r="B134" s="41" t="s">
         <v>151</v>
       </c>
-      <c r="C132" s="40" t="s">
-        <v>154</v>
-      </c>
-      <c r="D132" s="42" t="s">
-        <v>165</v>
-      </c>
-      <c r="E132" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="F132" s="14"/>
-      <c r="G132" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="H132" s="9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8">
-      <c r="A133" s="34"/>
-      <c r="B133" s="37"/>
-      <c r="C133" s="40"/>
-      <c r="D133" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="E133" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="F133" s="16"/>
-      <c r="G133" s="19" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8">
-      <c r="A134" s="34"/>
-      <c r="B134" s="37"/>
-      <c r="C134" s="40"/>
-      <c r="D134" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="E134" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="F134" s="16"/>
-      <c r="G134" s="19" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8">
-      <c r="A135" s="34"/>
-      <c r="B135" s="37"/>
-      <c r="C135" s="41"/>
+      <c r="C134" s="45" t="s">
+        <v>153</v>
+      </c>
+      <c r="D134" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="E134" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="F134" s="14"/>
+      <c r="G134" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="H134" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A135" s="39"/>
+      <c r="B135" s="41"/>
+      <c r="C135" s="45"/>
       <c r="D135" s="17" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E135" s="16" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F135" s="16"/>
       <c r="G135" s="19" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8">
-      <c r="A136" s="34"/>
-      <c r="B136" s="37"/>
-      <c r="C136" s="28" t="s">
-        <v>155</v>
-      </c>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A136" s="39"/>
+      <c r="B136" s="41"/>
+      <c r="C136" s="45"/>
       <c r="D136" s="17" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E136" s="16" t="s">
         <v>168</v>
       </c>
       <c r="F136" s="16"/>
-      <c r="G136" s="19"/>
-    </row>
-    <row r="137" spans="1:8">
-      <c r="A137" s="34"/>
-      <c r="B137" s="37"/>
-      <c r="C137" s="39" t="s">
-        <v>166</v>
-      </c>
+      <c r="G136" s="19" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A137" s="39"/>
+      <c r="B137" s="41"/>
+      <c r="C137" s="46"/>
       <c r="D137" s="17" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E137" s="16" t="s">
         <v>168</v>
       </c>
       <c r="F137" s="16"/>
       <c r="G137" s="19" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8">
-      <c r="A138" s="34"/>
-      <c r="B138" s="37"/>
-      <c r="C138" s="41"/>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A138" s="39"/>
+      <c r="B138" s="41"/>
+      <c r="C138" s="28" t="s">
+        <v>154</v>
+      </c>
       <c r="D138" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="E138" s="16"/>
+        <v>155</v>
+      </c>
+      <c r="E138" s="16" t="s">
+        <v>167</v>
+      </c>
       <c r="F138" s="16"/>
-      <c r="G138" s="19" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8">
-      <c r="A139" s="34"/>
-      <c r="B139" s="37"/>
-      <c r="C139" s="39" t="s">
+      <c r="G138" s="19"/>
+    </row>
+    <row r="139" spans="1:8" ht="102" x14ac:dyDescent="0.45">
+      <c r="A139" s="39"/>
+      <c r="B139" s="41"/>
+      <c r="C139" s="44" t="s">
+        <v>165</v>
+      </c>
+      <c r="D139" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="E139" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="D139" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="E139" s="16"/>
       <c r="F139" s="16"/>
-      <c r="G139" s="19"/>
-    </row>
-    <row r="140" spans="1:8">
-      <c r="A140" s="34"/>
-      <c r="B140" s="37"/>
-      <c r="C140" s="40"/>
+      <c r="G139" s="17" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="51" x14ac:dyDescent="0.45">
+      <c r="A140" s="39"/>
+      <c r="B140" s="41"/>
+      <c r="C140" s="45"/>
       <c r="D140" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="E140" s="16"/>
+        <v>201</v>
+      </c>
+      <c r="E140" s="16" t="s">
+        <v>132</v>
+      </c>
       <c r="F140" s="16"/>
-      <c r="G140" s="19"/>
-    </row>
-    <row r="141" spans="1:8">
-      <c r="A141" s="34"/>
-      <c r="B141" s="37"/>
-      <c r="C141" s="40"/>
+      <c r="G140" s="17" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A141" s="39"/>
+      <c r="B141" s="41"/>
+      <c r="C141" s="45"/>
       <c r="D141" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="E141" s="16"/>
+        <v>198</v>
+      </c>
+      <c r="E141" s="16" t="s">
+        <v>131</v>
+      </c>
       <c r="F141" s="16"/>
-      <c r="G141" s="19"/>
-    </row>
-    <row r="142" spans="1:8">
-      <c r="A142" s="34"/>
-      <c r="B142" s="37"/>
-      <c r="C142" s="41"/>
-      <c r="D142" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="E142" s="16"/>
+      <c r="G141" s="19" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A142" s="39"/>
+      <c r="B142" s="41"/>
+      <c r="C142" s="45"/>
+      <c r="D142" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="E142" s="16" t="s">
+        <v>131</v>
+      </c>
       <c r="F142" s="16"/>
-      <c r="G142" s="19"/>
-    </row>
-    <row r="143" spans="1:8">
-      <c r="A143" s="34"/>
-      <c r="B143" s="37"/>
-      <c r="C143" s="28" t="s">
-        <v>153</v>
-      </c>
-      <c r="D143" s="19"/>
+      <c r="G142" s="19" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A143" s="39"/>
+      <c r="B143" s="41"/>
+      <c r="C143" s="46"/>
+      <c r="D143" s="17" t="s">
+        <v>194</v>
+      </c>
       <c r="E143" s="16"/>
       <c r="F143" s="16"/>
-      <c r="G143" s="19"/>
-    </row>
-    <row r="144" spans="1:8">
-      <c r="A144" s="34"/>
-      <c r="B144" s="38"/>
-      <c r="C144" s="28"/>
-      <c r="D144" s="19"/>
+      <c r="G143" s="19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A144" s="39"/>
+      <c r="B144" s="41"/>
+      <c r="C144" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="D144" s="17" t="s">
+        <v>157</v>
+      </c>
       <c r="E144" s="16"/>
       <c r="F144" s="16"/>
       <c r="G144" s="19"/>
     </row>
-    <row r="145" spans="1:9">
-      <c r="A145" s="34"/>
-      <c r="B145" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="C145" s="28"/>
-      <c r="D145" s="19"/>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A145" s="39"/>
+      <c r="B145" s="41"/>
+      <c r="C145" s="45"/>
+      <c r="D145" s="17" t="s">
+        <v>160</v>
+      </c>
       <c r="E145" s="16"/>
       <c r="F145" s="16"/>
       <c r="G145" s="19"/>
     </row>
-    <row r="146" spans="1:9">
-      <c r="A146" s="34"/>
-      <c r="B146" s="37"/>
-      <c r="C146" s="28"/>
-      <c r="D146" s="19"/>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A146" s="39"/>
+      <c r="B146" s="41"/>
+      <c r="C146" s="45"/>
+      <c r="D146" s="17" t="s">
+        <v>159</v>
+      </c>
       <c r="E146" s="16"/>
       <c r="F146" s="16"/>
       <c r="G146" s="19"/>
     </row>
-    <row r="147" spans="1:9">
-      <c r="A147" s="34"/>
-      <c r="B147" s="38"/>
-      <c r="C147" s="28"/>
-      <c r="D147" s="19"/>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A147" s="39"/>
+      <c r="B147" s="41"/>
+      <c r="C147" s="46"/>
+      <c r="D147" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="E147" s="16"/>
       <c r="F147" s="16"/>
       <c r="G147" s="19"/>
     </row>
-    <row r="148" spans="1:9">
-      <c r="A148" s="34"/>
-      <c r="B148" s="29" t="s">
-        <v>176</v>
-      </c>
-      <c r="C148" s="28"/>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A148" s="39"/>
+      <c r="B148" s="41"/>
+      <c r="C148" s="28" t="s">
+        <v>152</v>
+      </c>
       <c r="D148" s="19"/>
       <c r="E148" s="16"/>
       <c r="F148" s="16"/>
       <c r="G148" s="19"/>
     </row>
-    <row r="149" spans="1:9">
-      <c r="A149" s="34"/>
-      <c r="B149" s="36" t="s">
-        <v>177</v>
-      </c>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A149" s="39"/>
+      <c r="B149" s="42"/>
       <c r="C149" s="28"/>
       <c r="D149" s="19"/>
       <c r="E149" s="16"/>
       <c r="F149" s="16"/>
       <c r="G149" s="19"/>
     </row>
-    <row r="150" spans="1:9">
-      <c r="A150" s="34"/>
-      <c r="B150" s="37"/>
-      <c r="C150" s="28" t="s">
-        <v>152</v>
-      </c>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A150" s="39"/>
+      <c r="B150" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="C150" s="28"/>
       <c r="D150" s="19"/>
       <c r="E150" s="16"/>
       <c r="F150" s="16"/>
       <c r="G150" s="19"/>
     </row>
-    <row r="151" spans="1:9">
-      <c r="A151" s="34"/>
-      <c r="B151" s="37"/>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A151" s="39"/>
+      <c r="B151" s="41"/>
       <c r="C151" s="28"/>
       <c r="D151" s="19"/>
       <c r="E151" s="16"/>
       <c r="F151" s="16"/>
       <c r="G151" s="19"/>
     </row>
-    <row r="152" spans="1:9">
-      <c r="A152" s="34"/>
-      <c r="B152" s="37"/>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A152" s="39"/>
+      <c r="B152" s="42"/>
       <c r="C152" s="28"/>
       <c r="D152" s="19"/>
       <c r="E152" s="16"/>
       <c r="F152" s="16"/>
       <c r="G152" s="19"/>
     </row>
-    <row r="153" spans="1:9">
-      <c r="A153" s="35"/>
-      <c r="B153" s="38"/>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A153" s="39"/>
+      <c r="B153" s="29" t="s">
+        <v>171</v>
+      </c>
       <c r="C153" s="28"/>
       <c r="D153" s="19"/>
       <c r="E153" s="16"/>
       <c r="F153" s="16"/>
       <c r="G153" s="19"/>
     </row>
-    <row r="154" spans="1:9">
-      <c r="B154" t="s">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A154" s="39"/>
+      <c r="B154" s="43" t="s">
+        <v>172</v>
+      </c>
+      <c r="C154" s="28"/>
+      <c r="D154" s="19"/>
+      <c r="E154" s="16"/>
+      <c r="F154" s="16"/>
+      <c r="G154" s="19"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A155" s="39"/>
+      <c r="B155" s="41"/>
+      <c r="C155" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="D155" s="19"/>
+      <c r="E155" s="16"/>
+      <c r="F155" s="16"/>
+      <c r="G155" s="19"/>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A156" s="39"/>
+      <c r="B156" s="41"/>
+      <c r="C156" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="D156" s="19"/>
+      <c r="E156" s="16"/>
+      <c r="F156" s="16"/>
+      <c r="G156" s="19" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A157" s="39"/>
+      <c r="B157" s="41"/>
+      <c r="C157" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="D157" s="19"/>
+      <c r="E157" s="16"/>
+      <c r="F157" s="16"/>
+      <c r="G157" s="19"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A158" s="39"/>
+      <c r="B158" s="41"/>
+      <c r="C158" s="28"/>
+      <c r="D158" s="19"/>
+      <c r="E158" s="16"/>
+      <c r="F158" s="16"/>
+      <c r="G158" s="19"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A159" s="39"/>
+      <c r="B159" s="41"/>
+      <c r="C159" s="28"/>
+      <c r="D159" s="19"/>
+      <c r="E159" s="16"/>
+      <c r="F159" s="16"/>
+      <c r="G159" s="19"/>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A160" s="39"/>
+      <c r="B160" s="41"/>
+      <c r="C160" s="28"/>
+      <c r="D160" s="19"/>
+      <c r="E160" s="16"/>
+      <c r="F160" s="16"/>
+      <c r="G160" s="19"/>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A161" s="40"/>
+      <c r="B161" s="42"/>
+      <c r="C161" s="28"/>
+      <c r="D161" s="19"/>
+      <c r="E161" s="16"/>
+      <c r="F161" s="16"/>
+      <c r="G161" s="19"/>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="B162" t="s">
         <v>144</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C162" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="155" spans="1:9">
-      <c r="I155" s="7"/>
-    </row>
-    <row r="156" spans="1:9">
-      <c r="I156" s="8"/>
-    </row>
-    <row r="157" spans="1:9">
-      <c r="I157" s="8"/>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="I163" s="7"/>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="C164" t="s">
+        <v>193</v>
+      </c>
+      <c r="I164" s="8"/>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="I165" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:G119" xr:uid="{34DC90E1-7112-4806-ADC5-98CA8498E977}"/>
   <mergeCells count="58">
+    <mergeCell ref="C9:C10"/>
     <mergeCell ref="C16:C18"/>
     <mergeCell ref="C21:C24"/>
     <mergeCell ref="C25:C28"/>
-    <mergeCell ref="B145:B147"/>
+    <mergeCell ref="B150:B152"/>
     <mergeCell ref="C92:C93"/>
     <mergeCell ref="C94:C95"/>
     <mergeCell ref="C96:C100"/>
-    <mergeCell ref="A119:A131"/>
-    <mergeCell ref="B122:B131"/>
-    <mergeCell ref="B119:B121"/>
-    <mergeCell ref="B111:B114"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="C113:C114"/>
-    <mergeCell ref="A5:A118"/>
-    <mergeCell ref="B5:B12"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B13:B28"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="B101:B110"/>
-    <mergeCell ref="C101:C103"/>
-    <mergeCell ref="C104:C107"/>
     <mergeCell ref="C108:C109"/>
     <mergeCell ref="B69:B82"/>
     <mergeCell ref="C69:C71"/>
@@ -4952,12 +5138,21 @@
     <mergeCell ref="C81:C82"/>
     <mergeCell ref="B83:B86"/>
     <mergeCell ref="C83:C84"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="B87:B100"/>
-    <mergeCell ref="C87:C89"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="A119:A133"/>
+    <mergeCell ref="B122:B133"/>
+    <mergeCell ref="B119:B121"/>
+    <mergeCell ref="B111:B114"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="C113:C114"/>
+    <mergeCell ref="A5:A118"/>
+    <mergeCell ref="B5:B12"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B13:B28"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="B101:B110"/>
+    <mergeCell ref="C101:C103"/>
+    <mergeCell ref="C104:C107"/>
     <mergeCell ref="B61:B68"/>
     <mergeCell ref="C61:C62"/>
     <mergeCell ref="C63:C68"/>
@@ -4972,12 +5167,18 @@
     <mergeCell ref="C49:C50"/>
     <mergeCell ref="C51:C53"/>
     <mergeCell ref="C54:C56"/>
-    <mergeCell ref="A132:A153"/>
-    <mergeCell ref="B132:B144"/>
-    <mergeCell ref="B149:B153"/>
-    <mergeCell ref="C139:C142"/>
-    <mergeCell ref="C132:C135"/>
-    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="A134:A161"/>
+    <mergeCell ref="B134:B149"/>
+    <mergeCell ref="B154:B161"/>
+    <mergeCell ref="C144:C147"/>
+    <mergeCell ref="C134:C137"/>
+    <mergeCell ref="C139:C143"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="B87:B100"/>
+    <mergeCell ref="C87:C89"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="C59:C60"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/금융감독원 홈페이지_UIUX_퍼블_컴포넌트리스트 .xlsx
+++ b/doc/금융감독원 홈페이지_UIUX_퍼블_컴포넌트리스트 .xlsx
@@ -8,16 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\03.Publishing\fss\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93260AC-0D20-45ED-99CC-47945DC6DC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3388EF8B-1D84-44CF-8529-6044779B968A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-5100" windowWidth="29040" windowHeight="15720" tabRatio="499" activeTab="1" xr2:uid="{BA3ED54C-CC85-4CD0-8ADB-46ECF631616A}"/>
+    <workbookView xWindow="46260" yWindow="-4680" windowWidth="20115" windowHeight="15105" tabRatio="499" activeTab="3" xr2:uid="{BA3ED54C-CC85-4CD0-8ADB-46ECF631616A}"/>
   </bookViews>
   <sheets>
     <sheet name="체크리스트_목록" sheetId="1" r:id="rId1"/>
     <sheet name="ia guide" sheetId="2" r:id="rId2"/>
+    <sheet name="design guide" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ia guide'!$A$4:$G$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'design guide'!$A$4:$G$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ia guide'!$A$4:$G$116</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">체크리스트_목록!$A$4:$F$164</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -30,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="214">
   <si>
     <t>대분류</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -830,6 +833,46 @@
 font.css
 common.css
 content.css</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02.20.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Identifier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Masthead</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Disabled</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pressed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hover</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>.krds-btn.link.basic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>.krds-btn.link</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>color: var(--krds-button--color-link-text)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3183,7 +3226,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:I165"/>
+  <dimension ref="A1:I162"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="21.25" customWidth="1"/>
@@ -3258,103 +3301,119 @@
       <c r="C6" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="D6" s="15"/>
+      <c r="D6" s="15" t="s">
+        <v>206</v>
+      </c>
       <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
+      <c r="F6" s="16" t="s">
+        <v>204</v>
+      </c>
       <c r="G6" s="19"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="39"/>
       <c r="B7" s="36"/>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="13" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>90</v>
+        <v>205</v>
       </c>
       <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
+      <c r="F7" s="16" t="s">
+        <v>204</v>
+      </c>
       <c r="G7" s="19"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" ht="34" x14ac:dyDescent="0.45">
       <c r="A8" s="39"/>
       <c r="B8" s="36"/>
-      <c r="C8" s="37"/>
+      <c r="C8" s="35" t="s">
+        <v>191</v>
+      </c>
       <c r="D8" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="19"/>
-    </row>
-    <row r="9" spans="1:8" ht="34" x14ac:dyDescent="0.45">
+        <v>88</v>
+      </c>
+      <c r="E8" s="24"/>
+      <c r="F8" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="39"/>
       <c r="B9" s="36"/>
-      <c r="C9" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="17" t="s">
-        <v>139</v>
-      </c>
+      <c r="C9" s="36"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="19"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="39"/>
       <c r="B10" s="36"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
+      <c r="C10" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
       <c r="G10" s="19"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="39"/>
       <c r="B11" s="36"/>
-      <c r="C11" s="35" t="s">
-        <v>192</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
       <c r="G11" s="19"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="39"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="B12" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" s="25"/>
+      <c r="F12" s="16" t="s">
+        <v>204</v>
+      </c>
       <c r="G12" s="19"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="39"/>
-      <c r="B13" s="35" t="s">
-        <v>6</v>
-      </c>
+      <c r="B13" s="36"/>
       <c r="C13" s="35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
+      <c r="F13" s="16" t="s">
+        <v>204</v>
+      </c>
       <c r="G13" s="19"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="39"/>
       <c r="B14" s="36"/>
       <c r="C14" s="36"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="D14" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
       <c r="G14" s="19"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
@@ -3369,141 +3428,145 @@
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="39"/>
       <c r="B16" s="36"/>
-      <c r="C16" s="35" t="s">
-        <v>11</v>
+      <c r="C16" s="13" t="s">
+        <v>12</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
+      <c r="F16" s="16" t="s">
+        <v>204</v>
+      </c>
       <c r="G16" s="19"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="39"/>
       <c r="B17" s="36"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
+      <c r="C17" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="23"/>
+      <c r="F17" s="16" t="s">
+        <v>204</v>
+      </c>
       <c r="G17" s="19"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="39"/>
       <c r="B18" s="36"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
+      <c r="C18" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
       <c r="G18" s="19"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="39"/>
       <c r="B19" s="36"/>
-      <c r="C19" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
       <c r="G19" s="19"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="39"/>
       <c r="B20" s="36"/>
-      <c r="C20" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="F20" s="23"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
       <c r="G20" s="19"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="39"/>
       <c r="B21" s="36"/>
-      <c r="C21" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
       <c r="G21" s="19"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="39"/>
       <c r="B22" s="36"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
+      <c r="C22" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="F22" s="16"/>
       <c r="G22" s="19"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="39"/>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
+      <c r="D23" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
       <c r="G23" s="19"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="39"/>
       <c r="B24" s="36"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
       <c r="G24" s="19"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="39"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="E25" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="F25" s="16"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
       <c r="G25" s="19"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="39"/>
-      <c r="B26" s="36"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
+      <c r="B26" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
       <c r="G26" s="19"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="39"/>
       <c r="B27" s="36"/>
       <c r="C27" s="36"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
+      <c r="D27" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
       <c r="G27" s="19"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="39"/>
-      <c r="B28" s="37"/>
-      <c r="C28" s="37"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
       <c r="D28" s="21"/>
       <c r="E28" s="21"/>
       <c r="F28" s="21"/>
@@ -3511,14 +3574,12 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="39"/>
-      <c r="B29" s="35" t="s">
-        <v>16</v>
-      </c>
+      <c r="B29" s="36"/>
       <c r="C29" s="35" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="E29" s="26"/>
       <c r="F29" s="26"/>
@@ -3528,17 +3589,15 @@
       <c r="A30" s="39"/>
       <c r="B30" s="36"/>
       <c r="C30" s="36"/>
-      <c r="D30" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
       <c r="G30" s="19"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="39"/>
       <c r="B31" s="36"/>
-      <c r="C31" s="36"/>
+      <c r="C31" s="37"/>
       <c r="D31" s="21"/>
       <c r="E31" s="21"/>
       <c r="F31" s="21"/>
@@ -3548,13 +3607,11 @@
       <c r="A32" s="39"/>
       <c r="B32" s="36"/>
       <c r="C32" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
+        <v>26</v>
+      </c>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
       <c r="G32" s="19"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
@@ -3569,7 +3626,7 @@
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="39"/>
       <c r="B34" s="36"/>
-      <c r="C34" s="37"/>
+      <c r="C34" s="36"/>
       <c r="D34" s="21"/>
       <c r="E34" s="21"/>
       <c r="F34" s="21"/>
@@ -3578,9 +3635,7 @@
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="39"/>
       <c r="B35" s="36"/>
-      <c r="C35" s="35" t="s">
-        <v>26</v>
-      </c>
+      <c r="C35" s="37"/>
       <c r="D35" s="21"/>
       <c r="E35" s="21"/>
       <c r="F35" s="21"/>
@@ -3589,16 +3644,20 @@
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" s="39"/>
       <c r="B36" s="36"/>
-      <c r="C36" s="36"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
+      <c r="C36" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
       <c r="G36" s="19"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" s="39"/>
       <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
+      <c r="C37" s="37"/>
       <c r="D37" s="21"/>
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
@@ -3607,20 +3666,22 @@
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" s="39"/>
       <c r="B38" s="36"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
+      <c r="C38" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
       <c r="G38" s="19"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" s="39"/>
       <c r="B39" s="36"/>
-      <c r="C39" s="35" t="s">
-        <v>27</v>
-      </c>
+      <c r="C39" s="36"/>
       <c r="D39" s="21" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="E39" s="26"/>
       <c r="F39" s="26"/>
@@ -3629,20 +3690,22 @@
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" s="39"/>
       <c r="B40" s="36"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
+      <c r="C40" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
       <c r="G40" s="19"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" s="39"/>
       <c r="B41" s="36"/>
-      <c r="C41" s="35" t="s">
-        <v>28</v>
-      </c>
+      <c r="C41" s="36"/>
       <c r="D41" s="21" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="E41" s="26"/>
       <c r="F41" s="26"/>
@@ -3651,9 +3714,9 @@
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" s="39"/>
       <c r="B42" s="36"/>
-      <c r="C42" s="36"/>
+      <c r="C42" s="37"/>
       <c r="D42" s="21" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="E42" s="26"/>
       <c r="F42" s="26"/>
@@ -3663,10 +3726,10 @@
       <c r="A43" s="39"/>
       <c r="B43" s="36"/>
       <c r="C43" s="35" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E43" s="26"/>
       <c r="F43" s="26"/>
@@ -3677,7 +3740,7 @@
       <c r="B44" s="36"/>
       <c r="C44" s="36"/>
       <c r="D44" s="21" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="E44" s="26"/>
       <c r="F44" s="26"/>
@@ -3687,55 +3750,53 @@
       <c r="A45" s="39"/>
       <c r="B45" s="36"/>
       <c r="C45" s="37"/>
-      <c r="D45" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E45" s="26"/>
-      <c r="F45" s="26"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
       <c r="G45" s="19"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" s="39"/>
       <c r="B46" s="36"/>
       <c r="C46" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="D46" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
+        <v>31</v>
+      </c>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
       <c r="G46" s="19"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" s="39"/>
       <c r="B47" s="36"/>
       <c r="C47" s="36"/>
-      <c r="D47" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="E47" s="26"/>
-      <c r="F47" s="26"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21"/>
       <c r="G47" s="19"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" s="39"/>
       <c r="B48" s="36"/>
-      <c r="C48" s="37"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="21"/>
+      <c r="C48" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
       <c r="G48" s="19"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" s="39"/>
       <c r="B49" s="36"/>
-      <c r="C49" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="21"/>
+      <c r="C49" s="36"/>
+      <c r="D49" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
       <c r="G49" s="19"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
@@ -3751,10 +3812,10 @@
       <c r="A51" s="39"/>
       <c r="B51" s="36"/>
       <c r="C51" s="35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="E51" s="26"/>
       <c r="F51" s="26"/>
@@ -3764,11 +3825,9 @@
       <c r="A52" s="39"/>
       <c r="B52" s="36"/>
       <c r="C52" s="36"/>
-      <c r="D52" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="E52" s="26"/>
-      <c r="F52" s="26"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="21"/>
       <c r="G52" s="19"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
@@ -3784,10 +3843,10 @@
       <c r="A54" s="39"/>
       <c r="B54" s="36"/>
       <c r="C54" s="35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E54" s="26"/>
       <c r="F54" s="26"/>
@@ -3796,7 +3855,7 @@
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" s="39"/>
       <c r="B55" s="36"/>
-      <c r="C55" s="36"/>
+      <c r="C55" s="37"/>
       <c r="D55" s="21"/>
       <c r="E55" s="21"/>
       <c r="F55" s="21"/>
@@ -3805,20 +3864,22 @@
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" s="39"/>
       <c r="B56" s="36"/>
-      <c r="C56" s="36"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="21"/>
+      <c r="C56" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="D56" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
       <c r="G56" s="19"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" s="39"/>
-      <c r="B57" s="36"/>
-      <c r="C57" s="35" t="s">
-        <v>34</v>
-      </c>
+      <c r="B57" s="37"/>
+      <c r="C57" s="36"/>
       <c r="D57" s="21" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E57" s="26"/>
       <c r="F57" s="26"/>
@@ -3826,47 +3887,51 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" s="39"/>
-      <c r="B58" s="36"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
+      <c r="B58" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C58" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E58" s="23"/>
+      <c r="F58" s="16" t="s">
+        <v>135</v>
+      </c>
       <c r="G58" s="19"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" s="39"/>
       <c r="B59" s="36"/>
-      <c r="C59" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="D59" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="E59" s="26"/>
-      <c r="F59" s="26"/>
+      <c r="C59" s="36"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="16"/>
       <c r="G59" s="19"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" s="39"/>
-      <c r="B60" s="37"/>
-      <c r="C60" s="36"/>
-      <c r="D60" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="E60" s="26"/>
-      <c r="F60" s="26"/>
+      <c r="B60" s="36"/>
+      <c r="C60" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E60" s="23"/>
+      <c r="F60" s="16" t="s">
+        <v>135</v>
+      </c>
       <c r="G60" s="19"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" s="39"/>
-      <c r="B61" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="C61" s="35" t="s">
-        <v>36</v>
-      </c>
+      <c r="B61" s="36"/>
+      <c r="C61" s="36"/>
       <c r="D61" s="15" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="E61" s="23"/>
       <c r="F61" s="16" t="s">
@@ -3878,19 +3943,21 @@
       <c r="A62" s="39"/>
       <c r="B62" s="36"/>
       <c r="C62" s="36"/>
-      <c r="D62" s="15"/>
-      <c r="E62" s="15"/>
-      <c r="F62" s="16"/>
+      <c r="D62" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E62" s="23"/>
+      <c r="F62" s="16" t="s">
+        <v>135</v>
+      </c>
       <c r="G62" s="19"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" s="39"/>
       <c r="B63" s="36"/>
-      <c r="C63" s="35" t="s">
-        <v>37</v>
-      </c>
+      <c r="C63" s="36"/>
       <c r="D63" s="15" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E63" s="23"/>
       <c r="F63" s="16" t="s">
@@ -3903,7 +3970,7 @@
       <c r="B64" s="36"/>
       <c r="C64" s="36"/>
       <c r="D64" s="15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E64" s="23"/>
       <c r="F64" s="16" t="s">
@@ -3916,7 +3983,7 @@
       <c r="B65" s="36"/>
       <c r="C65" s="36"/>
       <c r="D65" s="15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E65" s="23"/>
       <c r="F65" s="16" t="s">
@@ -3926,10 +3993,14 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A66" s="39"/>
-      <c r="B66" s="36"/>
-      <c r="C66" s="36"/>
+      <c r="B66" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="D66" s="15" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E66" s="23"/>
       <c r="F66" s="16" t="s">
@@ -3942,7 +4013,7 @@
       <c r="B67" s="36"/>
       <c r="C67" s="36"/>
       <c r="D67" s="15" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E67" s="23"/>
       <c r="F67" s="16" t="s">
@@ -3955,7 +4026,7 @@
       <c r="B68" s="36"/>
       <c r="C68" s="36"/>
       <c r="D68" s="15" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="E68" s="23"/>
       <c r="F68" s="16" t="s">
@@ -3965,14 +4036,12 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A69" s="39"/>
-      <c r="B69" s="35" t="s">
-        <v>18</v>
-      </c>
+      <c r="B69" s="36"/>
       <c r="C69" s="35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="E69" s="23"/>
       <c r="F69" s="16" t="s">
@@ -3985,7 +4054,7 @@
       <c r="B70" s="36"/>
       <c r="C70" s="36"/>
       <c r="D70" s="15" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="E70" s="23"/>
       <c r="F70" s="16" t="s">
@@ -3998,7 +4067,7 @@
       <c r="B71" s="36"/>
       <c r="C71" s="36"/>
       <c r="D71" s="15" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="E71" s="23"/>
       <c r="F71" s="16" t="s">
@@ -4006,55 +4075,53 @@
       </c>
       <c r="G71" s="19"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="39"/>
       <c r="B72" s="36"/>
       <c r="C72" s="35" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E72" s="23"/>
       <c r="F72" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G72" s="19"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="39"/>
       <c r="B73" s="36"/>
       <c r="C73" s="36"/>
       <c r="D73" s="15" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="E73" s="23"/>
       <c r="F73" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G73" s="19"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="39"/>
       <c r="B74" s="36"/>
       <c r="C74" s="36"/>
       <c r="D74" s="15" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="E74" s="23"/>
       <c r="F74" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G74" s="19"/>
     </row>
     <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="39"/>
       <c r="B75" s="36"/>
-      <c r="C75" s="35" t="s">
-        <v>40</v>
-      </c>
+      <c r="C75" s="36"/>
       <c r="D75" s="15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E75" s="23"/>
       <c r="F75" s="16" t="s">
@@ -4065,9 +4132,11 @@
     <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="39"/>
       <c r="B76" s="36"/>
-      <c r="C76" s="36"/>
+      <c r="C76" s="35" t="s">
+        <v>41</v>
+      </c>
       <c r="D76" s="15" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="E76" s="23"/>
       <c r="F76" s="16" t="s">
@@ -4080,7 +4149,7 @@
       <c r="B77" s="36"/>
       <c r="C77" s="36"/>
       <c r="D77" s="15" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E77" s="23"/>
       <c r="F77" s="16" t="s">
@@ -4091,9 +4160,11 @@
     <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="39"/>
       <c r="B78" s="36"/>
-      <c r="C78" s="36"/>
+      <c r="C78" s="35" t="s">
+        <v>42</v>
+      </c>
       <c r="D78" s="15" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="E78" s="23"/>
       <c r="F78" s="16" t="s">
@@ -4104,11 +4175,9 @@
     <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="39"/>
       <c r="B79" s="36"/>
-      <c r="C79" s="35" t="s">
-        <v>41</v>
-      </c>
+      <c r="C79" s="36"/>
       <c r="D79" s="15" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E79" s="23"/>
       <c r="F79" s="16" t="s">
@@ -4116,87 +4185,79 @@
       </c>
       <c r="G79" s="19"/>
     </row>
-    <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="39"/>
-      <c r="B80" s="36"/>
-      <c r="C80" s="36"/>
-      <c r="D80" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E80" s="23"/>
-      <c r="F80" s="16" t="s">
-        <v>136</v>
-      </c>
+      <c r="B80" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="C80" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="D80" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
       <c r="G80" s="19"/>
     </row>
     <row r="81" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="39"/>
       <c r="B81" s="36"/>
-      <c r="C81" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="D81" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="E81" s="23"/>
-      <c r="F81" s="16" t="s">
-        <v>136</v>
-      </c>
+      <c r="C81" s="37"/>
+      <c r="D81" s="15"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="15"/>
       <c r="G81" s="19"/>
     </row>
     <row r="82" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="39"/>
       <c r="B82" s="36"/>
-      <c r="C82" s="36"/>
+      <c r="C82" s="35" t="s">
+        <v>44</v>
+      </c>
       <c r="D82" s="15" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="E82" s="23"/>
-      <c r="F82" s="16" t="s">
-        <v>136</v>
-      </c>
+      <c r="F82" s="23"/>
       <c r="G82" s="19"/>
     </row>
-    <row r="83" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="39"/>
-      <c r="B83" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="C83" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="D83" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="E83" s="26"/>
-      <c r="F83" s="26"/>
+      <c r="B83" s="37"/>
+      <c r="C83" s="37"/>
+      <c r="D83" s="15"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="15"/>
       <c r="G83" s="19"/>
     </row>
     <row r="84" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="39"/>
-      <c r="B84" s="36"/>
-      <c r="C84" s="37"/>
-      <c r="D84" s="15"/>
-      <c r="E84" s="15"/>
-      <c r="F84" s="15"/>
+      <c r="B84" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C84" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="D84" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="E84" s="23"/>
+      <c r="F84" s="23"/>
       <c r="G84" s="19"/>
     </row>
     <row r="85" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="39"/>
       <c r="B85" s="36"/>
-      <c r="C85" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="D85" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E85" s="23"/>
-      <c r="F85" s="23"/>
+      <c r="C85" s="36"/>
+      <c r="D85" s="15"/>
+      <c r="E85" s="15"/>
+      <c r="F85" s="15"/>
       <c r="G85" s="19"/>
     </row>
     <row r="86" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="39"/>
-      <c r="B86" s="37"/>
+      <c r="B86" s="36"/>
       <c r="C86" s="37"/>
       <c r="D86" s="15"/>
       <c r="E86" s="15"/>
@@ -4205,14 +4266,12 @@
     </row>
     <row r="87" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="39"/>
-      <c r="B87" s="35" t="s">
-        <v>20</v>
-      </c>
+      <c r="B87" s="36"/>
       <c r="C87" s="35" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="E87" s="23"/>
       <c r="F87" s="23"/>
@@ -4230,64 +4289,66 @@
     <row r="89" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="39"/>
       <c r="B89" s="36"/>
-      <c r="C89" s="37"/>
-      <c r="D89" s="15"/>
-      <c r="E89" s="15"/>
-      <c r="F89" s="15"/>
+      <c r="C89" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="D89" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E89" s="23"/>
+      <c r="F89" s="23"/>
       <c r="G89" s="19"/>
     </row>
     <row r="90" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="39"/>
       <c r="B90" s="36"/>
-      <c r="C90" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="D90" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="E90" s="23"/>
-      <c r="F90" s="23"/>
+      <c r="C90" s="36"/>
+      <c r="D90" s="15"/>
+      <c r="E90" s="15"/>
+      <c r="F90" s="15"/>
       <c r="G90" s="19"/>
     </row>
     <row r="91" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="39"/>
       <c r="B91" s="36"/>
-      <c r="C91" s="36"/>
-      <c r="D91" s="15"/>
-      <c r="E91" s="15"/>
-      <c r="F91" s="15"/>
+      <c r="C91" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="D91" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E91" s="23"/>
+      <c r="F91" s="23"/>
       <c r="G91" s="19"/>
     </row>
     <row r="92" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="39"/>
       <c r="B92" s="36"/>
-      <c r="C92" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="D92" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="E92" s="23"/>
-      <c r="F92" s="23"/>
+      <c r="C92" s="36"/>
+      <c r="D92" s="15"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="15"/>
       <c r="G92" s="19"/>
     </row>
     <row r="93" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="39"/>
       <c r="B93" s="36"/>
-      <c r="C93" s="36"/>
-      <c r="D93" s="15"/>
-      <c r="E93" s="15"/>
-      <c r="F93" s="15"/>
+      <c r="C93" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="D93" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E93" s="23"/>
+      <c r="F93" s="23"/>
       <c r="G93" s="19"/>
     </row>
     <row r="94" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="39"/>
       <c r="B94" s="36"/>
-      <c r="C94" s="35" t="s">
-        <v>48</v>
-      </c>
+      <c r="C94" s="36"/>
       <c r="D94" s="15" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="E94" s="23"/>
       <c r="F94" s="23"/>
@@ -4297,74 +4358,76 @@
       <c r="A95" s="39"/>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
-      <c r="D95" s="15"/>
-      <c r="E95" s="15"/>
-      <c r="F95" s="15"/>
+      <c r="D95" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E95" s="23"/>
+      <c r="F95" s="23"/>
       <c r="G95" s="19"/>
     </row>
     <row r="96" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="39"/>
       <c r="B96" s="36"/>
-      <c r="C96" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="D96" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="E96" s="23"/>
-      <c r="F96" s="23"/>
+      <c r="C96" s="36"/>
+      <c r="D96" s="15"/>
+      <c r="E96" s="15"/>
+      <c r="F96" s="15"/>
       <c r="G96" s="19"/>
     </row>
     <row r="97" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="39"/>
       <c r="B97" s="36"/>
       <c r="C97" s="36"/>
-      <c r="D97" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="E97" s="23"/>
-      <c r="F97" s="23"/>
+      <c r="D97" s="15"/>
+      <c r="E97" s="15"/>
+      <c r="F97" s="15"/>
       <c r="G97" s="19"/>
     </row>
-    <row r="98" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A98" s="39"/>
-      <c r="B98" s="36"/>
-      <c r="C98" s="36"/>
+      <c r="B98" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="C98" s="35" t="s">
+        <v>50</v>
+      </c>
       <c r="D98" s="15" t="s">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="E98" s="23"/>
       <c r="F98" s="23"/>
       <c r="G98" s="19"/>
     </row>
-    <row r="99" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A99" s="39"/>
       <c r="B99" s="36"/>
       <c r="C99" s="36"/>
-      <c r="D99" s="15"/>
-      <c r="E99" s="15"/>
-      <c r="F99" s="15"/>
+      <c r="D99" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E99" s="23"/>
+      <c r="F99" s="23"/>
       <c r="G99" s="19"/>
     </row>
-    <row r="100" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A100" s="39"/>
       <c r="B100" s="36"/>
       <c r="C100" s="36"/>
-      <c r="D100" s="15"/>
-      <c r="E100" s="15"/>
-      <c r="F100" s="15"/>
+      <c r="D100" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E100" s="23"/>
+      <c r="F100" s="23"/>
       <c r="G100" s="19"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A101" s="39"/>
-      <c r="B101" s="35" t="s">
-        <v>21</v>
-      </c>
+      <c r="B101" s="36"/>
       <c r="C101" s="35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D101" s="15" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="E101" s="23"/>
       <c r="F101" s="23"/>
@@ -4375,7 +4438,7 @@
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
       <c r="D102" s="15" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="E102" s="23"/>
       <c r="F102" s="23"/>
@@ -4386,7 +4449,7 @@
       <c r="B103" s="36"/>
       <c r="C103" s="36"/>
       <c r="D103" s="15" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="E103" s="23"/>
       <c r="F103" s="23"/>
@@ -4395,11 +4458,9 @@
     <row r="104" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A104" s="39"/>
       <c r="B104" s="36"/>
-      <c r="C104" s="35" t="s">
-        <v>51</v>
-      </c>
+      <c r="C104" s="36"/>
       <c r="D104" s="15" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E104" s="23"/>
       <c r="F104" s="23"/>
@@ -4408,9 +4469,11 @@
     <row r="105" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A105" s="39"/>
       <c r="B105" s="36"/>
-      <c r="C105" s="36"/>
+      <c r="C105" s="35" t="s">
+        <v>52</v>
+      </c>
       <c r="D105" s="15" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E105" s="23"/>
       <c r="F105" s="23"/>
@@ -4420,19 +4483,19 @@
       <c r="A106" s="39"/>
       <c r="B106" s="36"/>
       <c r="C106" s="36"/>
-      <c r="D106" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="E106" s="23"/>
-      <c r="F106" s="23"/>
+      <c r="D106" s="15"/>
+      <c r="E106" s="15"/>
+      <c r="F106" s="15"/>
       <c r="G106" s="19"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A107" s="39"/>
       <c r="B107" s="36"/>
-      <c r="C107" s="36"/>
+      <c r="C107" s="13" t="s">
+        <v>53</v>
+      </c>
       <c r="D107" s="15" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="E107" s="23"/>
       <c r="F107" s="23"/>
@@ -4440,12 +4503,14 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A108" s="39"/>
-      <c r="B108" s="36"/>
+      <c r="B108" s="35" t="s">
+        <v>22</v>
+      </c>
       <c r="C108" s="35" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D108" s="15" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="E108" s="23"/>
       <c r="F108" s="23"/>
@@ -4454,20 +4519,22 @@
     <row r="109" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A109" s="39"/>
       <c r="B109" s="36"/>
-      <c r="C109" s="36"/>
-      <c r="D109" s="15"/>
-      <c r="E109" s="15"/>
-      <c r="F109" s="15"/>
+      <c r="C109" s="37"/>
+      <c r="D109" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E109" s="23"/>
+      <c r="F109" s="23"/>
       <c r="G109" s="19"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A110" s="39"/>
       <c r="B110" s="36"/>
-      <c r="C110" s="13" t="s">
-        <v>53</v>
+      <c r="C110" s="35" t="s">
+        <v>55</v>
       </c>
       <c r="D110" s="15" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="E110" s="23"/>
       <c r="F110" s="23"/>
@@ -4475,499 +4542,489 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A111" s="39"/>
-      <c r="B111" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="C111" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="D111" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="E111" s="23"/>
-      <c r="F111" s="23"/>
+      <c r="B111" s="37"/>
+      <c r="C111" s="37"/>
+      <c r="D111" s="15"/>
+      <c r="E111" s="15"/>
+      <c r="F111" s="15"/>
       <c r="G111" s="19"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A112" s="39"/>
-      <c r="B112" s="36"/>
-      <c r="C112" s="37"/>
-      <c r="D112" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="E112" s="23"/>
-      <c r="F112" s="23"/>
+      <c r="B112" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C112" s="11"/>
+      <c r="D112" s="15"/>
+      <c r="E112" s="15"/>
+      <c r="F112" s="15"/>
       <c r="G112" s="19"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A113" s="39"/>
-      <c r="B113" s="36"/>
-      <c r="C113" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="D113" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E113" s="23"/>
-      <c r="F113" s="23"/>
+      <c r="B113" s="11"/>
+      <c r="C113" s="11"/>
+      <c r="D113" s="15"/>
+      <c r="E113" s="15"/>
+      <c r="F113" s="15"/>
       <c r="G113" s="19"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A114" s="39"/>
-      <c r="B114" s="37"/>
-      <c r="C114" s="37"/>
+      <c r="B114" s="11"/>
+      <c r="C114" s="11"/>
       <c r="D114" s="15"/>
       <c r="E114" s="15"/>
       <c r="F114" s="15"/>
       <c r="G114" s="19"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A115" s="39"/>
-      <c r="B115" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C115" s="11"/>
+      <c r="A115" s="40"/>
+      <c r="B115" s="12"/>
+      <c r="C115" s="12"/>
       <c r="D115" s="15"/>
       <c r="E115" s="15"/>
       <c r="F115" s="15"/>
       <c r="G115" s="19"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A116" s="39"/>
-      <c r="B116" s="11"/>
-      <c r="C116" s="11"/>
-      <c r="D116" s="15"/>
-      <c r="E116" s="15"/>
-      <c r="F116" s="15"/>
+      <c r="A116" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="B116" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="C116" s="28"/>
+      <c r="D116" s="19"/>
+      <c r="E116" s="19"/>
+      <c r="F116" s="19"/>
       <c r="G116" s="19"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117" s="39"/>
-      <c r="B117" s="11"/>
-      <c r="C117" s="11"/>
-      <c r="D117" s="15"/>
-      <c r="E117" s="15"/>
-      <c r="F117" s="15"/>
+      <c r="B117" s="41"/>
+      <c r="C117" s="28"/>
+      <c r="D117" s="19"/>
+      <c r="E117" s="19"/>
+      <c r="F117" s="19"/>
       <c r="G117" s="19"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A118" s="40"/>
-      <c r="B118" s="12"/>
-      <c r="C118" s="12"/>
-      <c r="D118" s="15"/>
-      <c r="E118" s="15"/>
-      <c r="F118" s="15"/>
+      <c r="A118" s="39"/>
+      <c r="B118" s="42"/>
+      <c r="C118" s="28"/>
+      <c r="D118" s="19"/>
+      <c r="E118" s="19"/>
+      <c r="F118" s="19"/>
       <c r="G118" s="19"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A119" s="38" t="s">
-        <v>140</v>
-      </c>
+      <c r="A119" s="39"/>
       <c r="B119" s="43" t="s">
-        <v>141</v>
-      </c>
-      <c r="C119" s="28"/>
+        <v>142</v>
+      </c>
+      <c r="C119" s="28" t="s">
+        <v>146</v>
+      </c>
       <c r="D119" s="19"/>
       <c r="E119" s="19"/>
       <c r="F119" s="19"/>
       <c r="G119" s="19"/>
+      <c r="H119" s="9" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" s="39"/>
       <c r="B120" s="41"/>
-      <c r="C120" s="28"/>
-      <c r="D120" s="19"/>
+      <c r="C120" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="D120" s="19" t="s">
+        <v>185</v>
+      </c>
       <c r="E120" s="19"/>
-      <c r="F120" s="19"/>
-      <c r="G120" s="19"/>
+      <c r="F120" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="G120" s="19" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" s="39"/>
-      <c r="B121" s="42"/>
+      <c r="B121" s="41"/>
       <c r="C121" s="28"/>
-      <c r="D121" s="19"/>
+      <c r="D121" s="19" t="s">
+        <v>186</v>
+      </c>
       <c r="E121" s="19"/>
-      <c r="F121" s="19"/>
-      <c r="G121" s="19"/>
+      <c r="F121" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="G121" s="19" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122" s="39"/>
-      <c r="B122" s="43" t="s">
-        <v>142</v>
-      </c>
-      <c r="C122" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="D122" s="19"/>
+      <c r="B122" s="41"/>
+      <c r="C122" s="28"/>
+      <c r="D122" s="19" t="s">
+        <v>187</v>
+      </c>
       <c r="E122" s="19"/>
-      <c r="F122" s="19"/>
-      <c r="G122" s="19"/>
-      <c r="H122" s="9" t="s">
-        <v>179</v>
+      <c r="F122" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="G122" s="19" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" s="39"/>
       <c r="B123" s="41"/>
       <c r="C123" s="28" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D123" s="19" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E123" s="19"/>
       <c r="F123" s="16" t="s">
         <v>190</v>
       </c>
       <c r="G123" s="19" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124" s="39"/>
       <c r="B124" s="41"/>
-      <c r="C124" s="28"/>
+      <c r="C124" s="28" t="s">
+        <v>148</v>
+      </c>
       <c r="D124" s="19" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="E124" s="19"/>
-      <c r="F124" s="16" t="s">
-        <v>190</v>
-      </c>
+      <c r="F124" s="19"/>
       <c r="G124" s="19" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125" s="39"/>
       <c r="B125" s="41"/>
-      <c r="C125" s="28"/>
+      <c r="C125" s="28" t="s">
+        <v>149</v>
+      </c>
       <c r="D125" s="19" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="E125" s="19"/>
       <c r="F125" s="16" t="s">
         <v>190</v>
       </c>
       <c r="G125" s="19" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A126" s="39"/>
       <c r="B126" s="41"/>
       <c r="C126" s="28" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="D126" s="19" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E126" s="19"/>
-      <c r="F126" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="G126" s="19" t="s">
-        <v>183</v>
-      </c>
+      <c r="F126" s="19"/>
+      <c r="G126" s="19"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A127" s="39"/>
       <c r="B127" s="41"/>
-      <c r="C127" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="D127" s="19" t="s">
-        <v>176</v>
-      </c>
+      <c r="C127" s="28"/>
+      <c r="D127" s="19"/>
       <c r="E127" s="19"/>
       <c r="F127" s="19"/>
-      <c r="G127" s="19" t="s">
-        <v>177</v>
-      </c>
+      <c r="G127" s="19"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A128" s="39"/>
       <c r="B128" s="41"/>
-      <c r="C128" s="28" t="s">
-        <v>149</v>
-      </c>
-      <c r="D128" s="19" t="s">
-        <v>174</v>
-      </c>
+      <c r="C128" s="28"/>
+      <c r="D128" s="19"/>
       <c r="E128" s="19"/>
-      <c r="F128" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="G128" s="19" t="s">
-        <v>177</v>
-      </c>
+      <c r="F128" s="19"/>
+      <c r="G128" s="19"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A129" s="39"/>
       <c r="B129" s="41"/>
-      <c r="C129" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="D129" s="19" t="s">
-        <v>175</v>
-      </c>
+      <c r="C129" s="28"/>
+      <c r="D129" s="19"/>
       <c r="E129" s="19"/>
       <c r="F129" s="19"/>
       <c r="G129" s="19"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A130" s="39"/>
-      <c r="B130" s="41"/>
-      <c r="C130" s="28"/>
-      <c r="D130" s="19"/>
-      <c r="E130" s="19"/>
-      <c r="F130" s="19"/>
-      <c r="G130" s="19"/>
+    <row r="130" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A130" s="47"/>
+      <c r="B130" s="48"/>
+      <c r="C130" s="31"/>
+      <c r="D130" s="32"/>
+      <c r="E130" s="33"/>
+      <c r="F130" s="33"/>
+      <c r="G130" s="32"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A131" s="39"/>
-      <c r="B131" s="41"/>
-      <c r="C131" s="28"/>
-      <c r="D131" s="19"/>
-      <c r="E131" s="19"/>
-      <c r="F131" s="19"/>
-      <c r="G131" s="19"/>
+      <c r="A131" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="B131" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="C131" s="45" t="s">
+        <v>153</v>
+      </c>
+      <c r="D131" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="E131" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="F131" s="14"/>
+      <c r="G131" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="H131" s="9" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A132" s="39"/>
       <c r="B132" s="41"/>
-      <c r="C132" s="28"/>
-      <c r="D132" s="19"/>
-      <c r="E132" s="19"/>
-      <c r="F132" s="19"/>
-      <c r="G132" s="19"/>
-    </row>
-    <row r="133" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A133" s="47"/>
-      <c r="B133" s="48"/>
-      <c r="C133" s="31"/>
-      <c r="D133" s="32"/>
-      <c r="E133" s="33"/>
-      <c r="F133" s="33"/>
-      <c r="G133" s="32"/>
+      <c r="C132" s="45"/>
+      <c r="D132" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="E132" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="F132" s="16"/>
+      <c r="G132" s="19" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A133" s="39"/>
+      <c r="B133" s="41"/>
+      <c r="C133" s="45"/>
+      <c r="D133" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="E133" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="F133" s="16"/>
+      <c r="G133" s="19" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A134" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="B134" s="41" t="s">
-        <v>151</v>
-      </c>
-      <c r="C134" s="45" t="s">
-        <v>153</v>
-      </c>
-      <c r="D134" s="30" t="s">
-        <v>164</v>
-      </c>
-      <c r="E134" s="14" t="s">
+      <c r="A134" s="39"/>
+      <c r="B134" s="41"/>
+      <c r="C134" s="46"/>
+      <c r="D134" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="E134" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="F134" s="14"/>
-      <c r="G134" s="20" t="s">
+      <c r="F134" s="16"/>
+      <c r="G134" s="19" t="s">
         <v>156</v>
-      </c>
-      <c r="H134" s="9" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A135" s="39"/>
       <c r="B135" s="41"/>
-      <c r="C135" s="45"/>
+      <c r="C135" s="28" t="s">
+        <v>154</v>
+      </c>
       <c r="D135" s="17" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E135" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F135" s="16"/>
-      <c r="G135" s="19" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="G135" s="19"/>
+    </row>
+    <row r="136" spans="1:8" ht="102" x14ac:dyDescent="0.45">
       <c r="A136" s="39"/>
       <c r="B136" s="41"/>
-      <c r="C136" s="45"/>
+      <c r="C136" s="44" t="s">
+        <v>165</v>
+      </c>
       <c r="D136" s="17" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="E136" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F136" s="16"/>
-      <c r="G136" s="19" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="G136" s="17" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" ht="51" x14ac:dyDescent="0.45">
       <c r="A137" s="39"/>
       <c r="B137" s="41"/>
-      <c r="C137" s="46"/>
+      <c r="C137" s="45"/>
       <c r="D137" s="17" t="s">
-        <v>163</v>
+        <v>201</v>
       </c>
       <c r="E137" s="16" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="F137" s="16"/>
-      <c r="G137" s="19" t="s">
-        <v>156</v>
+      <c r="G137" s="17" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A138" s="39"/>
       <c r="B138" s="41"/>
-      <c r="C138" s="28" t="s">
-        <v>154</v>
-      </c>
+      <c r="C138" s="45"/>
       <c r="D138" s="17" t="s">
-        <v>155</v>
+        <v>198</v>
       </c>
       <c r="E138" s="16" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="F138" s="16"/>
-      <c r="G138" s="19"/>
-    </row>
-    <row r="139" spans="1:8" ht="102" x14ac:dyDescent="0.45">
+      <c r="G138" s="19" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A139" s="39"/>
       <c r="B139" s="41"/>
-      <c r="C139" s="44" t="s">
-        <v>165</v>
-      </c>
+      <c r="C139" s="45"/>
       <c r="D139" s="17" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E139" s="16" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="F139" s="16"/>
-      <c r="G139" s="17" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" ht="51" x14ac:dyDescent="0.45">
+      <c r="G139" s="19" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A140" s="39"/>
       <c r="B140" s="41"/>
-      <c r="C140" s="45"/>
+      <c r="C140" s="46"/>
       <c r="D140" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="E140" s="16" t="s">
-        <v>132</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="E140" s="16"/>
       <c r="F140" s="16"/>
-      <c r="G140" s="17" t="s">
-        <v>202</v>
+      <c r="G140" s="19" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A141" s="39"/>
       <c r="B141" s="41"/>
-      <c r="C141" s="45"/>
+      <c r="C141" s="44" t="s">
+        <v>166</v>
+      </c>
       <c r="D141" s="17" t="s">
-        <v>198</v>
-      </c>
-      <c r="E141" s="16" t="s">
-        <v>131</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="E141" s="16"/>
       <c r="F141" s="16"/>
-      <c r="G141" s="19" t="s">
-        <v>199</v>
-      </c>
+      <c r="G141" s="19"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A142" s="39"/>
       <c r="B142" s="41"/>
       <c r="C142" s="45"/>
       <c r="D142" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="E142" s="16" t="s">
-        <v>131</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="E142" s="16"/>
       <c r="F142" s="16"/>
-      <c r="G142" s="19" t="s">
-        <v>197</v>
-      </c>
+      <c r="G142" s="19"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A143" s="39"/>
       <c r="B143" s="41"/>
-      <c r="C143" s="46"/>
+      <c r="C143" s="45"/>
       <c r="D143" s="17" t="s">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="E143" s="16"/>
       <c r="F143" s="16"/>
-      <c r="G143" s="19" t="s">
-        <v>200</v>
-      </c>
+      <c r="G143" s="19"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A144" s="39"/>
       <c r="B144" s="41"/>
-      <c r="C144" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="D144" s="17" t="s">
-        <v>157</v>
+      <c r="C144" s="46"/>
+      <c r="D144" s="19" t="s">
+        <v>158</v>
       </c>
       <c r="E144" s="16"/>
       <c r="F144" s="16"/>
       <c r="G144" s="19"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A145" s="39"/>
       <c r="B145" s="41"/>
-      <c r="C145" s="45"/>
-      <c r="D145" s="17" t="s">
-        <v>160</v>
-      </c>
+      <c r="C145" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="D145" s="19"/>
       <c r="E145" s="16"/>
       <c r="F145" s="16"/>
       <c r="G145" s="19"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A146" s="39"/>
-      <c r="B146" s="41"/>
-      <c r="C146" s="45"/>
-      <c r="D146" s="17" t="s">
-        <v>159</v>
-      </c>
+      <c r="B146" s="42"/>
+      <c r="C146" s="28"/>
+      <c r="D146" s="19"/>
       <c r="E146" s="16"/>
       <c r="F146" s="16"/>
       <c r="G146" s="19"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A147" s="39"/>
-      <c r="B147" s="41"/>
-      <c r="C147" s="46"/>
-      <c r="D147" s="19" t="s">
-        <v>158</v>
-      </c>
+      <c r="B147" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="C147" s="28"/>
+      <c r="D147" s="19"/>
       <c r="E147" s="16"/>
       <c r="F147" s="16"/>
       <c r="G147" s="19"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A148" s="39"/>
       <c r="B148" s="41"/>
-      <c r="C148" s="28" t="s">
-        <v>152</v>
-      </c>
+      <c r="C148" s="28"/>
       <c r="D148" s="19"/>
       <c r="E148" s="16"/>
       <c r="F148" s="16"/>
       <c r="G148" s="19"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A149" s="39"/>
       <c r="B149" s="42"/>
       <c r="C149" s="28"/>
@@ -4976,10 +5033,10 @@
       <c r="F149" s="16"/>
       <c r="G149" s="19"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A150" s="39"/>
-      <c r="B150" s="43" t="s">
-        <v>170</v>
+      <c r="B150" s="29" t="s">
+        <v>171</v>
       </c>
       <c r="C150" s="28"/>
       <c r="D150" s="19"/>
@@ -4987,201 +5044,1731 @@
       <c r="F150" s="16"/>
       <c r="G150" s="19"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A151" s="39"/>
-      <c r="B151" s="41"/>
+      <c r="B151" s="43" t="s">
+        <v>172</v>
+      </c>
       <c r="C151" s="28"/>
       <c r="D151" s="19"/>
       <c r="E151" s="16"/>
       <c r="F151" s="16"/>
       <c r="G151" s="19"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A152" s="39"/>
-      <c r="B152" s="42"/>
-      <c r="C152" s="28"/>
+      <c r="B152" s="41"/>
+      <c r="C152" s="28" t="s">
+        <v>180</v>
+      </c>
       <c r="D152" s="19"/>
       <c r="E152" s="16"/>
       <c r="F152" s="16"/>
       <c r="G152" s="19"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A153" s="39"/>
-      <c r="B153" s="29" t="s">
-        <v>171</v>
-      </c>
-      <c r="C153" s="28"/>
+      <c r="B153" s="41"/>
+      <c r="C153" s="28" t="s">
+        <v>182</v>
+      </c>
       <c r="D153" s="19"/>
       <c r="E153" s="16"/>
       <c r="F153" s="16"/>
-      <c r="G153" s="19"/>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G153" s="19" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A154" s="39"/>
-      <c r="B154" s="43" t="s">
-        <v>172</v>
-      </c>
-      <c r="C154" s="28"/>
+      <c r="B154" s="41"/>
+      <c r="C154" s="28" t="s">
+        <v>181</v>
+      </c>
       <c r="D154" s="19"/>
       <c r="E154" s="16"/>
       <c r="F154" s="16"/>
       <c r="G154" s="19"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A155" s="39"/>
       <c r="B155" s="41"/>
-      <c r="C155" s="28" t="s">
-        <v>180</v>
-      </c>
+      <c r="C155" s="28"/>
       <c r="D155" s="19"/>
       <c r="E155" s="16"/>
       <c r="F155" s="16"/>
       <c r="G155" s="19"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A156" s="39"/>
       <c r="B156" s="41"/>
-      <c r="C156" s="28" t="s">
-        <v>182</v>
-      </c>
+      <c r="C156" s="28"/>
       <c r="D156" s="19"/>
       <c r="E156" s="16"/>
       <c r="F156" s="16"/>
-      <c r="G156" s="19" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G156" s="19"/>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A157" s="39"/>
       <c r="B157" s="41"/>
-      <c r="C157" s="28" t="s">
-        <v>181</v>
-      </c>
+      <c r="C157" s="28"/>
       <c r="D157" s="19"/>
       <c r="E157" s="16"/>
       <c r="F157" s="16"/>
       <c r="G157" s="19"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A158" s="39"/>
-      <c r="B158" s="41"/>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A158" s="40"/>
+      <c r="B158" s="42"/>
       <c r="C158" s="28"/>
       <c r="D158" s="19"/>
       <c r="E158" s="16"/>
       <c r="F158" s="16"/>
       <c r="G158" s="19"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A159" s="39"/>
-      <c r="B159" s="41"/>
-      <c r="C159" s="28"/>
-      <c r="D159" s="19"/>
-      <c r="E159" s="16"/>
-      <c r="F159" s="16"/>
-      <c r="G159" s="19"/>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A160" s="39"/>
-      <c r="B160" s="41"/>
-      <c r="C160" s="28"/>
-      <c r="D160" s="19"/>
-      <c r="E160" s="16"/>
-      <c r="F160" s="16"/>
-      <c r="G160" s="19"/>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A161" s="40"/>
-      <c r="B161" s="42"/>
-      <c r="C161" s="28"/>
-      <c r="D161" s="19"/>
-      <c r="E161" s="16"/>
-      <c r="F161" s="16"/>
-      <c r="G161" s="19"/>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="B162" t="s">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="B159" t="s">
         <v>144</v>
       </c>
-      <c r="C162" t="s">
+      <c r="C159" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="I163" s="7"/>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="C164" t="s">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="I160" s="7"/>
+    </row>
+    <row r="161" spans="3:9" x14ac:dyDescent="0.45">
+      <c r="C161" t="s">
         <v>193</v>
       </c>
-      <c r="I164" s="8"/>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="I165" s="8"/>
+      <c r="I161" s="8"/>
+    </row>
+    <row r="162" spans="3:9" x14ac:dyDescent="0.45">
+      <c r="I162" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G119" xr:uid="{34DC90E1-7112-4806-ADC5-98CA8498E977}"/>
-  <mergeCells count="58">
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C21:C24"/>
-    <mergeCell ref="C25:C28"/>
-    <mergeCell ref="B150:B152"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="C96:C100"/>
+  <autoFilter ref="A4:G116" xr:uid="{34DC90E1-7112-4806-ADC5-98CA8498E977}"/>
+  <mergeCells count="56">
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="B147:B149"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="C93:C97"/>
+    <mergeCell ref="C105:C106"/>
+    <mergeCell ref="B66:B79"/>
+    <mergeCell ref="C66:C68"/>
+    <mergeCell ref="C69:C71"/>
+    <mergeCell ref="C72:C75"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B80:B83"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="A116:A130"/>
+    <mergeCell ref="B119:B130"/>
+    <mergeCell ref="B116:B118"/>
+    <mergeCell ref="B108:B111"/>
     <mergeCell ref="C108:C109"/>
-    <mergeCell ref="B69:B82"/>
-    <mergeCell ref="C69:C71"/>
-    <mergeCell ref="C72:C74"/>
-    <mergeCell ref="C75:C78"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="B83:B86"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="A119:A133"/>
-    <mergeCell ref="B122:B133"/>
-    <mergeCell ref="B119:B121"/>
-    <mergeCell ref="B111:B114"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="C113:C114"/>
-    <mergeCell ref="A5:A118"/>
-    <mergeCell ref="B5:B12"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B13:B28"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="B101:B110"/>
-    <mergeCell ref="C101:C103"/>
-    <mergeCell ref="C104:C107"/>
-    <mergeCell ref="B61:B68"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="C63:C68"/>
-    <mergeCell ref="B29:B60"/>
+    <mergeCell ref="C110:C111"/>
+    <mergeCell ref="A5:A115"/>
+    <mergeCell ref="B5:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B12:B25"/>
+    <mergeCell ref="B98:B107"/>
+    <mergeCell ref="C98:C100"/>
+    <mergeCell ref="C101:C104"/>
+    <mergeCell ref="B58:B65"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="C60:C65"/>
+    <mergeCell ref="B26:B57"/>
+    <mergeCell ref="C26:C28"/>
     <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="C35:C38"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="C40:C42"/>
     <mergeCell ref="C43:C45"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="C48:C50"/>
     <mergeCell ref="C51:C53"/>
-    <mergeCell ref="C54:C56"/>
-    <mergeCell ref="A134:A161"/>
-    <mergeCell ref="B134:B149"/>
-    <mergeCell ref="B154:B161"/>
-    <mergeCell ref="C144:C147"/>
-    <mergeCell ref="C134:C137"/>
-    <mergeCell ref="C139:C143"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="B87:B100"/>
-    <mergeCell ref="C87:C89"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="A131:A158"/>
+    <mergeCell ref="B131:B146"/>
+    <mergeCell ref="B151:B158"/>
+    <mergeCell ref="C141:C144"/>
+    <mergeCell ref="C131:C134"/>
+    <mergeCell ref="C136:C140"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="B84:B97"/>
+    <mergeCell ref="C84:C86"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="C56:C57"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EFC0EAB-5103-4A10-AA81-95D4B4AEDD51}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:I133"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="21.25" customWidth="1"/>
+    <col min="2" max="2" width="18.58203125" customWidth="1"/>
+    <col min="3" max="3" width="29.08203125" customWidth="1"/>
+    <col min="4" max="4" width="29.83203125" style="3" customWidth="1"/>
+    <col min="5" max="6" width="10.83203125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="56.25" style="3" customWidth="1"/>
+    <col min="8" max="8" width="28.58203125" style="9" customWidth="1"/>
+    <col min="9" max="9" width="7.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="D1"/>
+    </row>
+    <row r="2" spans="1:8" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="34"/>
+    </row>
+    <row r="3" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D3"/>
+    </row>
+    <row r="4" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" s="38" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="13"/>
+      <c r="D5" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" s="39"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="E6" s="23"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="19"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" s="39"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="E7" s="23"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="19"/>
+    </row>
+    <row r="8" spans="1:8" ht="34" x14ac:dyDescent="0.45">
+      <c r="A8" s="39"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="24"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="17" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A9" s="39"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="19"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A10" s="39"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="19"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A11" s="39"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="19"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A12" s="39"/>
+      <c r="B12" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" s="25"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="19"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A13" s="39"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="25"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="19"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A14" s="39"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="19"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A15" s="39"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="19"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A16" s="39"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="25"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="19"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A17" s="39"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="23"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="19"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A18" s="39"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="19"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A19" s="39"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="19"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A20" s="39"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="19"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A21" s="39"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A22" s="39"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="19"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A23" s="39"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="19"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A24" s="39"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="19"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A25" s="39"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="19"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A26" s="39"/>
+      <c r="B26" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="19"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A27" s="39"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="19"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A28" s="39"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="19"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A29" s="39"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="19"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A30" s="39"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="19"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A31" s="39"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="19"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A32" s="39"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="19"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A33" s="39"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="19"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A34" s="39"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="19"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A35" s="39"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="19"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A36" s="39"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="19"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A37" s="39"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="19"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A38" s="39"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="19"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A39" s="39"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="36"/>
+      <c r="D39" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="19"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A40" s="39"/>
+      <c r="B40" s="36"/>
+      <c r="C40" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="19"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A41" s="39"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="19"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A42" s="39"/>
+      <c r="B42" s="36"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="19"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A43" s="39"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="19"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A44" s="39"/>
+      <c r="B44" s="36"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+      <c r="G44" s="19"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A45" s="39"/>
+      <c r="B45" s="36"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="19"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A46" s="39"/>
+      <c r="B46" s="36"/>
+      <c r="C46" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="19"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A47" s="39"/>
+      <c r="B47" s="36"/>
+      <c r="C47" s="36"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21"/>
+      <c r="G47" s="19"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A48" s="39"/>
+      <c r="B48" s="36"/>
+      <c r="C48" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="19"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A49" s="39"/>
+      <c r="B49" s="36"/>
+      <c r="C49" s="36"/>
+      <c r="D49" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="19"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A50" s="39"/>
+      <c r="B50" s="36"/>
+      <c r="C50" s="36"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="21"/>
+      <c r="F50" s="21"/>
+      <c r="G50" s="19"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A51" s="39"/>
+      <c r="B51" s="36"/>
+      <c r="C51" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="E51" s="26"/>
+      <c r="F51" s="26"/>
+      <c r="G51" s="19"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A52" s="39"/>
+      <c r="B52" s="36"/>
+      <c r="C52" s="36"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="21"/>
+      <c r="G52" s="19"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A53" s="39"/>
+      <c r="B53" s="36"/>
+      <c r="C53" s="36"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="21"/>
+      <c r="G53" s="19"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A54" s="39"/>
+      <c r="B54" s="36"/>
+      <c r="C54" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="D54" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="19"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A55" s="39"/>
+      <c r="B55" s="36"/>
+      <c r="C55" s="37"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="21"/>
+      <c r="G55" s="19"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A56" s="39"/>
+      <c r="B56" s="36"/>
+      <c r="C56" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="D56" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="19"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A57" s="39"/>
+      <c r="B57" s="37"/>
+      <c r="C57" s="36"/>
+      <c r="D57" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="19"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A58" s="39"/>
+      <c r="B58" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C58" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E58" s="23"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="19"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A59" s="39"/>
+      <c r="B59" s="36"/>
+      <c r="C59" s="36"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="19"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A60" s="39"/>
+      <c r="B60" s="36"/>
+      <c r="C60" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E60" s="23"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="19"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A61" s="39"/>
+      <c r="B61" s="36"/>
+      <c r="C61" s="36"/>
+      <c r="D61" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E61" s="23"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="19"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A62" s="39"/>
+      <c r="B62" s="36"/>
+      <c r="C62" s="36"/>
+      <c r="D62" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E62" s="23"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="19"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A63" s="39"/>
+      <c r="B63" s="36"/>
+      <c r="C63" s="36"/>
+      <c r="D63" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E63" s="23"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="19"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A64" s="39"/>
+      <c r="B64" s="36"/>
+      <c r="C64" s="36"/>
+      <c r="D64" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E64" s="23"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="19"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A65" s="39"/>
+      <c r="B65" s="36"/>
+      <c r="C65" s="36"/>
+      <c r="D65" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E65" s="23"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="19"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A66" s="39"/>
+      <c r="B66" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E66" s="23"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="19"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A67" s="39"/>
+      <c r="B67" s="36"/>
+      <c r="C67" s="36"/>
+      <c r="D67" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="E67" s="23"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="19"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A68" s="39"/>
+      <c r="B68" s="36"/>
+      <c r="C68" s="36"/>
+      <c r="D68" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="E68" s="23"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="19"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A69" s="39"/>
+      <c r="B69" s="36"/>
+      <c r="C69" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E69" s="23"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="19"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A70" s="39"/>
+      <c r="B70" s="36"/>
+      <c r="C70" s="36"/>
+      <c r="D70" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E70" s="23"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="19"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A71" s="39"/>
+      <c r="B71" s="36"/>
+      <c r="C71" s="36"/>
+      <c r="D71" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="E71" s="23"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="19"/>
+    </row>
+    <row r="72" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A72" s="39"/>
+      <c r="B72" s="36"/>
+      <c r="C72" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E72" s="23"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="19"/>
+    </row>
+    <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A73" s="39"/>
+      <c r="B73" s="36"/>
+      <c r="C73" s="36"/>
+      <c r="D73" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E73" s="23"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="19"/>
+    </row>
+    <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A74" s="39"/>
+      <c r="B74" s="36"/>
+      <c r="C74" s="36"/>
+      <c r="D74" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E74" s="23"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="19"/>
+    </row>
+    <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A75" s="39"/>
+      <c r="B75" s="36"/>
+      <c r="C75" s="36"/>
+      <c r="D75" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E75" s="23"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="19"/>
+    </row>
+    <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A76" s="39"/>
+      <c r="B76" s="36"/>
+      <c r="C76" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="D76" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E76" s="23"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="19"/>
+    </row>
+    <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A77" s="39"/>
+      <c r="B77" s="36"/>
+      <c r="C77" s="36"/>
+      <c r="D77" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E77" s="23"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="19"/>
+    </row>
+    <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A78" s="39"/>
+      <c r="B78" s="36"/>
+      <c r="C78" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="D78" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E78" s="23"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="19"/>
+    </row>
+    <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A79" s="39"/>
+      <c r="B79" s="36"/>
+      <c r="C79" s="36"/>
+      <c r="D79" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E79" s="23"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="19"/>
+    </row>
+    <row r="80" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A80" s="39"/>
+      <c r="B80" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="C80" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="D80" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="19"/>
+    </row>
+    <row r="81" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A81" s="39"/>
+      <c r="B81" s="36"/>
+      <c r="C81" s="37"/>
+      <c r="D81" s="15"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="15"/>
+      <c r="G81" s="19"/>
+    </row>
+    <row r="82" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A82" s="39"/>
+      <c r="B82" s="36"/>
+      <c r="C82" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="D82" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="E82" s="23"/>
+      <c r="F82" s="23"/>
+      <c r="G82" s="19"/>
+    </row>
+    <row r="83" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A83" s="39"/>
+      <c r="B83" s="37"/>
+      <c r="C83" s="37"/>
+      <c r="D83" s="15"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="15"/>
+      <c r="G83" s="19"/>
+    </row>
+    <row r="84" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A84" s="39"/>
+      <c r="B84" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C84" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="D84" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="E84" s="23"/>
+      <c r="F84" s="23"/>
+      <c r="G84" s="19"/>
+    </row>
+    <row r="85" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A85" s="39"/>
+      <c r="B85" s="36"/>
+      <c r="C85" s="36"/>
+      <c r="D85" s="15"/>
+      <c r="E85" s="15"/>
+      <c r="F85" s="15"/>
+      <c r="G85" s="19"/>
+    </row>
+    <row r="86" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A86" s="39"/>
+      <c r="B86" s="36"/>
+      <c r="C86" s="37"/>
+      <c r="D86" s="15"/>
+      <c r="E86" s="15"/>
+      <c r="F86" s="15"/>
+      <c r="G86" s="19"/>
+    </row>
+    <row r="87" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A87" s="39"/>
+      <c r="B87" s="36"/>
+      <c r="C87" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D87" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="E87" s="23"/>
+      <c r="F87" s="23"/>
+      <c r="G87" s="19"/>
+    </row>
+    <row r="88" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A88" s="39"/>
+      <c r="B88" s="36"/>
+      <c r="C88" s="36"/>
+      <c r="D88" s="15"/>
+      <c r="E88" s="15"/>
+      <c r="F88" s="15"/>
+      <c r="G88" s="19"/>
+    </row>
+    <row r="89" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A89" s="39"/>
+      <c r="B89" s="36"/>
+      <c r="C89" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="D89" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E89" s="23"/>
+      <c r="F89" s="23"/>
+      <c r="G89" s="19"/>
+    </row>
+    <row r="90" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A90" s="39"/>
+      <c r="B90" s="36"/>
+      <c r="C90" s="36"/>
+      <c r="D90" s="15"/>
+      <c r="E90" s="15"/>
+      <c r="F90" s="15"/>
+      <c r="G90" s="19"/>
+    </row>
+    <row r="91" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A91" s="39"/>
+      <c r="B91" s="36"/>
+      <c r="C91" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="D91" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E91" s="23"/>
+      <c r="F91" s="23"/>
+      <c r="G91" s="19"/>
+    </row>
+    <row r="92" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A92" s="39"/>
+      <c r="B92" s="36"/>
+      <c r="C92" s="36"/>
+      <c r="D92" s="15"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="15"/>
+      <c r="G92" s="19"/>
+    </row>
+    <row r="93" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A93" s="39"/>
+      <c r="B93" s="36"/>
+      <c r="C93" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="D93" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E93" s="23"/>
+      <c r="F93" s="23"/>
+      <c r="G93" s="19"/>
+    </row>
+    <row r="94" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A94" s="39"/>
+      <c r="B94" s="36"/>
+      <c r="C94" s="36"/>
+      <c r="D94" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="E94" s="23"/>
+      <c r="F94" s="23"/>
+      <c r="G94" s="19"/>
+    </row>
+    <row r="95" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A95" s="39"/>
+      <c r="B95" s="36"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E95" s="23"/>
+      <c r="F95" s="23"/>
+      <c r="G95" s="19"/>
+    </row>
+    <row r="96" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A96" s="39"/>
+      <c r="B96" s="36"/>
+      <c r="C96" s="36"/>
+      <c r="D96" s="15"/>
+      <c r="E96" s="15"/>
+      <c r="F96" s="15"/>
+      <c r="G96" s="19"/>
+    </row>
+    <row r="97" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A97" s="39"/>
+      <c r="B97" s="36"/>
+      <c r="C97" s="36"/>
+      <c r="D97" s="15"/>
+      <c r="E97" s="15"/>
+      <c r="F97" s="15"/>
+      <c r="G97" s="19"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A98" s="39"/>
+      <c r="B98" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="C98" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="D98" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="E98" s="23"/>
+      <c r="F98" s="23"/>
+      <c r="G98" s="19"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A99" s="39"/>
+      <c r="B99" s="36"/>
+      <c r="C99" s="36"/>
+      <c r="D99" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E99" s="23"/>
+      <c r="F99" s="23"/>
+      <c r="G99" s="19"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A100" s="39"/>
+      <c r="B100" s="36"/>
+      <c r="C100" s="36"/>
+      <c r="D100" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E100" s="23"/>
+      <c r="F100" s="23"/>
+      <c r="G100" s="19"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A101" s="39"/>
+      <c r="B101" s="36"/>
+      <c r="C101" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="D101" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E101" s="23"/>
+      <c r="F101" s="23"/>
+      <c r="G101" s="19"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A102" s="39"/>
+      <c r="B102" s="36"/>
+      <c r="C102" s="36"/>
+      <c r="D102" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="E102" s="23"/>
+      <c r="F102" s="23"/>
+      <c r="G102" s="19"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A103" s="39"/>
+      <c r="B103" s="36"/>
+      <c r="C103" s="36"/>
+      <c r="D103" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E103" s="23"/>
+      <c r="F103" s="23"/>
+      <c r="G103" s="19"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A104" s="39"/>
+      <c r="B104" s="36"/>
+      <c r="C104" s="36"/>
+      <c r="D104" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="E104" s="23"/>
+      <c r="F104" s="23"/>
+      <c r="G104" s="19"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A105" s="39"/>
+      <c r="B105" s="36"/>
+      <c r="C105" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="D105" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E105" s="23"/>
+      <c r="F105" s="23"/>
+      <c r="G105" s="19"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A106" s="39"/>
+      <c r="B106" s="36"/>
+      <c r="C106" s="36"/>
+      <c r="D106" s="15"/>
+      <c r="E106" s="15"/>
+      <c r="F106" s="15"/>
+      <c r="G106" s="19"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A107" s="39"/>
+      <c r="B107" s="36"/>
+      <c r="C107" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D107" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E107" s="23"/>
+      <c r="F107" s="23"/>
+      <c r="G107" s="19"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A108" s="39"/>
+      <c r="B108" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="C108" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="D108" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="E108" s="23"/>
+      <c r="F108" s="23"/>
+      <c r="G108" s="19"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A109" s="39"/>
+      <c r="B109" s="36"/>
+      <c r="C109" s="37"/>
+      <c r="D109" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E109" s="23"/>
+      <c r="F109" s="23"/>
+      <c r="G109" s="19"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A110" s="39"/>
+      <c r="B110" s="36"/>
+      <c r="C110" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="D110" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E110" s="23"/>
+      <c r="F110" s="23"/>
+      <c r="G110" s="19"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A111" s="39"/>
+      <c r="B111" s="37"/>
+      <c r="C111" s="37"/>
+      <c r="D111" s="15"/>
+      <c r="E111" s="15"/>
+      <c r="F111" s="15"/>
+      <c r="G111" s="19"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A112" s="39"/>
+      <c r="B112" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C112" s="11"/>
+      <c r="D112" s="15"/>
+      <c r="E112" s="15"/>
+      <c r="F112" s="15"/>
+      <c r="G112" s="19"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A113" s="39"/>
+      <c r="B113" s="11"/>
+      <c r="C113" s="11"/>
+      <c r="D113" s="15"/>
+      <c r="E113" s="15"/>
+      <c r="F113" s="15"/>
+      <c r="G113" s="19"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A114" s="39"/>
+      <c r="B114" s="11"/>
+      <c r="C114" s="11"/>
+      <c r="D114" s="15"/>
+      <c r="E114" s="15"/>
+      <c r="F114" s="15"/>
+      <c r="G114" s="19"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A115" s="40"/>
+      <c r="B115" s="12"/>
+      <c r="C115" s="12"/>
+      <c r="D115" s="15"/>
+      <c r="E115" s="15"/>
+      <c r="F115" s="15"/>
+      <c r="G115" s="19"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A116" s="39"/>
+      <c r="B116" s="41"/>
+      <c r="C116" s="28"/>
+      <c r="D116" s="19"/>
+      <c r="E116" s="19"/>
+      <c r="F116" s="19"/>
+      <c r="G116" s="19"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A117" s="39"/>
+      <c r="B117" s="42"/>
+      <c r="C117" s="28"/>
+      <c r="D117" s="19"/>
+      <c r="E117" s="19"/>
+      <c r="F117" s="19"/>
+      <c r="G117" s="19"/>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A118" s="39"/>
+      <c r="B118" s="43"/>
+      <c r="C118" s="28"/>
+      <c r="D118" s="19"/>
+      <c r="E118" s="19"/>
+      <c r="F118" s="19"/>
+      <c r="G118" s="19"/>
+      <c r="H118" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A119" s="39"/>
+      <c r="B119" s="41"/>
+      <c r="C119" s="28"/>
+      <c r="D119" s="19"/>
+      <c r="E119" s="19"/>
+      <c r="F119" s="16"/>
+      <c r="G119" s="19"/>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A120" s="39"/>
+      <c r="B120" s="41"/>
+      <c r="C120" s="28"/>
+      <c r="D120" s="19"/>
+      <c r="E120" s="19"/>
+      <c r="F120" s="16"/>
+      <c r="G120" s="19"/>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A121" s="39"/>
+      <c r="B121" s="41"/>
+      <c r="C121" s="28"/>
+      <c r="D121" s="19"/>
+      <c r="E121" s="19"/>
+      <c r="F121" s="16"/>
+      <c r="G121" s="19"/>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A122" s="39"/>
+      <c r="B122" s="41"/>
+      <c r="C122" s="28"/>
+      <c r="D122" s="19"/>
+      <c r="E122" s="19"/>
+      <c r="F122" s="16"/>
+      <c r="G122" s="19"/>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A123" s="39"/>
+      <c r="B123" s="41"/>
+      <c r="C123" s="28"/>
+      <c r="D123" s="19"/>
+      <c r="E123" s="19"/>
+      <c r="F123" s="19"/>
+      <c r="G123" s="19"/>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A124" s="39"/>
+      <c r="B124" s="41"/>
+      <c r="C124" s="28"/>
+      <c r="D124" s="19"/>
+      <c r="E124" s="19"/>
+      <c r="F124" s="16"/>
+      <c r="G124" s="19"/>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A125" s="39"/>
+      <c r="B125" s="41"/>
+      <c r="C125" s="28"/>
+      <c r="D125" s="19"/>
+      <c r="E125" s="19"/>
+      <c r="F125" s="19"/>
+      <c r="G125" s="19"/>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A126" s="39"/>
+      <c r="B126" s="41"/>
+      <c r="C126" s="28"/>
+      <c r="D126" s="19"/>
+      <c r="E126" s="19"/>
+      <c r="F126" s="19"/>
+      <c r="G126" s="19"/>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A127" s="39"/>
+      <c r="B127" s="41"/>
+      <c r="C127" s="28"/>
+      <c r="D127" s="19"/>
+      <c r="E127" s="19"/>
+      <c r="F127" s="19"/>
+      <c r="G127" s="19"/>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A128" s="39"/>
+      <c r="B128" s="41"/>
+      <c r="C128" s="28"/>
+      <c r="D128" s="19"/>
+      <c r="E128" s="19"/>
+      <c r="F128" s="19"/>
+      <c r="G128" s="19"/>
+    </row>
+    <row r="129" spans="1:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A129" s="47"/>
+      <c r="B129" s="48"/>
+      <c r="C129" s="31"/>
+      <c r="D129" s="32"/>
+      <c r="E129" s="33"/>
+      <c r="F129" s="33"/>
+      <c r="G129" s="32"/>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="I131" s="7"/>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="I132" s="8"/>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="I133" s="8"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:G115" xr:uid="{34DC90E1-7112-4806-ADC5-98CA8498E977}"/>
+  <mergeCells count="49">
+    <mergeCell ref="A116:A129"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="B118:B129"/>
+    <mergeCell ref="B98:B107"/>
+    <mergeCell ref="C98:C100"/>
+    <mergeCell ref="C101:C104"/>
+    <mergeCell ref="C105:C106"/>
+    <mergeCell ref="B108:B111"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="C110:C111"/>
+    <mergeCell ref="B80:B83"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="B84:B97"/>
+    <mergeCell ref="C84:C86"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="C93:C97"/>
+    <mergeCell ref="B66:B79"/>
+    <mergeCell ref="C66:C68"/>
+    <mergeCell ref="C69:C71"/>
+    <mergeCell ref="C72:C75"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="B58:B65"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="C60:C65"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="A5:A115"/>
+    <mergeCell ref="B5:B11"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B12:B25"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="B26:B57"/>
+    <mergeCell ref="C26:C28"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2D875BA-B2A2-4199-A659-BF030CE3032F}">
+  <dimension ref="C2:H9"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="11.75" customWidth="1"/>
+    <col min="3" max="3" width="21.4140625" customWidth="1"/>
+    <col min="4" max="4" width="36.1640625" customWidth="1"/>
+    <col min="5" max="8" width="17.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:8" s="5" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="E2" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="3:8" s="5" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="C3" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C4" t="s">
+        <v>212</v>
+      </c>
+      <c r="D4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C9" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/doc/금융감독원 홈페이지_UIUX_퍼블_컴포넌트리스트 .xlsx
+++ b/doc/금융감독원 홈페이지_UIUX_퍼블_컴포넌트리스트 .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\03.Publishing\fss\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3388EF8B-1D84-44CF-8529-6044779B968A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E87BA87-0522-4FE1-9E33-BCD93584425B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46260" yWindow="-4680" windowWidth="20115" windowHeight="15105" tabRatio="499" activeTab="3" xr2:uid="{BA3ED54C-CC85-4CD0-8ADB-46ECF631616A}"/>
+    <workbookView xWindow="46260" yWindow="-4680" windowWidth="20730" windowHeight="15105" tabRatio="499" activeTab="3" xr2:uid="{BA3ED54C-CC85-4CD0-8ADB-46ECF631616A}"/>
   </bookViews>
   <sheets>
     <sheet name="체크리스트_목록" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="221">
   <si>
     <t>대분류</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -873,6 +873,34 @@
   </si>
   <si>
     <t>color: var(--krds-button--color-link-text)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>color: var(--krds-light-color-text-basic)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#063A74</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#052B57</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#031F3F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#8A949E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#5917B8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visited</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6721,49 +6749,70 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2D875BA-B2A2-4199-A659-BF030CE3032F}">
-  <dimension ref="C2:H9"/>
+  <dimension ref="B2:H9"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="11.75" customWidth="1"/>
-    <col min="3" max="3" width="21.4140625" customWidth="1"/>
-    <col min="4" max="4" width="36.1640625" customWidth="1"/>
-    <col min="5" max="8" width="17.33203125" customWidth="1"/>
+    <col min="1" max="1" width="5.4140625" customWidth="1"/>
+    <col min="2" max="2" width="21.4140625" customWidth="1"/>
+    <col min="3" max="3" width="35.25" customWidth="1"/>
+    <col min="4" max="7" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:8" s="5" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="D2" s="5" t="s">
+        <v>210</v>
+      </c>
       <c r="E2" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="3" spans="3:8" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="C3" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>212</v>
+      </c>
       <c r="C4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D4" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.45">
+        <v>215</v>
+      </c>
+      <c r="E4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F4" t="s">
+        <v>217</v>
+      </c>
+      <c r="G4" t="s">
+        <v>218</v>
+      </c>
+      <c r="H4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
+        <v>211</v>
+      </c>
       <c r="C5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.45">
-      <c r="C9" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B9" s="5" t="s">
         <v>64</v>
       </c>
     </row>

--- a/doc/금융감독원 홈페이지_UIUX_퍼블_컴포넌트리스트 .xlsx
+++ b/doc/금융감독원 홈페이지_UIUX_퍼블_컴포넌트리스트 .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\03.Publishing\fss\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E87BA87-0522-4FE1-9E33-BCD93584425B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4FC5DB-33B6-41F2-BDA6-7FDCD243F0CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46260" yWindow="-4680" windowWidth="20730" windowHeight="15105" tabRatio="499" activeTab="3" xr2:uid="{BA3ED54C-CC85-4CD0-8ADB-46ECF631616A}"/>
+    <workbookView xWindow="38280" yWindow="3345" windowWidth="29040" windowHeight="15720" tabRatio="499" activeTab="1" xr2:uid="{BA3ED54C-CC85-4CD0-8ADB-46ECF631616A}"/>
   </bookViews>
   <sheets>
     <sheet name="체크리스트_목록" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'design guide'!$A$4:$G$115</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ia guide'!$A$4:$G$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ia guide'!$A$4:$G$154</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">체크리스트_목록!$A$4:$F$164</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="229">
   <si>
     <t>대분류</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -901,6 +901,35 @@
   </si>
   <si>
     <t>visited</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02.26.</t>
+  </si>
+  <si>
+    <t>02.26.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02.25.</t>
+  </si>
+  <si>
+    <t>02.25.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02.24.</t>
+  </si>
+  <si>
+    <t>02.24.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02.26.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입력으로 통합</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1200,10 +1229,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1215,13 +1244,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1232,12 +1267,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1640,7 +1669,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="39"/>
-      <c r="B6" s="36"/>
+      <c r="B6" s="37"/>
       <c r="C6" s="13" t="s">
         <v>130</v>
       </c>
@@ -1650,7 +1679,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="39"/>
-      <c r="B7" s="36"/>
+      <c r="B7" s="37"/>
       <c r="C7" s="35" t="s">
         <v>7</v>
       </c>
@@ -1662,8 +1691,8 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="39"/>
-      <c r="B8" s="36"/>
-      <c r="C8" s="37"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="36"/>
       <c r="D8" s="15" t="s">
         <v>95</v>
       </c>
@@ -1672,7 +1701,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="39"/>
-      <c r="B9" s="36"/>
+      <c r="B9" s="37"/>
       <c r="C9" s="35" t="s">
         <v>8</v>
       </c>
@@ -1686,15 +1715,15 @@
     </row>
     <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A10" s="39"/>
-      <c r="B10" s="36"/>
-      <c r="C10" s="36"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="37"/>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
       <c r="F10" s="16"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="39"/>
-      <c r="B11" s="36"/>
+      <c r="B11" s="37"/>
       <c r="C11" s="35" t="s">
         <v>9</v>
       </c>
@@ -1708,8 +1737,8 @@
     </row>
     <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A12" s="39"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="37"/>
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
       <c r="F12" s="16"/>
@@ -1732,23 +1761,23 @@
     </row>
     <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A14" s="39"/>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
       <c r="D14" s="18"/>
       <c r="E14" s="18"/>
       <c r="F14" s="16"/>
     </row>
     <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15" s="39"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="37"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="36"/>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
       <c r="F15" s="16"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="39"/>
-      <c r="B16" s="36"/>
+      <c r="B16" s="37"/>
       <c r="C16" s="35" t="s">
         <v>11</v>
       </c>
@@ -1762,8 +1791,8 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="39"/>
-      <c r="B17" s="36"/>
-      <c r="C17" s="36"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="37"/>
       <c r="D17" s="18" t="s">
         <v>60</v>
       </c>
@@ -1774,31 +1803,31 @@
     </row>
     <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18" s="39"/>
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
       <c r="D18" s="18"/>
       <c r="E18" s="18"/>
       <c r="F18" s="16"/>
     </row>
     <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19" s="39"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="37"/>
       <c r="D19" s="18"/>
       <c r="E19" s="18"/>
       <c r="F19" s="16"/>
     </row>
     <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A20" s="39"/>
-      <c r="B20" s="36"/>
-      <c r="C20" s="37"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="36"/>
       <c r="D20" s="18"/>
       <c r="E20" s="18"/>
       <c r="F20" s="16"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="39"/>
-      <c r="B21" s="36"/>
+      <c r="B21" s="37"/>
       <c r="C21" s="35" t="s">
         <v>12</v>
       </c>
@@ -1812,23 +1841,23 @@
     </row>
     <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22" s="39"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="36"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="37"/>
       <c r="D22" s="18"/>
       <c r="E22" s="18"/>
       <c r="F22" s="16"/>
     </row>
     <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A23" s="39"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="37"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="36"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="16"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" s="39"/>
-      <c r="B24" s="36"/>
+      <c r="B24" s="37"/>
       <c r="C24" s="13" t="s">
         <v>13</v>
       </c>
@@ -1842,7 +1871,7 @@
     </row>
     <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A25" s="39"/>
-      <c r="B25" s="36"/>
+      <c r="B25" s="37"/>
       <c r="C25" s="35" t="s">
         <v>14</v>
       </c>
@@ -1852,31 +1881,31 @@
     </row>
     <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26" s="39"/>
-      <c r="B26" s="36"/>
-      <c r="C26" s="36"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="37"/>
       <c r="D26" s="15"/>
       <c r="E26" s="15"/>
       <c r="F26" s="16"/>
     </row>
     <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27" s="39"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
       <c r="D27" s="15"/>
       <c r="E27" s="15"/>
       <c r="F27" s="16"/>
     </row>
     <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A28" s="39"/>
-      <c r="B28" s="36"/>
-      <c r="C28" s="37"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="36"/>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
       <c r="F28" s="16"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" s="39"/>
-      <c r="B29" s="36"/>
+      <c r="B29" s="37"/>
       <c r="C29" s="35" t="s">
         <v>15</v>
       </c>
@@ -1890,8 +1919,8 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" s="39"/>
-      <c r="B30" s="36"/>
-      <c r="C30" s="36"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
       <c r="D30" s="20" t="s">
         <v>98</v>
       </c>
@@ -1900,56 +1929,56 @@
     </row>
     <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31" s="39"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="36"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="37"/>
       <c r="D31" s="21"/>
       <c r="E31" s="21"/>
       <c r="F31" s="16"/>
     </row>
     <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A32" s="39"/>
-      <c r="B32" s="36"/>
-      <c r="C32" s="36"/>
+      <c r="B32" s="37"/>
+      <c r="C32" s="37"/>
       <c r="D32" s="21"/>
       <c r="E32" s="21"/>
       <c r="F32" s="16"/>
     </row>
     <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A33" s="39"/>
-      <c r="B33" s="36"/>
-      <c r="C33" s="36"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="37"/>
       <c r="D33" s="21"/>
       <c r="E33" s="21"/>
       <c r="F33" s="16"/>
     </row>
     <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A34" s="39"/>
-      <c r="B34" s="36"/>
-      <c r="C34" s="36"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="37"/>
       <c r="D34" s="21"/>
       <c r="E34" s="21"/>
       <c r="F34" s="16"/>
     </row>
     <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A35" s="39"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="36"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="37"/>
       <c r="D35" s="21"/>
       <c r="E35" s="21"/>
       <c r="F35" s="16"/>
     </row>
     <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A36" s="39"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="36"/>
+      <c r="B36" s="37"/>
+      <c r="C36" s="37"/>
       <c r="D36" s="21"/>
       <c r="E36" s="21"/>
       <c r="F36" s="16"/>
     </row>
     <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A37" s="39"/>
-      <c r="B37" s="37"/>
-      <c r="C37" s="37"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="36"/>
       <c r="D37" s="21"/>
       <c r="E37" s="21"/>
       <c r="F37" s="16"/>
@@ -1970,8 +1999,8 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39" s="39"/>
-      <c r="B39" s="36"/>
-      <c r="C39" s="36"/>
+      <c r="B39" s="37"/>
+      <c r="C39" s="37"/>
       <c r="D39" s="21" t="s">
         <v>111</v>
       </c>
@@ -1980,15 +2009,15 @@
     </row>
     <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A40" s="39"/>
-      <c r="B40" s="36"/>
-      <c r="C40" s="36"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="37"/>
       <c r="D40" s="21"/>
       <c r="E40" s="21"/>
       <c r="F40" s="16"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41" s="39"/>
-      <c r="B41" s="36"/>
+      <c r="B41" s="37"/>
       <c r="C41" s="35" t="s">
         <v>25</v>
       </c>
@@ -2000,23 +2029,23 @@
     </row>
     <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A42" s="39"/>
-      <c r="B42" s="36"/>
-      <c r="C42" s="36"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="37"/>
       <c r="D42" s="21"/>
       <c r="E42" s="21"/>
       <c r="F42" s="16"/>
     </row>
     <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43" s="39"/>
-      <c r="B43" s="36"/>
-      <c r="C43" s="37"/>
+      <c r="B43" s="37"/>
+      <c r="C43" s="36"/>
       <c r="D43" s="21"/>
       <c r="E43" s="21"/>
       <c r="F43" s="16"/>
     </row>
     <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A44" s="39"/>
-      <c r="B44" s="36"/>
+      <c r="B44" s="37"/>
       <c r="C44" s="35" t="s">
         <v>26</v>
       </c>
@@ -2026,31 +2055,31 @@
     </row>
     <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A45" s="39"/>
-      <c r="B45" s="36"/>
-      <c r="C45" s="36"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="37"/>
       <c r="D45" s="21"/>
       <c r="E45" s="21"/>
       <c r="F45" s="16"/>
     </row>
     <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A46" s="39"/>
-      <c r="B46" s="36"/>
-      <c r="C46" s="36"/>
+      <c r="B46" s="37"/>
+      <c r="C46" s="37"/>
       <c r="D46" s="21"/>
       <c r="E46" s="21"/>
       <c r="F46" s="16"/>
     </row>
     <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A47" s="39"/>
-      <c r="B47" s="36"/>
-      <c r="C47" s="37"/>
+      <c r="B47" s="37"/>
+      <c r="C47" s="36"/>
       <c r="D47" s="21"/>
       <c r="E47" s="21"/>
       <c r="F47" s="16"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48" s="39"/>
-      <c r="B48" s="36"/>
+      <c r="B48" s="37"/>
       <c r="C48" s="35" t="s">
         <v>27</v>
       </c>
@@ -2062,15 +2091,15 @@
     </row>
     <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A49" s="39"/>
-      <c r="B49" s="36"/>
-      <c r="C49" s="37"/>
+      <c r="B49" s="37"/>
+      <c r="C49" s="36"/>
       <c r="D49" s="21"/>
       <c r="E49" s="21"/>
       <c r="F49" s="16"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50" s="39"/>
-      <c r="B50" s="36"/>
+      <c r="B50" s="37"/>
       <c r="C50" s="35" t="s">
         <v>28</v>
       </c>
@@ -2082,8 +2111,8 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51" s="39"/>
-      <c r="B51" s="36"/>
-      <c r="C51" s="36"/>
+      <c r="B51" s="37"/>
+      <c r="C51" s="37"/>
       <c r="D51" s="21" t="s">
         <v>97</v>
       </c>
@@ -2092,7 +2121,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A52" s="39"/>
-      <c r="B52" s="36"/>
+      <c r="B52" s="37"/>
       <c r="C52" s="35" t="s">
         <v>29</v>
       </c>
@@ -2104,8 +2133,8 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A53" s="39"/>
-      <c r="B53" s="36"/>
-      <c r="C53" s="36"/>
+      <c r="B53" s="37"/>
+      <c r="C53" s="37"/>
       <c r="D53" s="21" t="s">
         <v>81</v>
       </c>
@@ -2114,8 +2143,8 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A54" s="39"/>
-      <c r="B54" s="36"/>
-      <c r="C54" s="37"/>
+      <c r="B54" s="37"/>
+      <c r="C54" s="36"/>
       <c r="D54" s="21" t="s">
         <v>82</v>
       </c>
@@ -2124,7 +2153,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A55" s="39"/>
-      <c r="B55" s="36"/>
+      <c r="B55" s="37"/>
       <c r="C55" s="35" t="s">
         <v>30</v>
       </c>
@@ -2136,8 +2165,8 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A56" s="39"/>
-      <c r="B56" s="36"/>
-      <c r="C56" s="36"/>
+      <c r="B56" s="37"/>
+      <c r="C56" s="37"/>
       <c r="D56" s="21" t="s">
         <v>62</v>
       </c>
@@ -2146,15 +2175,15 @@
     </row>
     <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A57" s="39"/>
-      <c r="B57" s="36"/>
-      <c r="C57" s="37"/>
+      <c r="B57" s="37"/>
+      <c r="C57" s="36"/>
       <c r="D57" s="21"/>
       <c r="E57" s="21"/>
       <c r="F57" s="16"/>
     </row>
     <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A58" s="39"/>
-      <c r="B58" s="36"/>
+      <c r="B58" s="37"/>
       <c r="C58" s="35" t="s">
         <v>31</v>
       </c>
@@ -2164,15 +2193,15 @@
     </row>
     <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A59" s="39"/>
-      <c r="B59" s="36"/>
-      <c r="C59" s="36"/>
+      <c r="B59" s="37"/>
+      <c r="C59" s="37"/>
       <c r="D59" s="21"/>
       <c r="E59" s="21"/>
       <c r="F59" s="16"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A60" s="39"/>
-      <c r="B60" s="36"/>
+      <c r="B60" s="37"/>
       <c r="C60" s="35" t="s">
         <v>32</v>
       </c>
@@ -2184,8 +2213,8 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A61" s="39"/>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
+      <c r="B61" s="37"/>
+      <c r="C61" s="37"/>
       <c r="D61" s="21" t="s">
         <v>73</v>
       </c>
@@ -2194,31 +2223,31 @@
     </row>
     <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A62" s="39"/>
-      <c r="B62" s="36"/>
-      <c r="C62" s="36"/>
+      <c r="B62" s="37"/>
+      <c r="C62" s="37"/>
       <c r="D62" s="21"/>
       <c r="E62" s="21"/>
       <c r="F62" s="16"/>
     </row>
     <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A63" s="39"/>
-      <c r="B63" s="36"/>
-      <c r="C63" s="36"/>
+      <c r="B63" s="37"/>
+      <c r="C63" s="37"/>
       <c r="D63" s="21"/>
       <c r="E63" s="21"/>
       <c r="F63" s="16"/>
     </row>
     <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A64" s="39"/>
-      <c r="B64" s="36"/>
-      <c r="C64" s="37"/>
+      <c r="B64" s="37"/>
+      <c r="C64" s="36"/>
       <c r="D64" s="21"/>
       <c r="E64" s="21"/>
       <c r="F64" s="16"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A65" s="39"/>
-      <c r="B65" s="36"/>
+      <c r="B65" s="37"/>
       <c r="C65" s="35" t="s">
         <v>33</v>
       </c>
@@ -2230,39 +2259,39 @@
     </row>
     <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A66" s="39"/>
-      <c r="B66" s="36"/>
-      <c r="C66" s="36"/>
+      <c r="B66" s="37"/>
+      <c r="C66" s="37"/>
       <c r="D66" s="21"/>
       <c r="E66" s="21"/>
       <c r="F66" s="16"/>
     </row>
     <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A67" s="39"/>
-      <c r="B67" s="36"/>
-      <c r="C67" s="36"/>
+      <c r="B67" s="37"/>
+      <c r="C67" s="37"/>
       <c r="D67" s="21"/>
       <c r="E67" s="21"/>
       <c r="F67" s="16"/>
     </row>
     <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A68" s="39"/>
-      <c r="B68" s="36"/>
-      <c r="C68" s="36"/>
+      <c r="B68" s="37"/>
+      <c r="C68" s="37"/>
       <c r="D68" s="21"/>
       <c r="E68" s="21"/>
       <c r="F68" s="16"/>
     </row>
     <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A69" s="39"/>
-      <c r="B69" s="36"/>
-      <c r="C69" s="36"/>
+      <c r="B69" s="37"/>
+      <c r="C69" s="37"/>
       <c r="D69" s="21"/>
       <c r="E69" s="21"/>
       <c r="F69" s="16"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A70" s="39"/>
-      <c r="B70" s="36"/>
+      <c r="B70" s="37"/>
       <c r="C70" s="35" t="s">
         <v>34</v>
       </c>
@@ -2274,15 +2303,15 @@
     </row>
     <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A71" s="39"/>
-      <c r="B71" s="36"/>
-      <c r="C71" s="37"/>
+      <c r="B71" s="37"/>
+      <c r="C71" s="36"/>
       <c r="D71" s="21"/>
       <c r="E71" s="21"/>
       <c r="F71" s="16"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A72" s="39"/>
-      <c r="B72" s="36"/>
+      <c r="B72" s="37"/>
       <c r="C72" s="35" t="s">
         <v>35</v>
       </c>
@@ -2294,8 +2323,8 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A73" s="39"/>
-      <c r="B73" s="37"/>
-      <c r="C73" s="36"/>
+      <c r="B73" s="36"/>
+      <c r="C73" s="37"/>
       <c r="D73" s="21" t="s">
         <v>121</v>
       </c>
@@ -2318,39 +2347,39 @@
     </row>
     <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A75" s="39"/>
-      <c r="B75" s="36"/>
-      <c r="C75" s="36"/>
+      <c r="B75" s="37"/>
+      <c r="C75" s="37"/>
       <c r="D75" s="15"/>
       <c r="E75" s="15"/>
       <c r="F75" s="16"/>
     </row>
     <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A76" s="39"/>
-      <c r="B76" s="36"/>
-      <c r="C76" s="36"/>
+      <c r="B76" s="37"/>
+      <c r="C76" s="37"/>
       <c r="D76" s="15"/>
       <c r="E76" s="15"/>
       <c r="F76" s="16"/>
     </row>
     <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A77" s="39"/>
-      <c r="B77" s="36"/>
-      <c r="C77" s="36"/>
+      <c r="B77" s="37"/>
+      <c r="C77" s="37"/>
       <c r="D77" s="15"/>
       <c r="E77" s="15"/>
       <c r="F77" s="16"/>
     </row>
     <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A78" s="39"/>
-      <c r="B78" s="36"/>
-      <c r="C78" s="36"/>
+      <c r="B78" s="37"/>
+      <c r="C78" s="37"/>
       <c r="D78" s="15"/>
       <c r="E78" s="15"/>
       <c r="F78" s="16"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A79" s="39"/>
-      <c r="B79" s="36"/>
+      <c r="B79" s="37"/>
       <c r="C79" s="35" t="s">
         <v>37</v>
       </c>
@@ -2362,8 +2391,8 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A80" s="39"/>
-      <c r="B80" s="36"/>
-      <c r="C80" s="36"/>
+      <c r="B80" s="37"/>
+      <c r="C80" s="37"/>
       <c r="D80" s="15" t="s">
         <v>65</v>
       </c>
@@ -2372,8 +2401,8 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A81" s="39"/>
-      <c r="B81" s="36"/>
-      <c r="C81" s="36"/>
+      <c r="B81" s="37"/>
+      <c r="C81" s="37"/>
       <c r="D81" s="15" t="s">
         <v>66</v>
       </c>
@@ -2382,8 +2411,8 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A82" s="39"/>
-      <c r="B82" s="36"/>
-      <c r="C82" s="36"/>
+      <c r="B82" s="37"/>
+      <c r="C82" s="37"/>
       <c r="D82" s="15" t="s">
         <v>67</v>
       </c>
@@ -2392,8 +2421,8 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A83" s="39"/>
-      <c r="B83" s="36"/>
-      <c r="C83" s="36"/>
+      <c r="B83" s="37"/>
+      <c r="C83" s="37"/>
       <c r="D83" s="15" t="s">
         <v>68</v>
       </c>
@@ -2402,8 +2431,8 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A84" s="39"/>
-      <c r="B84" s="36"/>
-      <c r="C84" s="36"/>
+      <c r="B84" s="37"/>
+      <c r="C84" s="37"/>
       <c r="D84" s="15" t="s">
         <v>69</v>
       </c>
@@ -2412,8 +2441,8 @@
     </row>
     <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A85" s="39"/>
-      <c r="B85" s="36"/>
-      <c r="C85" s="36"/>
+      <c r="B85" s="37"/>
+      <c r="C85" s="37"/>
       <c r="D85" s="15"/>
       <c r="E85" s="15"/>
       <c r="F85" s="16"/>
@@ -2434,8 +2463,8 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A87" s="39"/>
-      <c r="B87" s="36"/>
-      <c r="C87" s="36"/>
+      <c r="B87" s="37"/>
+      <c r="C87" s="37"/>
       <c r="D87" s="15" t="s">
         <v>100</v>
       </c>
@@ -2444,8 +2473,8 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A88" s="39"/>
-      <c r="B88" s="36"/>
-      <c r="C88" s="36"/>
+      <c r="B88" s="37"/>
+      <c r="C88" s="37"/>
       <c r="D88" s="15" t="s">
         <v>101</v>
       </c>
@@ -2454,31 +2483,31 @@
     </row>
     <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A89" s="39"/>
-      <c r="B89" s="36"/>
-      <c r="C89" s="36"/>
+      <c r="B89" s="37"/>
+      <c r="C89" s="37"/>
       <c r="D89" s="15"/>
       <c r="E89" s="15"/>
       <c r="F89" s="16"/>
     </row>
     <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A90" s="39"/>
-      <c r="B90" s="36"/>
-      <c r="C90" s="36"/>
+      <c r="B90" s="37"/>
+      <c r="C90" s="37"/>
       <c r="D90" s="15"/>
       <c r="E90" s="15"/>
       <c r="F90" s="16"/>
     </row>
     <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A91" s="39"/>
-      <c r="B91" s="36"/>
-      <c r="C91" s="37"/>
+      <c r="B91" s="37"/>
+      <c r="C91" s="36"/>
       <c r="D91" s="15"/>
       <c r="E91" s="15"/>
       <c r="F91" s="16"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A92" s="39"/>
-      <c r="B92" s="36"/>
+      <c r="B92" s="37"/>
       <c r="C92" s="35" t="s">
         <v>39</v>
       </c>
@@ -2490,8 +2519,8 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A93" s="39"/>
-      <c r="B93" s="36"/>
-      <c r="C93" s="36"/>
+      <c r="B93" s="37"/>
+      <c r="C93" s="37"/>
       <c r="D93" s="15" t="s">
         <v>75</v>
       </c>
@@ -2500,8 +2529,8 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A94" s="39"/>
-      <c r="B94" s="36"/>
-      <c r="C94" s="36"/>
+      <c r="B94" s="37"/>
+      <c r="C94" s="37"/>
       <c r="D94" s="15" t="s">
         <v>76</v>
       </c>
@@ -2510,31 +2539,31 @@
     </row>
     <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A95" s="39"/>
-      <c r="B95" s="36"/>
-      <c r="C95" s="36"/>
+      <c r="B95" s="37"/>
+      <c r="C95" s="37"/>
       <c r="D95" s="15"/>
       <c r="E95" s="15"/>
       <c r="F95" s="16"/>
     </row>
     <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A96" s="39"/>
-      <c r="B96" s="36"/>
-      <c r="C96" s="36"/>
+      <c r="B96" s="37"/>
+      <c r="C96" s="37"/>
       <c r="D96" s="15"/>
       <c r="E96" s="15"/>
       <c r="F96" s="16"/>
     </row>
     <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A97" s="39"/>
-      <c r="B97" s="36"/>
-      <c r="C97" s="37"/>
+      <c r="B97" s="37"/>
+      <c r="C97" s="36"/>
       <c r="D97" s="15"/>
       <c r="E97" s="15"/>
       <c r="F97" s="16"/>
     </row>
     <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="39"/>
-      <c r="B98" s="36"/>
+      <c r="B98" s="37"/>
       <c r="C98" s="35" t="s">
         <v>40</v>
       </c>
@@ -2546,8 +2575,8 @@
     </row>
     <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="39"/>
-      <c r="B99" s="36"/>
-      <c r="C99" s="36"/>
+      <c r="B99" s="37"/>
+      <c r="C99" s="37"/>
       <c r="D99" s="15" t="s">
         <v>104</v>
       </c>
@@ -2556,8 +2585,8 @@
     </row>
     <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="39"/>
-      <c r="B100" s="36"/>
-      <c r="C100" s="36"/>
+      <c r="B100" s="37"/>
+      <c r="C100" s="37"/>
       <c r="D100" s="15" t="s">
         <v>105</v>
       </c>
@@ -2566,8 +2595,8 @@
     </row>
     <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="39"/>
-      <c r="B101" s="36"/>
-      <c r="C101" s="36"/>
+      <c r="B101" s="37"/>
+      <c r="C101" s="37"/>
       <c r="D101" s="15" t="s">
         <v>106</v>
       </c>
@@ -2576,15 +2605,15 @@
     </row>
     <row r="102" spans="1:6" ht="15.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="39"/>
-      <c r="B102" s="36"/>
-      <c r="C102" s="37"/>
+      <c r="B102" s="37"/>
+      <c r="C102" s="36"/>
       <c r="D102" s="15"/>
       <c r="E102" s="15"/>
       <c r="F102" s="16"/>
     </row>
     <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="39"/>
-      <c r="B103" s="36"/>
+      <c r="B103" s="37"/>
       <c r="C103" s="35" t="s">
         <v>41</v>
       </c>
@@ -2596,8 +2625,8 @@
     </row>
     <row r="104" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="39"/>
-      <c r="B104" s="36"/>
-      <c r="C104" s="36"/>
+      <c r="B104" s="37"/>
+      <c r="C104" s="37"/>
       <c r="D104" s="15" t="s">
         <v>115</v>
       </c>
@@ -2606,23 +2635,23 @@
     </row>
     <row r="105" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="39"/>
-      <c r="B105" s="36"/>
-      <c r="C105" s="36"/>
+      <c r="B105" s="37"/>
+      <c r="C105" s="37"/>
       <c r="D105" s="15"/>
       <c r="E105" s="15"/>
       <c r="F105" s="16"/>
     </row>
     <row r="106" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="39"/>
-      <c r="B106" s="36"/>
-      <c r="C106" s="37"/>
+      <c r="B106" s="37"/>
+      <c r="C106" s="36"/>
       <c r="D106" s="15"/>
       <c r="E106" s="15"/>
       <c r="F106" s="16"/>
     </row>
     <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="39"/>
-      <c r="B107" s="36"/>
+      <c r="B107" s="37"/>
       <c r="C107" s="35" t="s">
         <v>42</v>
       </c>
@@ -2634,8 +2663,8 @@
     </row>
     <row r="108" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="39"/>
-      <c r="B108" s="36"/>
-      <c r="C108" s="36"/>
+      <c r="B108" s="37"/>
+      <c r="C108" s="37"/>
       <c r="D108" s="15" t="s">
         <v>124</v>
       </c>
@@ -2644,24 +2673,24 @@
     </row>
     <row r="109" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="39"/>
-      <c r="B109" s="36"/>
-      <c r="C109" s="36"/>
+      <c r="B109" s="37"/>
+      <c r="C109" s="37"/>
       <c r="D109" s="15"/>
       <c r="E109" s="15"/>
       <c r="F109" s="16"/>
     </row>
     <row r="110" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="39"/>
-      <c r="B110" s="36"/>
-      <c r="C110" s="36"/>
+      <c r="B110" s="37"/>
+      <c r="C110" s="37"/>
       <c r="D110" s="15"/>
       <c r="E110" s="15"/>
       <c r="F110" s="16"/>
     </row>
     <row r="111" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="39"/>
-      <c r="B111" s="37"/>
-      <c r="C111" s="37"/>
+      <c r="B111" s="36"/>
+      <c r="C111" s="36"/>
       <c r="D111" s="15"/>
       <c r="E111" s="15"/>
       <c r="F111" s="16"/>
@@ -2682,23 +2711,23 @@
     </row>
     <row r="113" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="39"/>
-      <c r="B113" s="36"/>
-      <c r="C113" s="36"/>
+      <c r="B113" s="37"/>
+      <c r="C113" s="37"/>
       <c r="D113" s="15"/>
       <c r="E113" s="15"/>
       <c r="F113" s="16"/>
     </row>
     <row r="114" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="39"/>
-      <c r="B114" s="36"/>
-      <c r="C114" s="37"/>
+      <c r="B114" s="37"/>
+      <c r="C114" s="36"/>
       <c r="D114" s="15"/>
       <c r="E114" s="15"/>
       <c r="F114" s="16"/>
     </row>
     <row r="115" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="39"/>
-      <c r="B115" s="36"/>
+      <c r="B115" s="37"/>
       <c r="C115" s="35" t="s">
         <v>44</v>
       </c>
@@ -2710,8 +2739,8 @@
     </row>
     <row r="116" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="39"/>
-      <c r="B116" s="37"/>
-      <c r="C116" s="37"/>
+      <c r="B116" s="36"/>
+      <c r="C116" s="36"/>
       <c r="D116" s="15"/>
       <c r="E116" s="15"/>
       <c r="F116" s="16"/>
@@ -2732,47 +2761,47 @@
     </row>
     <row r="118" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="39"/>
-      <c r="B118" s="36"/>
-      <c r="C118" s="36"/>
+      <c r="B118" s="37"/>
+      <c r="C118" s="37"/>
       <c r="D118" s="15"/>
       <c r="E118" s="15"/>
       <c r="F118" s="16"/>
     </row>
     <row r="119" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="39"/>
-      <c r="B119" s="36"/>
-      <c r="C119" s="36"/>
+      <c r="B119" s="37"/>
+      <c r="C119" s="37"/>
       <c r="D119" s="15"/>
       <c r="E119" s="15"/>
       <c r="F119" s="16"/>
     </row>
     <row r="120" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="39"/>
-      <c r="B120" s="36"/>
-      <c r="C120" s="36"/>
+      <c r="B120" s="37"/>
+      <c r="C120" s="37"/>
       <c r="D120" s="15"/>
       <c r="E120" s="15"/>
       <c r="F120" s="16"/>
     </row>
     <row r="121" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="39"/>
-      <c r="B121" s="36"/>
-      <c r="C121" s="36"/>
+      <c r="B121" s="37"/>
+      <c r="C121" s="37"/>
       <c r="D121" s="15"/>
       <c r="E121" s="15"/>
       <c r="F121" s="16"/>
     </row>
     <row r="122" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="39"/>
-      <c r="B122" s="36"/>
-      <c r="C122" s="37"/>
+      <c r="B122" s="37"/>
+      <c r="C122" s="36"/>
       <c r="D122" s="15"/>
       <c r="E122" s="15"/>
       <c r="F122" s="16"/>
     </row>
     <row r="123" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="39"/>
-      <c r="B123" s="36"/>
+      <c r="B123" s="37"/>
       <c r="C123" s="35" t="s">
         <v>46</v>
       </c>
@@ -2784,15 +2813,15 @@
     </row>
     <row r="124" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="39"/>
-      <c r="B124" s="36"/>
-      <c r="C124" s="36"/>
+      <c r="B124" s="37"/>
+      <c r="C124" s="37"/>
       <c r="D124" s="15"/>
       <c r="E124" s="15"/>
       <c r="F124" s="16"/>
     </row>
     <row r="125" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="39"/>
-      <c r="B125" s="36"/>
+      <c r="B125" s="37"/>
       <c r="C125" s="35" t="s">
         <v>47</v>
       </c>
@@ -2804,55 +2833,55 @@
     </row>
     <row r="126" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="39"/>
-      <c r="B126" s="36"/>
-      <c r="C126" s="36"/>
+      <c r="B126" s="37"/>
+      <c r="C126" s="37"/>
       <c r="D126" s="15"/>
       <c r="E126" s="15"/>
       <c r="F126" s="16"/>
     </row>
     <row r="127" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="39"/>
-      <c r="B127" s="36"/>
-      <c r="C127" s="36"/>
+      <c r="B127" s="37"/>
+      <c r="C127" s="37"/>
       <c r="D127" s="15"/>
       <c r="E127" s="15"/>
       <c r="F127" s="16"/>
     </row>
     <row r="128" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="39"/>
-      <c r="B128" s="36"/>
-      <c r="C128" s="36"/>
+      <c r="B128" s="37"/>
+      <c r="C128" s="37"/>
       <c r="D128" s="15"/>
       <c r="E128" s="15"/>
       <c r="F128" s="16"/>
     </row>
     <row r="129" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="39"/>
-      <c r="B129" s="36"/>
-      <c r="C129" s="36"/>
+      <c r="B129" s="37"/>
+      <c r="C129" s="37"/>
       <c r="D129" s="15"/>
       <c r="E129" s="15"/>
       <c r="F129" s="16"/>
     </row>
     <row r="130" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="39"/>
-      <c r="B130" s="36"/>
-      <c r="C130" s="36"/>
+      <c r="B130" s="37"/>
+      <c r="C130" s="37"/>
       <c r="D130" s="15"/>
       <c r="E130" s="15"/>
       <c r="F130" s="16"/>
     </row>
     <row r="131" spans="1:6" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="39"/>
-      <c r="B131" s="36"/>
-      <c r="C131" s="37"/>
+      <c r="B131" s="37"/>
+      <c r="C131" s="36"/>
       <c r="D131" s="15"/>
       <c r="E131" s="15"/>
       <c r="F131" s="16"/>
     </row>
     <row r="132" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="39"/>
-      <c r="B132" s="36"/>
+      <c r="B132" s="37"/>
       <c r="C132" s="35" t="s">
         <v>48</v>
       </c>
@@ -2864,23 +2893,23 @@
     </row>
     <row r="133" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A133" s="39"/>
-      <c r="B133" s="36"/>
-      <c r="C133" s="36"/>
+      <c r="B133" s="37"/>
+      <c r="C133" s="37"/>
       <c r="D133" s="15"/>
       <c r="E133" s="15"/>
       <c r="F133" s="16"/>
     </row>
     <row r="134" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A134" s="39"/>
-      <c r="B134" s="36"/>
-      <c r="C134" s="37"/>
+      <c r="B134" s="37"/>
+      <c r="C134" s="36"/>
       <c r="D134" s="15"/>
       <c r="E134" s="15"/>
       <c r="F134" s="16"/>
     </row>
     <row r="135" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A135" s="39"/>
-      <c r="B135" s="36"/>
+      <c r="B135" s="37"/>
       <c r="C135" s="35" t="s">
         <v>49</v>
       </c>
@@ -2892,8 +2921,8 @@
     </row>
     <row r="136" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A136" s="39"/>
-      <c r="B136" s="36"/>
-      <c r="C136" s="36"/>
+      <c r="B136" s="37"/>
+      <c r="C136" s="37"/>
       <c r="D136" s="15" t="s">
         <v>126</v>
       </c>
@@ -2902,8 +2931,8 @@
     </row>
     <row r="137" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A137" s="39"/>
-      <c r="B137" s="36"/>
-      <c r="C137" s="36"/>
+      <c r="B137" s="37"/>
+      <c r="C137" s="37"/>
       <c r="D137" s="15" t="s">
         <v>127</v>
       </c>
@@ -2912,16 +2941,16 @@
     </row>
     <row r="138" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A138" s="39"/>
-      <c r="B138" s="36"/>
-      <c r="C138" s="36"/>
+      <c r="B138" s="37"/>
+      <c r="C138" s="37"/>
       <c r="D138" s="15"/>
       <c r="E138" s="15"/>
       <c r="F138" s="16"/>
     </row>
     <row r="139" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A139" s="39"/>
-      <c r="B139" s="36"/>
-      <c r="C139" s="36"/>
+      <c r="B139" s="37"/>
+      <c r="C139" s="37"/>
       <c r="D139" s="15"/>
       <c r="E139" s="15"/>
       <c r="F139" s="16"/>
@@ -2942,8 +2971,8 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A141" s="39"/>
-      <c r="B141" s="36"/>
-      <c r="C141" s="36"/>
+      <c r="B141" s="37"/>
+      <c r="C141" s="37"/>
       <c r="D141" s="15" t="s">
         <v>71</v>
       </c>
@@ -2952,8 +2981,8 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A142" s="39"/>
-      <c r="B142" s="36"/>
-      <c r="C142" s="36"/>
+      <c r="B142" s="37"/>
+      <c r="C142" s="37"/>
       <c r="D142" s="15" t="s">
         <v>83</v>
       </c>
@@ -2962,7 +2991,7 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A143" s="39"/>
-      <c r="B143" s="36"/>
+      <c r="B143" s="37"/>
       <c r="C143" s="35" t="s">
         <v>51</v>
       </c>
@@ -2974,8 +3003,8 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A144" s="39"/>
-      <c r="B144" s="36"/>
-      <c r="C144" s="36"/>
+      <c r="B144" s="37"/>
+      <c r="C144" s="37"/>
       <c r="D144" s="15" t="s">
         <v>117</v>
       </c>
@@ -2984,8 +3013,8 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A145" s="39"/>
-      <c r="B145" s="36"/>
-      <c r="C145" s="36"/>
+      <c r="B145" s="37"/>
+      <c r="C145" s="37"/>
       <c r="D145" s="15" t="s">
         <v>118</v>
       </c>
@@ -2994,8 +3023,8 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A146" s="39"/>
-      <c r="B146" s="36"/>
-      <c r="C146" s="36"/>
+      <c r="B146" s="37"/>
+      <c r="C146" s="37"/>
       <c r="D146" s="15" t="s">
         <v>119</v>
       </c>
@@ -3004,7 +3033,7 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A147" s="39"/>
-      <c r="B147" s="36"/>
+      <c r="B147" s="37"/>
       <c r="C147" s="35" t="s">
         <v>52</v>
       </c>
@@ -3016,31 +3045,31 @@
     </row>
     <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A148" s="39"/>
-      <c r="B148" s="36"/>
-      <c r="C148" s="36"/>
+      <c r="B148" s="37"/>
+      <c r="C148" s="37"/>
       <c r="D148" s="15"/>
       <c r="E148" s="15"/>
       <c r="F148" s="16"/>
     </row>
     <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A149" s="39"/>
-      <c r="B149" s="36"/>
-      <c r="C149" s="36"/>
+      <c r="B149" s="37"/>
+      <c r="C149" s="37"/>
       <c r="D149" s="15"/>
       <c r="E149" s="15"/>
       <c r="F149" s="16"/>
     </row>
     <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A150" s="39"/>
-      <c r="B150" s="36"/>
-      <c r="C150" s="36"/>
+      <c r="B150" s="37"/>
+      <c r="C150" s="37"/>
       <c r="D150" s="15"/>
       <c r="E150" s="15"/>
       <c r="F150" s="16"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A151" s="39"/>
-      <c r="B151" s="36"/>
+      <c r="B151" s="37"/>
       <c r="C151" s="35" t="s">
         <v>53</v>
       </c>
@@ -3052,32 +3081,32 @@
     </row>
     <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A152" s="39"/>
-      <c r="B152" s="36"/>
-      <c r="C152" s="36"/>
+      <c r="B152" s="37"/>
+      <c r="C152" s="37"/>
       <c r="D152" s="15"/>
       <c r="E152" s="15"/>
       <c r="F152" s="16"/>
     </row>
     <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A153" s="39"/>
-      <c r="B153" s="36"/>
-      <c r="C153" s="36"/>
+      <c r="B153" s="37"/>
+      <c r="C153" s="37"/>
       <c r="D153" s="15"/>
       <c r="E153" s="15"/>
       <c r="F153" s="16"/>
     </row>
     <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A154" s="39"/>
-      <c r="B154" s="36"/>
-      <c r="C154" s="36"/>
+      <c r="B154" s="37"/>
+      <c r="C154" s="37"/>
       <c r="D154" s="15"/>
       <c r="E154" s="15"/>
       <c r="F154" s="16"/>
     </row>
     <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A155" s="39"/>
-      <c r="B155" s="36"/>
-      <c r="C155" s="36"/>
+      <c r="B155" s="37"/>
+      <c r="C155" s="37"/>
       <c r="D155" s="15"/>
       <c r="E155" s="15"/>
       <c r="F155" s="16"/>
@@ -3098,8 +3127,8 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A157" s="39"/>
-      <c r="B157" s="36"/>
-      <c r="C157" s="37"/>
+      <c r="B157" s="37"/>
+      <c r="C157" s="36"/>
       <c r="D157" s="15" t="s">
         <v>93</v>
       </c>
@@ -3108,7 +3137,7 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A158" s="39"/>
-      <c r="B158" s="36"/>
+      <c r="B158" s="37"/>
       <c r="C158" s="35" t="s">
         <v>55</v>
       </c>
@@ -3120,8 +3149,8 @@
     </row>
     <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.45">
       <c r="A159" s="39"/>
-      <c r="B159" s="37"/>
-      <c r="C159" s="37"/>
+      <c r="B159" s="36"/>
+      <c r="C159" s="36"/>
       <c r="D159" s="15"/>
       <c r="E159" s="15"/>
       <c r="F159" s="16"/>
@@ -3192,34 +3221,12 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="50">
-    <mergeCell ref="C156:C157"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="C74:C78"/>
-    <mergeCell ref="C65:C69"/>
-    <mergeCell ref="C60:C64"/>
-    <mergeCell ref="C125:C131"/>
-    <mergeCell ref="C132:C134"/>
-    <mergeCell ref="C135:C139"/>
-    <mergeCell ref="C123:C124"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="C25:C28"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="C44:C47"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="C29:C37"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C16:C20"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="B74:B85"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="B38:B73"/>
-    <mergeCell ref="C79:C85"/>
-    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="B112:B116"/>
+    <mergeCell ref="C107:C111"/>
+    <mergeCell ref="C103:C106"/>
+    <mergeCell ref="C98:C102"/>
+    <mergeCell ref="B86:B111"/>
+    <mergeCell ref="C92:C97"/>
     <mergeCell ref="B140:B155"/>
     <mergeCell ref="A5:A163"/>
     <mergeCell ref="B5:B12"/>
@@ -3236,12 +3243,34 @@
     <mergeCell ref="C143:C146"/>
     <mergeCell ref="C86:C91"/>
     <mergeCell ref="B117:B139"/>
-    <mergeCell ref="B112:B116"/>
-    <mergeCell ref="C107:C111"/>
-    <mergeCell ref="C103:C106"/>
-    <mergeCell ref="C98:C102"/>
-    <mergeCell ref="B86:B111"/>
-    <mergeCell ref="C92:C97"/>
+    <mergeCell ref="B74:B85"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="B38:B73"/>
+    <mergeCell ref="C79:C85"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="C44:C47"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="C29:C37"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C16:C20"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C156:C157"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="C74:C78"/>
+    <mergeCell ref="C65:C69"/>
+    <mergeCell ref="C60:C64"/>
+    <mergeCell ref="C125:C131"/>
+    <mergeCell ref="C132:C134"/>
+    <mergeCell ref="C135:C139"/>
+    <mergeCell ref="C123:C124"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3251,10 +3280,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C70A9B08-4A20-445F-A3D8-4985C4AC9A61}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:I162"/>
+  <dimension ref="A1:I157"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="21.25" customWidth="1"/>
@@ -3325,7 +3354,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="39"/>
-      <c r="B6" s="36"/>
+      <c r="B6" s="37"/>
       <c r="C6" s="13" t="s">
         <v>130</v>
       </c>
@@ -3340,7 +3369,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="39"/>
-      <c r="B7" s="36"/>
+      <c r="B7" s="37"/>
       <c r="C7" s="13" t="s">
         <v>7</v>
       </c>
@@ -3355,7 +3384,7 @@
     </row>
     <row r="8" spans="1:8" ht="34" x14ac:dyDescent="0.45">
       <c r="A8" s="39"/>
-      <c r="B8" s="36"/>
+      <c r="B8" s="37"/>
       <c r="C8" s="35" t="s">
         <v>191</v>
       </c>
@@ -3370,10 +3399,10 @@
         <v>139</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A9" s="39"/>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
       <c r="F9" s="15"/>
@@ -3381,7 +3410,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="39"/>
-      <c r="B10" s="36"/>
+      <c r="B10" s="37"/>
       <c r="C10" s="35" t="s">
         <v>192</v>
       </c>
@@ -3392,10 +3421,10 @@
       <c r="F10" s="24"/>
       <c r="G10" s="19"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A11" s="39"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="37"/>
       <c r="D11" s="17"/>
       <c r="E11" s="17"/>
       <c r="F11" s="17"/>
@@ -3420,7 +3449,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="39"/>
-      <c r="B13" s="36"/>
+      <c r="B13" s="37"/>
       <c r="C13" s="35" t="s">
         <v>11</v>
       </c>
@@ -3435,8 +3464,8 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="39"/>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
       <c r="D14" s="18" t="s">
         <v>60</v>
       </c>
@@ -3444,10 +3473,10 @@
       <c r="F14" s="25"/>
       <c r="G14" s="19"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15" s="39"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="37"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="36"/>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
       <c r="F15" s="18"/>
@@ -3455,7 +3484,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="39"/>
-      <c r="B16" s="36"/>
+      <c r="B16" s="37"/>
       <c r="C16" s="13" t="s">
         <v>12</v>
       </c>
@@ -3470,7 +3499,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="39"/>
-      <c r="B17" s="36"/>
+      <c r="B17" s="37"/>
       <c r="C17" s="13" t="s">
         <v>13</v>
       </c>
@@ -3483,9 +3512,9 @@
       </c>
       <c r="G17" s="19"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18" s="39"/>
-      <c r="B18" s="36"/>
+      <c r="B18" s="37"/>
       <c r="C18" s="35" t="s">
         <v>14</v>
       </c>
@@ -3494,28 +3523,28 @@
       <c r="F18" s="15"/>
       <c r="G18" s="19"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19" s="39"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="37"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="15"/>
       <c r="G19" s="19"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A20" s="39"/>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="37"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="15"/>
       <c r="G20" s="19"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A21" s="39"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="37"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="36"/>
       <c r="D21" s="19"/>
       <c r="E21" s="19"/>
       <c r="F21" s="19"/>
@@ -3523,7 +3552,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="39"/>
-      <c r="B22" s="36"/>
+      <c r="B22" s="37"/>
       <c r="C22" s="35" t="s">
         <v>15</v>
       </c>
@@ -3538,8 +3567,8 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="39"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
       <c r="D23" s="20" t="s">
         <v>98</v>
       </c>
@@ -3547,10 +3576,10 @@
       <c r="F23" s="14"/>
       <c r="G23" s="19"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A24" s="39"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="37"/>
       <c r="D24" s="21"/>
       <c r="E24" s="21"/>
       <c r="F24" s="21"/>
@@ -3558,73 +3587,85 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="39"/>
-      <c r="B25" s="37"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
+      <c r="B25" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26" t="s">
+        <v>224</v>
+      </c>
       <c r="G25" s="19"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="39"/>
-      <c r="B26" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" s="35" t="s">
-        <v>24</v>
-      </c>
+      <c r="B26" s="37"/>
+      <c r="C26" s="37"/>
       <c r="D26" s="21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
+      <c r="F26" s="26" t="s">
+        <v>224</v>
+      </c>
       <c r="G26" s="19"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27" s="39"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
       <c r="G27" s="19"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="39"/>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26" t="s">
+        <v>224</v>
+      </c>
       <c r="G28" s="19"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A29" s="39"/>
-      <c r="B29" s="36"/>
-      <c r="C29" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
+      <c r="B29" s="37"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
       <c r="G29" s="19"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A30" s="39"/>
-      <c r="B30" s="36"/>
-      <c r="C30" s="36"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="35" t="s">
+        <v>26</v>
+      </c>
       <c r="D30" s="21"/>
       <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="19"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F30" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31" s="39"/>
-      <c r="B31" s="36"/>
+      <c r="B31" s="37"/>
       <c r="C31" s="37"/>
       <c r="D31" s="21"/>
       <c r="E31" s="21"/>
@@ -3633,18 +3674,22 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="39"/>
-      <c r="B32" s="36"/>
+      <c r="B32" s="37"/>
       <c r="C32" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
+        <v>27</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26" t="s">
+        <v>224</v>
+      </c>
       <c r="G32" s="19"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A33" s="39"/>
-      <c r="B33" s="36"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="36"/>
       <c r="D33" s="21"/>
       <c r="E33" s="21"/>
@@ -3653,142 +3698,164 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="39"/>
-      <c r="B34" s="36"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34" s="26"/>
+      <c r="F34" s="16" t="s">
+        <v>222</v>
+      </c>
       <c r="G34" s="19"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="39"/>
-      <c r="B35" s="36"/>
+      <c r="B35" s="37"/>
       <c r="C35" s="37"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
+      <c r="D35" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="E35" s="26"/>
+      <c r="F35" s="16" t="s">
+        <v>222</v>
+      </c>
       <c r="G35" s="19"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" s="39"/>
-      <c r="B36" s="36"/>
+      <c r="B36" s="37"/>
       <c r="C36" s="35" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E36" s="26"/>
-      <c r="F36" s="26"/>
+      <c r="F36" s="26" t="s">
+        <v>223</v>
+      </c>
       <c r="G36" s="19"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" s="39"/>
-      <c r="B37" s="36"/>
+      <c r="B37" s="37"/>
       <c r="C37" s="37"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
+      <c r="D37" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26" t="s">
+        <v>223</v>
+      </c>
       <c r="G37" s="19"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" s="39"/>
-      <c r="B38" s="36"/>
-      <c r="C38" s="35" t="s">
-        <v>28</v>
-      </c>
+      <c r="B38" s="37"/>
+      <c r="C38" s="36"/>
       <c r="D38" s="21" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
+      <c r="F38" s="26" t="s">
+        <v>223</v>
+      </c>
       <c r="G38" s="19"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" s="39"/>
-      <c r="B39" s="36"/>
-      <c r="C39" s="36"/>
+      <c r="B39" s="37"/>
+      <c r="C39" s="35" t="s">
+        <v>30</v>
+      </c>
       <c r="D39" s="21" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
+      <c r="F39" s="26" t="s">
+        <v>224</v>
+      </c>
       <c r="G39" s="19"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" s="39"/>
-      <c r="B40" s="36"/>
-      <c r="C40" s="35" t="s">
-        <v>29</v>
-      </c>
+      <c r="B40" s="37"/>
+      <c r="C40" s="37"/>
       <c r="D40" s="21" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
+      <c r="F40" s="26" t="s">
+        <v>224</v>
+      </c>
       <c r="G40" s="19"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A41" s="39"/>
-      <c r="B41" s="36"/>
+      <c r="B41" s="37"/>
       <c r="C41" s="36"/>
-      <c r="D41" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
       <c r="G41" s="19"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A42" s="39"/>
-      <c r="B42" s="36"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="16" t="s">
+        <v>222</v>
+      </c>
       <c r="G42" s="19"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43" s="39"/>
-      <c r="B43" s="36"/>
-      <c r="C43" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="D43" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="E43" s="26"/>
-      <c r="F43" s="26"/>
+      <c r="B43" s="37"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
       <c r="G43" s="19"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" s="39"/>
-      <c r="B44" s="36"/>
-      <c r="C44" s="36"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="35" t="s">
+        <v>32</v>
+      </c>
       <c r="D44" s="21" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E44" s="26"/>
-      <c r="F44" s="26"/>
+      <c r="F44" s="16" t="s">
+        <v>222</v>
+      </c>
       <c r="G44" s="19"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" s="39"/>
-      <c r="B45" s="36"/>
+      <c r="B45" s="37"/>
       <c r="C45" s="37"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="21"/>
+      <c r="D45" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E45" s="26"/>
+      <c r="F45" s="16" t="s">
+        <v>222</v>
+      </c>
       <c r="G45" s="19"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A46" s="39"/>
-      <c r="B46" s="36"/>
-      <c r="C46" s="35" t="s">
-        <v>31</v>
-      </c>
+      <c r="B46" s="37"/>
+      <c r="C46" s="37"/>
       <c r="D46" s="21"/>
       <c r="E46" s="21"/>
       <c r="F46" s="21"/>
@@ -3796,40 +3863,46 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" s="39"/>
-      <c r="B47" s="36"/>
-      <c r="C47" s="36"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
+      <c r="B47" s="37"/>
+      <c r="C47" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="D47" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26" t="s">
+        <v>224</v>
+      </c>
       <c r="G47" s="19"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A48" s="39"/>
-      <c r="B48" s="36"/>
-      <c r="C48" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="D48" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="E48" s="26"/>
-      <c r="F48" s="26"/>
+      <c r="B48" s="37"/>
+      <c r="C48" s="37"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="21"/>
+      <c r="F48" s="21"/>
       <c r="G48" s="19"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" s="39"/>
-      <c r="B49" s="36"/>
-      <c r="C49" s="36"/>
+      <c r="B49" s="37"/>
+      <c r="C49" s="35" t="s">
+        <v>34</v>
+      </c>
       <c r="D49" s="21" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="E49" s="26"/>
-      <c r="F49" s="26"/>
+      <c r="F49" s="26" t="s">
+        <v>224</v>
+      </c>
       <c r="G49" s="19"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A50" s="39"/>
-      <c r="B50" s="36"/>
+      <c r="B50" s="37"/>
       <c r="C50" s="36"/>
       <c r="D50" s="21"/>
       <c r="E50" s="21"/>
@@ -3838,91 +3911,105 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" s="39"/>
-      <c r="B51" s="36"/>
+      <c r="B51" s="37"/>
       <c r="C51" s="35" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E51" s="26"/>
-      <c r="F51" s="26"/>
+      <c r="F51" s="26" t="s">
+        <v>224</v>
+      </c>
       <c r="G51" s="19"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" s="39"/>
       <c r="B52" s="36"/>
-      <c r="C52" s="36"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21"/>
+      <c r="C52" s="37"/>
+      <c r="D52" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="E52" s="26"/>
+      <c r="F52" s="26" t="s">
+        <v>223</v>
+      </c>
       <c r="G52" s="19"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" s="39"/>
-      <c r="B53" s="36"/>
-      <c r="C53" s="36"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="21"/>
+      <c r="B53" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E53" s="23"/>
+      <c r="F53" s="16" t="s">
+        <v>135</v>
+      </c>
       <c r="G53" s="19"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A54" s="39"/>
-      <c r="B54" s="36"/>
-      <c r="C54" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="D54" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="E54" s="26"/>
-      <c r="F54" s="26"/>
+      <c r="B54" s="37"/>
+      <c r="C54" s="37"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="16"/>
       <c r="G54" s="19"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" s="39"/>
-      <c r="B55" s="36"/>
-      <c r="C55" s="37"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
+      <c r="B55" s="37"/>
+      <c r="C55" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E55" s="23"/>
+      <c r="F55" s="16" t="s">
+        <v>135</v>
+      </c>
       <c r="G55" s="19"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" s="39"/>
-      <c r="B56" s="36"/>
-      <c r="C56" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="D56" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="E56" s="26"/>
-      <c r="F56" s="26"/>
+      <c r="B56" s="37"/>
+      <c r="C56" s="37"/>
+      <c r="D56" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E56" s="23"/>
+      <c r="F56" s="16" t="s">
+        <v>135</v>
+      </c>
       <c r="G56" s="19"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" s="39"/>
       <c r="B57" s="37"/>
-      <c r="C57" s="36"/>
-      <c r="D57" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="E57" s="26"/>
-      <c r="F57" s="26"/>
+      <c r="C57" s="37"/>
+      <c r="D57" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E57" s="23"/>
+      <c r="F57" s="16" t="s">
+        <v>135</v>
+      </c>
       <c r="G57" s="19"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" s="39"/>
-      <c r="B58" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="C58" s="35" t="s">
-        <v>36</v>
-      </c>
+      <c r="B58" s="37"/>
+      <c r="C58" s="37"/>
       <c r="D58" s="15" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="E58" s="23"/>
       <c r="F58" s="16" t="s">
@@ -3932,21 +4019,23 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" s="39"/>
-      <c r="B59" s="36"/>
-      <c r="C59" s="36"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="16"/>
+      <c r="B59" s="37"/>
+      <c r="C59" s="37"/>
+      <c r="D59" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E59" s="23"/>
+      <c r="F59" s="16" t="s">
+        <v>135</v>
+      </c>
       <c r="G59" s="19"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" s="39"/>
-      <c r="B60" s="36"/>
-      <c r="C60" s="35" t="s">
-        <v>37</v>
-      </c>
+      <c r="B60" s="37"/>
+      <c r="C60" s="37"/>
       <c r="D60" s="15" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E60" s="23"/>
       <c r="F60" s="16" t="s">
@@ -3956,10 +4045,14 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" s="39"/>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
+      <c r="B61" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="D61" s="15" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="E61" s="23"/>
       <c r="F61" s="16" t="s">
@@ -3969,10 +4062,10 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" s="39"/>
-      <c r="B62" s="36"/>
-      <c r="C62" s="36"/>
+      <c r="B62" s="37"/>
+      <c r="C62" s="37"/>
       <c r="D62" s="15" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="E62" s="23"/>
       <c r="F62" s="16" t="s">
@@ -3982,10 +4075,10 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" s="39"/>
-      <c r="B63" s="36"/>
-      <c r="C63" s="36"/>
+      <c r="B63" s="37"/>
+      <c r="C63" s="37"/>
       <c r="D63" s="15" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="E63" s="23"/>
       <c r="F63" s="16" t="s">
@@ -3995,10 +4088,12 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" s="39"/>
-      <c r="B64" s="36"/>
-      <c r="C64" s="36"/>
+      <c r="B64" s="37"/>
+      <c r="C64" s="35" t="s">
+        <v>39</v>
+      </c>
       <c r="D64" s="15" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E64" s="23"/>
       <c r="F64" s="16" t="s">
@@ -4008,10 +4103,10 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A65" s="39"/>
-      <c r="B65" s="36"/>
-      <c r="C65" s="36"/>
+      <c r="B65" s="37"/>
+      <c r="C65" s="37"/>
       <c r="D65" s="15" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E65" s="23"/>
       <c r="F65" s="16" t="s">
@@ -4021,14 +4116,10 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A66" s="39"/>
-      <c r="B66" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="C66" s="35" t="s">
-        <v>38</v>
-      </c>
+      <c r="B66" s="37"/>
+      <c r="C66" s="37"/>
       <c r="D66" s="15" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="E66" s="23"/>
       <c r="F66" s="16" t="s">
@@ -4036,81 +4127,81 @@
       </c>
       <c r="G66" s="19"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="39"/>
-      <c r="B67" s="36"/>
-      <c r="C67" s="36"/>
+      <c r="B67" s="37"/>
+      <c r="C67" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="D67" s="15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E67" s="23"/>
       <c r="F67" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G67" s="19"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="39"/>
-      <c r="B68" s="36"/>
-      <c r="C68" s="36"/>
+      <c r="B68" s="37"/>
+      <c r="C68" s="37"/>
       <c r="D68" s="15" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E68" s="23"/>
       <c r="F68" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G68" s="19"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="39"/>
-      <c r="B69" s="36"/>
-      <c r="C69" s="35" t="s">
-        <v>39</v>
-      </c>
+      <c r="B69" s="37"/>
+      <c r="C69" s="37"/>
       <c r="D69" s="15" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="E69" s="23"/>
       <c r="F69" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G69" s="19"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="39"/>
-      <c r="B70" s="36"/>
-      <c r="C70" s="36"/>
+      <c r="B70" s="37"/>
+      <c r="C70" s="37"/>
       <c r="D70" s="15" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E70" s="23"/>
       <c r="F70" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G70" s="19"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="39"/>
-      <c r="B71" s="36"/>
-      <c r="C71" s="36"/>
+      <c r="B71" s="37"/>
+      <c r="C71" s="35" t="s">
+        <v>41</v>
+      </c>
       <c r="D71" s="15" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="E71" s="23"/>
       <c r="F71" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G71" s="19"/>
     </row>
     <row r="72" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="39"/>
-      <c r="B72" s="36"/>
-      <c r="C72" s="35" t="s">
-        <v>40</v>
-      </c>
+      <c r="B72" s="37"/>
+      <c r="C72" s="37"/>
       <c r="D72" s="15" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E72" s="23"/>
       <c r="F72" s="16" t="s">
@@ -4120,10 +4211,12 @@
     </row>
     <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="39"/>
-      <c r="B73" s="36"/>
-      <c r="C73" s="36"/>
+      <c r="B73" s="37"/>
+      <c r="C73" s="35" t="s">
+        <v>42</v>
+      </c>
       <c r="D73" s="15" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="E73" s="23"/>
       <c r="F73" s="16" t="s">
@@ -4133,10 +4226,10 @@
     </row>
     <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="39"/>
-      <c r="B74" s="36"/>
-      <c r="C74" s="36"/>
+      <c r="B74" s="37"/>
+      <c r="C74" s="37"/>
       <c r="D74" s="15" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="E74" s="23"/>
       <c r="F74" s="16" t="s">
@@ -4144,94 +4237,86 @@
       </c>
       <c r="G74" s="19"/>
     </row>
-    <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="39"/>
-      <c r="B75" s="36"/>
-      <c r="C75" s="36"/>
-      <c r="D75" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E75" s="23"/>
-      <c r="F75" s="16" t="s">
-        <v>136</v>
+      <c r="B75" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="C75" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="D75" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="E75" s="26"/>
+      <c r="F75" s="26" t="s">
+        <v>226</v>
       </c>
       <c r="G75" s="19"/>
     </row>
-    <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="39"/>
-      <c r="B76" s="36"/>
-      <c r="C76" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D76" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="E76" s="23"/>
-      <c r="F76" s="16" t="s">
-        <v>136</v>
-      </c>
+      <c r="B76" s="37"/>
+      <c r="C76" s="36"/>
+      <c r="D76" s="15"/>
+      <c r="E76" s="15"/>
+      <c r="F76" s="15"/>
       <c r="G76" s="19"/>
     </row>
     <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="39"/>
-      <c r="B77" s="36"/>
-      <c r="C77" s="36"/>
+      <c r="B77" s="37"/>
+      <c r="C77" s="35" t="s">
+        <v>44</v>
+      </c>
       <c r="D77" s="15" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E77" s="23"/>
-      <c r="F77" s="16" t="s">
-        <v>136</v>
+      <c r="F77" s="23" t="s">
+        <v>226</v>
       </c>
       <c r="G77" s="19"/>
     </row>
-    <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="39"/>
       <c r="B78" s="36"/>
-      <c r="C78" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="D78" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="E78" s="23"/>
-      <c r="F78" s="16" t="s">
-        <v>136</v>
-      </c>
+      <c r="C78" s="36"/>
+      <c r="D78" s="15"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="15"/>
       <c r="G78" s="19"/>
     </row>
     <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="39"/>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
+      <c r="B79" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C79" s="35" t="s">
+        <v>45</v>
+      </c>
       <c r="D79" s="15" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="E79" s="23"/>
-      <c r="F79" s="16" t="s">
-        <v>136</v>
+      <c r="F79" s="23" t="s">
+        <v>226</v>
       </c>
       <c r="G79" s="19"/>
     </row>
-    <row r="80" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="39"/>
-      <c r="B80" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="C80" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="D80" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="E80" s="26"/>
-      <c r="F80" s="26"/>
+      <c r="B80" s="37"/>
+      <c r="C80" s="37"/>
+      <c r="D80" s="15"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="15"/>
       <c r="G80" s="19"/>
     </row>
-    <row r="81" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="39"/>
-      <c r="B81" s="36"/>
-      <c r="C81" s="37"/>
+      <c r="B81" s="37"/>
+      <c r="C81" s="36"/>
       <c r="D81" s="15"/>
       <c r="E81" s="15"/>
       <c r="F81" s="15"/>
@@ -4239,18 +4324,18 @@
     </row>
     <row r="82" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="39"/>
-      <c r="B82" s="36"/>
+      <c r="B82" s="37"/>
       <c r="C82" s="35" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="E82" s="23"/>
       <c r="F82" s="23"/>
       <c r="G82" s="19"/>
     </row>
-    <row r="83" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="39"/>
       <c r="B83" s="37"/>
       <c r="C83" s="37"/>
@@ -4261,23 +4346,23 @@
     </row>
     <row r="84" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="39"/>
-      <c r="B84" s="35" t="s">
-        <v>20</v>
-      </c>
+      <c r="B84" s="37"/>
       <c r="C84" s="35" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E84" s="23"/>
-      <c r="F84" s="23"/>
+      <c r="F84" s="23" t="s">
+        <v>226</v>
+      </c>
       <c r="G84" s="19"/>
     </row>
-    <row r="85" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="39"/>
-      <c r="B85" s="36"/>
-      <c r="C85" s="36"/>
+      <c r="B85" s="37"/>
+      <c r="C85" s="37"/>
       <c r="D85" s="15"/>
       <c r="E85" s="15"/>
       <c r="F85" s="15"/>
@@ -4285,142 +4370,160 @@
     </row>
     <row r="86" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="39"/>
-      <c r="B86" s="36"/>
-      <c r="C86" s="37"/>
-      <c r="D86" s="15"/>
-      <c r="E86" s="15"/>
-      <c r="F86" s="15"/>
+      <c r="B86" s="37"/>
+      <c r="C86" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="D86" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E86" s="23"/>
+      <c r="F86" s="23" t="s">
+        <v>226</v>
+      </c>
       <c r="G86" s="19"/>
     </row>
-    <row r="87" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="39"/>
-      <c r="B87" s="36"/>
-      <c r="C87" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="D87" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="E87" s="23"/>
-      <c r="F87" s="23"/>
+      <c r="B87" s="37"/>
+      <c r="C87" s="37"/>
+      <c r="D87" s="15"/>
+      <c r="E87" s="15"/>
+      <c r="F87" s="15"/>
       <c r="G87" s="19"/>
     </row>
     <row r="88" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="39"/>
-      <c r="B88" s="36"/>
-      <c r="C88" s="36"/>
-      <c r="D88" s="15"/>
-      <c r="E88" s="15"/>
-      <c r="F88" s="15"/>
+      <c r="B88" s="37"/>
+      <c r="C88" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="D88" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E88" s="23"/>
+      <c r="F88" s="23" t="s">
+        <v>226</v>
+      </c>
       <c r="G88" s="19"/>
     </row>
     <row r="89" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="39"/>
-      <c r="B89" s="36"/>
-      <c r="C89" s="35" t="s">
-        <v>47</v>
-      </c>
+      <c r="B89" s="37"/>
+      <c r="C89" s="37"/>
       <c r="D89" s="15" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="E89" s="23"/>
-      <c r="F89" s="23"/>
+      <c r="F89" s="23" t="s">
+        <v>225</v>
+      </c>
       <c r="G89" s="19"/>
     </row>
     <row r="90" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="39"/>
-      <c r="B90" s="36"/>
-      <c r="C90" s="36"/>
-      <c r="D90" s="15"/>
-      <c r="E90" s="15"/>
-      <c r="F90" s="15"/>
+      <c r="B90" s="37"/>
+      <c r="C90" s="37"/>
+      <c r="D90" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E90" s="23"/>
+      <c r="F90" s="23" t="s">
+        <v>225</v>
+      </c>
       <c r="G90" s="19"/>
     </row>
-    <row r="91" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="39"/>
-      <c r="B91" s="36"/>
-      <c r="C91" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="D91" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="E91" s="23"/>
-      <c r="F91" s="23"/>
+      <c r="B91" s="37"/>
+      <c r="C91" s="37"/>
+      <c r="D91" s="15"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="15"/>
       <c r="G91" s="19"/>
     </row>
-    <row r="92" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="39"/>
-      <c r="B92" s="36"/>
-      <c r="C92" s="36"/>
+      <c r="B92" s="37"/>
+      <c r="C92" s="37"/>
       <c r="D92" s="15"/>
       <c r="E92" s="15"/>
       <c r="F92" s="15"/>
       <c r="G92" s="19"/>
     </row>
-    <row r="93" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A93" s="39"/>
-      <c r="B93" s="36"/>
+      <c r="B93" s="35" t="s">
+        <v>21</v>
+      </c>
       <c r="C93" s="35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D93" s="15" t="s">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="E93" s="23"/>
-      <c r="F93" s="23"/>
+      <c r="F93" s="23" t="s">
+        <v>227</v>
+      </c>
       <c r="G93" s="19"/>
     </row>
-    <row r="94" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A94" s="39"/>
-      <c r="B94" s="36"/>
-      <c r="C94" s="36"/>
+      <c r="B94" s="37"/>
+      <c r="C94" s="37"/>
       <c r="D94" s="15" t="s">
-        <v>126</v>
+        <v>71</v>
       </c>
       <c r="E94" s="23"/>
-      <c r="F94" s="23"/>
+      <c r="F94" s="23" t="s">
+        <v>221</v>
+      </c>
       <c r="G94" s="19"/>
     </row>
-    <row r="95" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A95" s="39"/>
-      <c r="B95" s="36"/>
-      <c r="C95" s="36"/>
+      <c r="B95" s="37"/>
+      <c r="C95" s="37"/>
       <c r="D95" s="15" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="E95" s="23"/>
-      <c r="F95" s="23"/>
+      <c r="F95" s="23" t="s">
+        <v>221</v>
+      </c>
       <c r="G95" s="19"/>
     </row>
-    <row r="96" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A96" s="39"/>
-      <c r="B96" s="36"/>
-      <c r="C96" s="36"/>
-      <c r="D96" s="15"/>
-      <c r="E96" s="15"/>
-      <c r="F96" s="15"/>
+      <c r="B96" s="37"/>
+      <c r="C96" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="D96" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E96" s="23"/>
+      <c r="F96" s="23"/>
       <c r="G96" s="19"/>
     </row>
-    <row r="97" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A97" s="39"/>
-      <c r="B97" s="36"/>
-      <c r="C97" s="36"/>
-      <c r="D97" s="15"/>
-      <c r="E97" s="15"/>
-      <c r="F97" s="15"/>
+      <c r="B97" s="37"/>
+      <c r="C97" s="37"/>
+      <c r="D97" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="E97" s="23"/>
+      <c r="F97" s="23"/>
       <c r="G97" s="19"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A98" s="39"/>
-      <c r="B98" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="C98" s="35" t="s">
-        <v>50</v>
-      </c>
+      <c r="B98" s="37"/>
+      <c r="C98" s="37"/>
       <c r="D98" s="15" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="E98" s="23"/>
       <c r="F98" s="23"/>
@@ -4428,10 +4531,10 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A99" s="39"/>
-      <c r="B99" s="36"/>
-      <c r="C99" s="36"/>
+      <c r="B99" s="37"/>
+      <c r="C99" s="37"/>
       <c r="D99" s="15" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="E99" s="23"/>
       <c r="F99" s="23"/>
@@ -4439,34 +4542,34 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A100" s="39"/>
-      <c r="B100" s="36"/>
-      <c r="C100" s="36"/>
+      <c r="B100" s="37"/>
+      <c r="C100" s="35" t="s">
+        <v>52</v>
+      </c>
       <c r="D100" s="15" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="E100" s="23"/>
       <c r="F100" s="23"/>
       <c r="G100" s="19"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A101" s="39"/>
-      <c r="B101" s="36"/>
-      <c r="C101" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="D101" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="E101" s="23"/>
-      <c r="F101" s="23"/>
+      <c r="B101" s="37"/>
+      <c r="C101" s="37"/>
+      <c r="D101" s="15"/>
+      <c r="E101" s="15"/>
+      <c r="F101" s="15"/>
       <c r="G101" s="19"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A102" s="39"/>
-      <c r="B102" s="36"/>
-      <c r="C102" s="36"/>
+      <c r="B102" s="37"/>
+      <c r="C102" s="13" t="s">
+        <v>53</v>
+      </c>
       <c r="D102" s="15" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="E102" s="23"/>
       <c r="F102" s="23"/>
@@ -4474,10 +4577,14 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A103" s="39"/>
-      <c r="B103" s="36"/>
-      <c r="C103" s="36"/>
+      <c r="B103" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="C103" s="35" t="s">
+        <v>54</v>
+      </c>
       <c r="D103" s="15" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="E103" s="23"/>
       <c r="F103" s="23"/>
@@ -4485,10 +4592,10 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A104" s="39"/>
-      <c r="B104" s="36"/>
+      <c r="B104" s="37"/>
       <c r="C104" s="36"/>
       <c r="D104" s="15" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="E104" s="23"/>
       <c r="F104" s="23"/>
@@ -4496,18 +4603,18 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A105" s="39"/>
-      <c r="B105" s="36"/>
+      <c r="B105" s="37"/>
       <c r="C105" s="35" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D105" s="15" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="E105" s="23"/>
       <c r="F105" s="23"/>
       <c r="G105" s="19"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A106" s="39"/>
       <c r="B106" s="36"/>
       <c r="C106" s="36"/>
@@ -4516,723 +4623,668 @@
       <c r="F106" s="15"/>
       <c r="G106" s="19"/>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A107" s="39"/>
-      <c r="B107" s="36"/>
-      <c r="C107" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D107" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E107" s="23"/>
-      <c r="F107" s="23"/>
+      <c r="B107" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C107" s="11"/>
+      <c r="D107" s="15"/>
+      <c r="E107" s="15"/>
+      <c r="F107" s="15"/>
       <c r="G107" s="19"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A108" s="39"/>
-      <c r="B108" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="C108" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="D108" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="E108" s="23"/>
-      <c r="F108" s="23"/>
+      <c r="B108" s="11"/>
+      <c r="C108" s="11"/>
+      <c r="D108" s="15"/>
+      <c r="E108" s="15"/>
+      <c r="F108" s="15"/>
       <c r="G108" s="19"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A109" s="39"/>
-      <c r="B109" s="36"/>
-      <c r="C109" s="37"/>
-      <c r="D109" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="E109" s="23"/>
-      <c r="F109" s="23"/>
+      <c r="B109" s="11"/>
+      <c r="C109" s="11"/>
+      <c r="D109" s="15"/>
+      <c r="E109" s="15"/>
+      <c r="F109" s="15"/>
       <c r="G109" s="19"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A110" s="39"/>
-      <c r="B110" s="36"/>
-      <c r="C110" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="D110" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E110" s="23"/>
-      <c r="F110" s="23"/>
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A110" s="40"/>
+      <c r="B110" s="12"/>
+      <c r="C110" s="12"/>
+      <c r="D110" s="15"/>
+      <c r="E110" s="15"/>
+      <c r="F110" s="15"/>
       <c r="G110" s="19"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A111" s="39"/>
-      <c r="B111" s="37"/>
-      <c r="C111" s="37"/>
-      <c r="D111" s="15"/>
-      <c r="E111" s="15"/>
-      <c r="F111" s="15"/>
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A111" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="B111" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="C111" s="28"/>
+      <c r="D111" s="19"/>
+      <c r="E111" s="19"/>
+      <c r="F111" s="19"/>
       <c r="G111" s="19"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A112" s="39"/>
-      <c r="B112" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C112" s="11"/>
-      <c r="D112" s="15"/>
-      <c r="E112" s="15"/>
-      <c r="F112" s="15"/>
+      <c r="B112" s="42"/>
+      <c r="C112" s="28"/>
+      <c r="D112" s="19"/>
+      <c r="E112" s="19"/>
+      <c r="F112" s="19"/>
       <c r="G112" s="19"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A113" s="39"/>
-      <c r="B113" s="11"/>
-      <c r="C113" s="11"/>
-      <c r="D113" s="15"/>
-      <c r="E113" s="15"/>
-      <c r="F113" s="15"/>
+      <c r="B113" s="43"/>
+      <c r="C113" s="28"/>
+      <c r="D113" s="19"/>
+      <c r="E113" s="19"/>
+      <c r="F113" s="19"/>
       <c r="G113" s="19"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A114" s="39"/>
-      <c r="B114" s="11"/>
-      <c r="C114" s="11"/>
-      <c r="D114" s="15"/>
-      <c r="E114" s="15"/>
-      <c r="F114" s="15"/>
+      <c r="B114" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="C114" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="D114" s="19"/>
+      <c r="E114" s="19"/>
+      <c r="F114" s="19"/>
       <c r="G114" s="19"/>
+      <c r="H114" s="9" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A115" s="40"/>
-      <c r="B115" s="12"/>
-      <c r="C115" s="12"/>
-      <c r="D115" s="15"/>
-      <c r="E115" s="15"/>
-      <c r="F115" s="15"/>
-      <c r="G115" s="19"/>
+      <c r="A115" s="39"/>
+      <c r="B115" s="42"/>
+      <c r="C115" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="D115" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="E115" s="19"/>
+      <c r="F115" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="G115" s="19" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A116" s="38" t="s">
-        <v>140</v>
-      </c>
-      <c r="B116" s="43" t="s">
-        <v>141</v>
-      </c>
+      <c r="A116" s="39"/>
+      <c r="B116" s="42"/>
       <c r="C116" s="28"/>
-      <c r="D116" s="19"/>
+      <c r="D116" s="19" t="s">
+        <v>186</v>
+      </c>
       <c r="E116" s="19"/>
-      <c r="F116" s="19"/>
-      <c r="G116" s="19"/>
+      <c r="F116" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="G116" s="19" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117" s="39"/>
-      <c r="B117" s="41"/>
+      <c r="B117" s="42"/>
       <c r="C117" s="28"/>
-      <c r="D117" s="19"/>
+      <c r="D117" s="19" t="s">
+        <v>187</v>
+      </c>
       <c r="E117" s="19"/>
-      <c r="F117" s="19"/>
-      <c r="G117" s="19"/>
+      <c r="F117" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="G117" s="19" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118" s="39"/>
       <c r="B118" s="42"/>
-      <c r="C118" s="28"/>
-      <c r="D118" s="19"/>
+      <c r="C118" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D118" s="19" t="s">
+        <v>178</v>
+      </c>
       <c r="E118" s="19"/>
-      <c r="F118" s="19"/>
-      <c r="G118" s="19"/>
+      <c r="F118" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="G118" s="19" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119" s="39"/>
-      <c r="B119" s="43" t="s">
-        <v>142</v>
-      </c>
+      <c r="B119" s="42"/>
       <c r="C119" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="D119" s="19"/>
+        <v>148</v>
+      </c>
+      <c r="D119" s="19" t="s">
+        <v>176</v>
+      </c>
       <c r="E119" s="19"/>
       <c r="F119" s="19"/>
-      <c r="G119" s="19"/>
-      <c r="H119" s="9" t="s">
-        <v>179</v>
+      <c r="G119" s="19" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" s="39"/>
-      <c r="B120" s="41"/>
+      <c r="B120" s="42"/>
       <c r="C120" s="28" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D120" s="19" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="E120" s="19"/>
       <c r="F120" s="16" t="s">
         <v>190</v>
       </c>
       <c r="G120" s="19" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" s="39"/>
-      <c r="B121" s="41"/>
-      <c r="C121" s="28"/>
+      <c r="B121" s="42"/>
+      <c r="C121" s="28" t="s">
+        <v>173</v>
+      </c>
       <c r="D121" s="19" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="E121" s="19"/>
-      <c r="F121" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="G121" s="19" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="F121" s="19"/>
+      <c r="G121" s="19"/>
+    </row>
+    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A122" s="39"/>
-      <c r="B122" s="41"/>
+      <c r="B122" s="42"/>
       <c r="C122" s="28"/>
-      <c r="D122" s="19" t="s">
-        <v>187</v>
-      </c>
+      <c r="D122" s="19"/>
       <c r="E122" s="19"/>
-      <c r="F122" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="G122" s="19" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="F122" s="19"/>
+      <c r="G122" s="19"/>
+    </row>
+    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A123" s="39"/>
-      <c r="B123" s="41"/>
-      <c r="C123" s="28" t="s">
-        <v>147</v>
-      </c>
-      <c r="D123" s="19" t="s">
-        <v>178</v>
-      </c>
+      <c r="B123" s="42"/>
+      <c r="C123" s="28"/>
+      <c r="D123" s="19"/>
       <c r="E123" s="19"/>
-      <c r="F123" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="G123" s="19" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="F123" s="19"/>
+      <c r="G123" s="19"/>
+    </row>
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A124" s="39"/>
-      <c r="B124" s="41"/>
-      <c r="C124" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="D124" s="19" t="s">
-        <v>176</v>
-      </c>
+      <c r="B124" s="42"/>
+      <c r="C124" s="28"/>
+      <c r="D124" s="19"/>
       <c r="E124" s="19"/>
       <c r="F124" s="19"/>
-      <c r="G124" s="19" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A125" s="39"/>
-      <c r="B125" s="41"/>
-      <c r="C125" s="28" t="s">
-        <v>149</v>
-      </c>
-      <c r="D125" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="E125" s="19"/>
-      <c r="F125" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="G125" s="19" t="s">
-        <v>177</v>
-      </c>
+      <c r="G124" s="19"/>
+    </row>
+    <row r="125" spans="1:8" ht="17.5" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A125" s="44"/>
+      <c r="B125" s="45"/>
+      <c r="C125" s="31"/>
+      <c r="D125" s="32"/>
+      <c r="E125" s="33"/>
+      <c r="F125" s="33"/>
+      <c r="G125" s="32"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A126" s="39"/>
-      <c r="B126" s="41"/>
-      <c r="C126" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="D126" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="E126" s="19"/>
-      <c r="F126" s="19"/>
-      <c r="G126" s="19"/>
+      <c r="A126" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="B126" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="C126" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="D126" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="E126" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="F126" s="14"/>
+      <c r="G126" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="H126" s="9" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A127" s="39"/>
-      <c r="B127" s="41"/>
-      <c r="C127" s="28"/>
-      <c r="D127" s="19"/>
-      <c r="E127" s="19"/>
-      <c r="F127" s="19"/>
-      <c r="G127" s="19"/>
+      <c r="B127" s="42"/>
+      <c r="C127" s="47"/>
+      <c r="D127" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="E127" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="F127" s="16"/>
+      <c r="G127" s="19" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A128" s="39"/>
-      <c r="B128" s="41"/>
-      <c r="C128" s="28"/>
-      <c r="D128" s="19"/>
-      <c r="E128" s="19"/>
-      <c r="F128" s="19"/>
-      <c r="G128" s="19"/>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B128" s="42"/>
+      <c r="C128" s="47"/>
+      <c r="D128" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="E128" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="F128" s="16"/>
+      <c r="G128" s="19" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A129" s="39"/>
-      <c r="B129" s="41"/>
-      <c r="C129" s="28"/>
-      <c r="D129" s="19"/>
-      <c r="E129" s="19"/>
-      <c r="F129" s="19"/>
-      <c r="G129" s="19"/>
-    </row>
-    <row r="130" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A130" s="47"/>
-      <c r="B130" s="48"/>
-      <c r="C130" s="31"/>
-      <c r="D130" s="32"/>
-      <c r="E130" s="33"/>
-      <c r="F130" s="33"/>
-      <c r="G130" s="32"/>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A131" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="B131" s="41" t="s">
-        <v>151</v>
-      </c>
-      <c r="C131" s="45" t="s">
-        <v>153</v>
-      </c>
-      <c r="D131" s="30" t="s">
-        <v>164</v>
-      </c>
-      <c r="E131" s="14" t="s">
+      <c r="B129" s="42"/>
+      <c r="C129" s="48"/>
+      <c r="D129" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="E129" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="F131" s="14"/>
-      <c r="G131" s="20" t="s">
+      <c r="F129" s="16"/>
+      <c r="G129" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="H131" s="9" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A130" s="39"/>
+      <c r="B130" s="42"/>
+      <c r="C130" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="D130" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E130" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="F130" s="16"/>
+      <c r="G130" s="19"/>
+    </row>
+    <row r="131" spans="1:7" ht="102" x14ac:dyDescent="0.45">
+      <c r="A131" s="39"/>
+      <c r="B131" s="42"/>
+      <c r="C131" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="D131" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="E131" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="F131" s="16"/>
+      <c r="G131" s="17" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="51" x14ac:dyDescent="0.45">
       <c r="A132" s="39"/>
-      <c r="B132" s="41"/>
-      <c r="C132" s="45"/>
+      <c r="B132" s="42"/>
+      <c r="C132" s="47"/>
       <c r="D132" s="17" t="s">
-        <v>161</v>
+        <v>201</v>
       </c>
       <c r="E132" s="16" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="F132" s="16"/>
-      <c r="G132" s="19" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="G132" s="17" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A133" s="39"/>
-      <c r="B133" s="41"/>
-      <c r="C133" s="45"/>
+      <c r="B133" s="42"/>
+      <c r="C133" s="47"/>
       <c r="D133" s="17" t="s">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="E133" s="16" t="s">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="F133" s="16"/>
       <c r="G133" s="19" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.45">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A134" s="39"/>
-      <c r="B134" s="41"/>
-      <c r="C134" s="46"/>
+      <c r="B134" s="42"/>
+      <c r="C134" s="47"/>
       <c r="D134" s="17" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="E134" s="16" t="s">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="F134" s="16"/>
       <c r="G134" s="19" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.45">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A135" s="39"/>
-      <c r="B135" s="41"/>
-      <c r="C135" s="28" t="s">
-        <v>154</v>
-      </c>
+      <c r="B135" s="42"/>
+      <c r="C135" s="48"/>
       <c r="D135" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="E135" s="16" t="s">
-        <v>167</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="E135" s="16"/>
       <c r="F135" s="16"/>
-      <c r="G135" s="19"/>
-    </row>
-    <row r="136" spans="1:8" ht="102" x14ac:dyDescent="0.45">
+      <c r="G135" s="19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A136" s="39"/>
-      <c r="B136" s="41"/>
-      <c r="C136" s="44" t="s">
-        <v>165</v>
+      <c r="B136" s="42"/>
+      <c r="C136" s="46" t="s">
+        <v>166</v>
       </c>
       <c r="D136" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="E136" s="16" t="s">
-        <v>167</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="E136" s="16"/>
       <c r="F136" s="16"/>
-      <c r="G136" s="17" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" ht="51" x14ac:dyDescent="0.45">
+      <c r="G136" s="19"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A137" s="39"/>
-      <c r="B137" s="41"/>
-      <c r="C137" s="45"/>
+      <c r="B137" s="42"/>
+      <c r="C137" s="47"/>
       <c r="D137" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="E137" s="16" t="s">
-        <v>132</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="E137" s="16"/>
       <c r="F137" s="16"/>
-      <c r="G137" s="17" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="G137" s="19"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A138" s="39"/>
-      <c r="B138" s="41"/>
-      <c r="C138" s="45"/>
+      <c r="B138" s="42"/>
+      <c r="C138" s="47"/>
       <c r="D138" s="17" t="s">
-        <v>198</v>
-      </c>
-      <c r="E138" s="16" t="s">
-        <v>131</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="E138" s="16"/>
       <c r="F138" s="16"/>
-      <c r="G138" s="19" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="G138" s="19"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A139" s="39"/>
-      <c r="B139" s="41"/>
-      <c r="C139" s="45"/>
-      <c r="D139" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="E139" s="16" t="s">
-        <v>131</v>
-      </c>
+      <c r="B139" s="42"/>
+      <c r="C139" s="48"/>
+      <c r="D139" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="E139" s="16"/>
       <c r="F139" s="16"/>
-      <c r="G139" s="19" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="G139" s="19"/>
+    </row>
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A140" s="39"/>
-      <c r="B140" s="41"/>
-      <c r="C140" s="46"/>
-      <c r="D140" s="17" t="s">
-        <v>194</v>
-      </c>
+      <c r="B140" s="42"/>
+      <c r="C140" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="D140" s="19"/>
       <c r="E140" s="16"/>
       <c r="F140" s="16"/>
-      <c r="G140" s="19" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="G140" s="19"/>
+    </row>
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A141" s="39"/>
-      <c r="B141" s="41"/>
-      <c r="C141" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="D141" s="17" t="s">
-        <v>157</v>
-      </c>
+      <c r="B141" s="43"/>
+      <c r="C141" s="28"/>
+      <c r="D141" s="19"/>
       <c r="E141" s="16"/>
       <c r="F141" s="16"/>
       <c r="G141" s="19"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A142" s="39"/>
-      <c r="B142" s="41"/>
-      <c r="C142" s="45"/>
-      <c r="D142" s="17" t="s">
-        <v>160</v>
-      </c>
+      <c r="B142" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="C142" s="28"/>
+      <c r="D142" s="19"/>
       <c r="E142" s="16"/>
       <c r="F142" s="16"/>
       <c r="G142" s="19"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A143" s="39"/>
-      <c r="B143" s="41"/>
-      <c r="C143" s="45"/>
-      <c r="D143" s="17" t="s">
-        <v>159</v>
-      </c>
+      <c r="B143" s="42"/>
+      <c r="C143" s="28"/>
+      <c r="D143" s="19"/>
       <c r="E143" s="16"/>
       <c r="F143" s="16"/>
       <c r="G143" s="19"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A144" s="39"/>
-      <c r="B144" s="41"/>
-      <c r="C144" s="46"/>
-      <c r="D144" s="19" t="s">
-        <v>158</v>
-      </c>
+      <c r="B144" s="43"/>
+      <c r="C144" s="28"/>
+      <c r="D144" s="19"/>
       <c r="E144" s="16"/>
       <c r="F144" s="16"/>
       <c r="G144" s="19"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A145" s="39"/>
-      <c r="B145" s="41"/>
-      <c r="C145" s="28" t="s">
-        <v>152</v>
-      </c>
+      <c r="B145" s="29" t="s">
+        <v>171</v>
+      </c>
+      <c r="C145" s="28"/>
       <c r="D145" s="19"/>
       <c r="E145" s="16"/>
       <c r="F145" s="16"/>
       <c r="G145" s="19"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A146" s="39"/>
-      <c r="B146" s="42"/>
+      <c r="B146" s="41" t="s">
+        <v>172</v>
+      </c>
       <c r="C146" s="28"/>
       <c r="D146" s="19"/>
       <c r="E146" s="16"/>
       <c r="F146" s="16"/>
       <c r="G146" s="19"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A147" s="39"/>
-      <c r="B147" s="43" t="s">
-        <v>170</v>
-      </c>
-      <c r="C147" s="28"/>
+      <c r="B147" s="42"/>
+      <c r="C147" s="28" t="s">
+        <v>180</v>
+      </c>
       <c r="D147" s="19"/>
       <c r="E147" s="16"/>
       <c r="F147" s="16"/>
       <c r="G147" s="19"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A148" s="39"/>
-      <c r="B148" s="41"/>
-      <c r="C148" s="28"/>
+      <c r="B148" s="42"/>
+      <c r="C148" s="28" t="s">
+        <v>182</v>
+      </c>
       <c r="D148" s="19"/>
       <c r="E148" s="16"/>
       <c r="F148" s="16"/>
-      <c r="G148" s="19"/>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="G148" s="19" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A149" s="39"/>
       <c r="B149" s="42"/>
-      <c r="C149" s="28"/>
+      <c r="C149" s="28" t="s">
+        <v>181</v>
+      </c>
       <c r="D149" s="19"/>
       <c r="E149" s="16"/>
       <c r="F149" s="16"/>
       <c r="G149" s="19"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A150" s="39"/>
-      <c r="B150" s="29" t="s">
-        <v>171</v>
-      </c>
+      <c r="B150" s="42"/>
       <c r="C150" s="28"/>
       <c r="D150" s="19"/>
       <c r="E150" s="16"/>
       <c r="F150" s="16"/>
       <c r="G150" s="19"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A151" s="39"/>
-      <c r="B151" s="43" t="s">
-        <v>172</v>
-      </c>
+      <c r="B151" s="42"/>
       <c r="C151" s="28"/>
       <c r="D151" s="19"/>
       <c r="E151" s="16"/>
       <c r="F151" s="16"/>
       <c r="G151" s="19"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A152" s="39"/>
-      <c r="B152" s="41"/>
-      <c r="C152" s="28" t="s">
-        <v>180</v>
-      </c>
+      <c r="B152" s="42"/>
+      <c r="C152" s="28"/>
       <c r="D152" s="19"/>
       <c r="E152" s="16"/>
       <c r="F152" s="16"/>
       <c r="G152" s="19"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A153" s="39"/>
-      <c r="B153" s="41"/>
-      <c r="C153" s="28" t="s">
-        <v>182</v>
-      </c>
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A153" s="40"/>
+      <c r="B153" s="43"/>
+      <c r="C153" s="28"/>
       <c r="D153" s="19"/>
       <c r="E153" s="16"/>
       <c r="F153" s="16"/>
-      <c r="G153" s="19" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A154" s="39"/>
-      <c r="B154" s="41"/>
-      <c r="C154" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="D154" s="19"/>
-      <c r="E154" s="16"/>
-      <c r="F154" s="16"/>
-      <c r="G154" s="19"/>
+      <c r="G153" s="19"/>
+    </row>
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B154" t="s">
+        <v>144</v>
+      </c>
+      <c r="C154" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A155" s="39"/>
-      <c r="B155" s="41"/>
-      <c r="C155" s="28"/>
-      <c r="D155" s="19"/>
-      <c r="E155" s="16"/>
-      <c r="F155" s="16"/>
-      <c r="G155" s="19"/>
+      <c r="I155" s="7"/>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A156" s="39"/>
-      <c r="B156" s="41"/>
-      <c r="C156" s="28"/>
-      <c r="D156" s="19"/>
-      <c r="E156" s="16"/>
-      <c r="F156" s="16"/>
-      <c r="G156" s="19"/>
+      <c r="C156" t="s">
+        <v>193</v>
+      </c>
+      <c r="I156" s="8"/>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A157" s="39"/>
-      <c r="B157" s="41"/>
-      <c r="C157" s="28"/>
-      <c r="D157" s="19"/>
-      <c r="E157" s="16"/>
-      <c r="F157" s="16"/>
-      <c r="G157" s="19"/>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A158" s="40"/>
-      <c r="B158" s="42"/>
-      <c r="C158" s="28"/>
-      <c r="D158" s="19"/>
-      <c r="E158" s="16"/>
-      <c r="F158" s="16"/>
-      <c r="G158" s="19"/>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="B159" t="s">
-        <v>144</v>
-      </c>
-      <c r="C159" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="I160" s="7"/>
-    </row>
-    <row r="161" spans="3:9" x14ac:dyDescent="0.45">
-      <c r="C161" t="s">
-        <v>193</v>
-      </c>
-      <c r="I161" s="8"/>
-    </row>
-    <row r="162" spans="3:9" x14ac:dyDescent="0.45">
-      <c r="I162" s="8"/>
+      <c r="I157" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G116" xr:uid="{34DC90E1-7112-4806-ADC5-98CA8498E977}"/>
+  <autoFilter ref="A4:G154" xr:uid="{34DC90E1-7112-4806-ADC5-98CA8498E977}">
+    <filterColumn colId="3">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="56">
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="B79:B92"/>
+    <mergeCell ref="C79:C81"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="A126:A153"/>
+    <mergeCell ref="B126:B141"/>
+    <mergeCell ref="B146:B153"/>
+    <mergeCell ref="C136:C139"/>
+    <mergeCell ref="C126:C129"/>
+    <mergeCell ref="C131:C135"/>
+    <mergeCell ref="C55:C60"/>
+    <mergeCell ref="B25:B52"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="A111:A125"/>
+    <mergeCell ref="B114:B125"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B103:B106"/>
+    <mergeCell ref="C103:C104"/>
+    <mergeCell ref="C105:C106"/>
+    <mergeCell ref="A5:A110"/>
+    <mergeCell ref="B5:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B12:B24"/>
+    <mergeCell ref="B93:B102"/>
+    <mergeCell ref="C93:C95"/>
+    <mergeCell ref="C96:C99"/>
+    <mergeCell ref="B53:B60"/>
+    <mergeCell ref="C53:C54"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="C18:C21"/>
-    <mergeCell ref="C22:C25"/>
-    <mergeCell ref="B147:B149"/>
-    <mergeCell ref="C89:C90"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="C93:C97"/>
-    <mergeCell ref="C105:C106"/>
-    <mergeCell ref="B66:B79"/>
-    <mergeCell ref="C66:C68"/>
-    <mergeCell ref="C69:C71"/>
-    <mergeCell ref="C72:C75"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B80:B83"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="A116:A130"/>
-    <mergeCell ref="B119:B130"/>
-    <mergeCell ref="B116:B118"/>
-    <mergeCell ref="B108:B111"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="C110:C111"/>
-    <mergeCell ref="A5:A115"/>
-    <mergeCell ref="B5:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="B12:B25"/>
-    <mergeCell ref="B98:B107"/>
-    <mergeCell ref="C98:C100"/>
-    <mergeCell ref="C101:C104"/>
-    <mergeCell ref="B58:B65"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="C60:C65"/>
-    <mergeCell ref="B26:B57"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="C48:C50"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="A131:A158"/>
-    <mergeCell ref="B131:B146"/>
-    <mergeCell ref="B151:B158"/>
-    <mergeCell ref="C141:C144"/>
-    <mergeCell ref="C131:C134"/>
-    <mergeCell ref="C136:C140"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="B84:B97"/>
-    <mergeCell ref="C84:C86"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="B142:B144"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="C88:C92"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="B61:B74"/>
+    <mergeCell ref="C61:C63"/>
+    <mergeCell ref="C64:C66"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="B75:B78"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5316,7 +5368,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="39"/>
-      <c r="B6" s="36"/>
+      <c r="B6" s="37"/>
       <c r="C6" s="13" t="s">
         <v>130</v>
       </c>
@@ -5329,7 +5381,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="39"/>
-      <c r="B7" s="36"/>
+      <c r="B7" s="37"/>
       <c r="C7" s="13" t="s">
         <v>7</v>
       </c>
@@ -5342,7 +5394,7 @@
     </row>
     <row r="8" spans="1:8" ht="34" x14ac:dyDescent="0.45">
       <c r="A8" s="39"/>
-      <c r="B8" s="36"/>
+      <c r="B8" s="37"/>
       <c r="C8" s="35" t="s">
         <v>191</v>
       </c>
@@ -5357,8 +5409,8 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="39"/>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
       <c r="F9" s="15"/>
@@ -5366,7 +5418,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="39"/>
-      <c r="B10" s="36"/>
+      <c r="B10" s="37"/>
       <c r="C10" s="35" t="s">
         <v>192</v>
       </c>
@@ -5379,8 +5431,8 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="39"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="37"/>
       <c r="D11" s="17"/>
       <c r="E11" s="17"/>
       <c r="F11" s="17"/>
@@ -5403,7 +5455,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="39"/>
-      <c r="B13" s="36"/>
+      <c r="B13" s="37"/>
       <c r="C13" s="35" t="s">
         <v>11</v>
       </c>
@@ -5416,8 +5468,8 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="39"/>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
       <c r="D14" s="18" t="s">
         <v>60</v>
       </c>
@@ -5427,8 +5479,8 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" s="39"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="37"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="36"/>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
       <c r="F15" s="18"/>
@@ -5436,7 +5488,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="39"/>
-      <c r="B16" s="36"/>
+      <c r="B16" s="37"/>
       <c r="C16" s="13" t="s">
         <v>12</v>
       </c>
@@ -5449,7 +5501,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="39"/>
-      <c r="B17" s="36"/>
+      <c r="B17" s="37"/>
       <c r="C17" s="13" t="s">
         <v>13</v>
       </c>
@@ -5462,7 +5514,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="39"/>
-      <c r="B18" s="36"/>
+      <c r="B18" s="37"/>
       <c r="C18" s="35" t="s">
         <v>14</v>
       </c>
@@ -5473,8 +5525,8 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="39"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="37"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="15"/>
@@ -5482,8 +5534,8 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="39"/>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="37"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="15"/>
@@ -5491,8 +5543,8 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="39"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="37"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="36"/>
       <c r="D21" s="19"/>
       <c r="E21" s="19"/>
       <c r="F21" s="19"/>
@@ -5500,7 +5552,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="39"/>
-      <c r="B22" s="36"/>
+      <c r="B22" s="37"/>
       <c r="C22" s="35" t="s">
         <v>15</v>
       </c>
@@ -5515,8 +5567,8 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="39"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
       <c r="D23" s="20" t="s">
         <v>98</v>
       </c>
@@ -5526,8 +5578,8 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="39"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="37"/>
       <c r="D24" s="21"/>
       <c r="E24" s="21"/>
       <c r="F24" s="21"/>
@@ -5535,8 +5587,8 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="39"/>
-      <c r="B25" s="37"/>
-      <c r="C25" s="37"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
       <c r="D25" s="21"/>
       <c r="E25" s="21"/>
       <c r="F25" s="21"/>
@@ -5559,8 +5611,8 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="39"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
       <c r="D27" s="21" t="s">
         <v>111</v>
       </c>
@@ -5570,8 +5622,8 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="39"/>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
       <c r="D28" s="21"/>
       <c r="E28" s="21"/>
       <c r="F28" s="21"/>
@@ -5579,7 +5631,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="39"/>
-      <c r="B29" s="36"/>
+      <c r="B29" s="37"/>
       <c r="C29" s="35" t="s">
         <v>25</v>
       </c>
@@ -5592,8 +5644,8 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="39"/>
-      <c r="B30" s="36"/>
-      <c r="C30" s="36"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
       <c r="D30" s="21"/>
       <c r="E30" s="21"/>
       <c r="F30" s="21"/>
@@ -5601,8 +5653,8 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="39"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="37"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="36"/>
       <c r="D31" s="21"/>
       <c r="E31" s="21"/>
       <c r="F31" s="21"/>
@@ -5610,7 +5662,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="39"/>
-      <c r="B32" s="36"/>
+      <c r="B32" s="37"/>
       <c r="C32" s="35" t="s">
         <v>26</v>
       </c>
@@ -5621,8 +5673,8 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="39"/>
-      <c r="B33" s="36"/>
-      <c r="C33" s="36"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="37"/>
       <c r="D33" s="21"/>
       <c r="E33" s="21"/>
       <c r="F33" s="21"/>
@@ -5630,8 +5682,8 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="39"/>
-      <c r="B34" s="36"/>
-      <c r="C34" s="36"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="37"/>
       <c r="D34" s="21"/>
       <c r="E34" s="21"/>
       <c r="F34" s="21"/>
@@ -5639,8 +5691,8 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="39"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="37"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="36"/>
       <c r="D35" s="21"/>
       <c r="E35" s="21"/>
       <c r="F35" s="21"/>
@@ -5648,7 +5700,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" s="39"/>
-      <c r="B36" s="36"/>
+      <c r="B36" s="37"/>
       <c r="C36" s="35" t="s">
         <v>27</v>
       </c>
@@ -5661,8 +5713,8 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" s="39"/>
-      <c r="B37" s="36"/>
-      <c r="C37" s="37"/>
+      <c r="B37" s="37"/>
+      <c r="C37" s="36"/>
       <c r="D37" s="21"/>
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
@@ -5670,7 +5722,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" s="39"/>
-      <c r="B38" s="36"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="35" t="s">
         <v>28</v>
       </c>
@@ -5683,8 +5735,8 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" s="39"/>
-      <c r="B39" s="36"/>
-      <c r="C39" s="36"/>
+      <c r="B39" s="37"/>
+      <c r="C39" s="37"/>
       <c r="D39" s="21" t="s">
         <v>97</v>
       </c>
@@ -5694,7 +5746,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" s="39"/>
-      <c r="B40" s="36"/>
+      <c r="B40" s="37"/>
       <c r="C40" s="35" t="s">
         <v>29</v>
       </c>
@@ -5707,8 +5759,8 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" s="39"/>
-      <c r="B41" s="36"/>
-      <c r="C41" s="36"/>
+      <c r="B41" s="37"/>
+      <c r="C41" s="37"/>
       <c r="D41" s="21" t="s">
         <v>81</v>
       </c>
@@ -5718,8 +5770,8 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" s="39"/>
-      <c r="B42" s="36"/>
-      <c r="C42" s="37"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="36"/>
       <c r="D42" s="21" t="s">
         <v>82</v>
       </c>
@@ -5729,7 +5781,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" s="39"/>
-      <c r="B43" s="36"/>
+      <c r="B43" s="37"/>
       <c r="C43" s="35" t="s">
         <v>30</v>
       </c>
@@ -5742,8 +5794,8 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" s="39"/>
-      <c r="B44" s="36"/>
-      <c r="C44" s="36"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="37"/>
       <c r="D44" s="21" t="s">
         <v>62</v>
       </c>
@@ -5753,8 +5805,8 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" s="39"/>
-      <c r="B45" s="36"/>
-      <c r="C45" s="37"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="36"/>
       <c r="D45" s="21"/>
       <c r="E45" s="21"/>
       <c r="F45" s="21"/>
@@ -5762,7 +5814,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" s="39"/>
-      <c r="B46" s="36"/>
+      <c r="B46" s="37"/>
       <c r="C46" s="35" t="s">
         <v>31</v>
       </c>
@@ -5773,8 +5825,8 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" s="39"/>
-      <c r="B47" s="36"/>
-      <c r="C47" s="36"/>
+      <c r="B47" s="37"/>
+      <c r="C47" s="37"/>
       <c r="D47" s="21"/>
       <c r="E47" s="21"/>
       <c r="F47" s="21"/>
@@ -5782,7 +5834,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" s="39"/>
-      <c r="B48" s="36"/>
+      <c r="B48" s="37"/>
       <c r="C48" s="35" t="s">
         <v>32</v>
       </c>
@@ -5795,8 +5847,8 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" s="39"/>
-      <c r="B49" s="36"/>
-      <c r="C49" s="36"/>
+      <c r="B49" s="37"/>
+      <c r="C49" s="37"/>
       <c r="D49" s="21" t="s">
         <v>73</v>
       </c>
@@ -5806,8 +5858,8 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" s="39"/>
-      <c r="B50" s="36"/>
-      <c r="C50" s="36"/>
+      <c r="B50" s="37"/>
+      <c r="C50" s="37"/>
       <c r="D50" s="21"/>
       <c r="E50" s="21"/>
       <c r="F50" s="21"/>
@@ -5815,7 +5867,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" s="39"/>
-      <c r="B51" s="36"/>
+      <c r="B51" s="37"/>
       <c r="C51" s="35" t="s">
         <v>33</v>
       </c>
@@ -5828,8 +5880,8 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" s="39"/>
-      <c r="B52" s="36"/>
-      <c r="C52" s="36"/>
+      <c r="B52" s="37"/>
+      <c r="C52" s="37"/>
       <c r="D52" s="21"/>
       <c r="E52" s="21"/>
       <c r="F52" s="21"/>
@@ -5837,8 +5889,8 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" s="39"/>
-      <c r="B53" s="36"/>
-      <c r="C53" s="36"/>
+      <c r="B53" s="37"/>
+      <c r="C53" s="37"/>
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
       <c r="F53" s="21"/>
@@ -5846,7 +5898,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" s="39"/>
-      <c r="B54" s="36"/>
+      <c r="B54" s="37"/>
       <c r="C54" s="35" t="s">
         <v>34</v>
       </c>
@@ -5859,8 +5911,8 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" s="39"/>
-      <c r="B55" s="36"/>
-      <c r="C55" s="37"/>
+      <c r="B55" s="37"/>
+      <c r="C55" s="36"/>
       <c r="D55" s="21"/>
       <c r="E55" s="21"/>
       <c r="F55" s="21"/>
@@ -5868,7 +5920,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" s="39"/>
-      <c r="B56" s="36"/>
+      <c r="B56" s="37"/>
       <c r="C56" s="35" t="s">
         <v>35</v>
       </c>
@@ -5881,8 +5933,8 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" s="39"/>
-      <c r="B57" s="37"/>
-      <c r="C57" s="36"/>
+      <c r="B57" s="36"/>
+      <c r="C57" s="37"/>
       <c r="D57" s="21" t="s">
         <v>121</v>
       </c>
@@ -5907,8 +5959,8 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" s="39"/>
-      <c r="B59" s="36"/>
-      <c r="C59" s="36"/>
+      <c r="B59" s="37"/>
+      <c r="C59" s="37"/>
       <c r="D59" s="15"/>
       <c r="E59" s="15"/>
       <c r="F59" s="16"/>
@@ -5916,7 +5968,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" s="39"/>
-      <c r="B60" s="36"/>
+      <c r="B60" s="37"/>
       <c r="C60" s="35" t="s">
         <v>37</v>
       </c>
@@ -5929,8 +5981,8 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" s="39"/>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
+      <c r="B61" s="37"/>
+      <c r="C61" s="37"/>
       <c r="D61" s="15" t="s">
         <v>65</v>
       </c>
@@ -5940,8 +5992,8 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" s="39"/>
-      <c r="B62" s="36"/>
-      <c r="C62" s="36"/>
+      <c r="B62" s="37"/>
+      <c r="C62" s="37"/>
       <c r="D62" s="15" t="s">
         <v>66</v>
       </c>
@@ -5951,8 +6003,8 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" s="39"/>
-      <c r="B63" s="36"/>
-      <c r="C63" s="36"/>
+      <c r="B63" s="37"/>
+      <c r="C63" s="37"/>
       <c r="D63" s="15" t="s">
         <v>67</v>
       </c>
@@ -5962,8 +6014,8 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" s="39"/>
-      <c r="B64" s="36"/>
-      <c r="C64" s="36"/>
+      <c r="B64" s="37"/>
+      <c r="C64" s="37"/>
       <c r="D64" s="15" t="s">
         <v>68</v>
       </c>
@@ -5973,8 +6025,8 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A65" s="39"/>
-      <c r="B65" s="36"/>
-      <c r="C65" s="36"/>
+      <c r="B65" s="37"/>
+      <c r="C65" s="37"/>
       <c r="D65" s="15" t="s">
         <v>69</v>
       </c>
@@ -5999,8 +6051,8 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A67" s="39"/>
-      <c r="B67" s="36"/>
-      <c r="C67" s="36"/>
+      <c r="B67" s="37"/>
+      <c r="C67" s="37"/>
       <c r="D67" s="15" t="s">
         <v>100</v>
       </c>
@@ -6010,8 +6062,8 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A68" s="39"/>
-      <c r="B68" s="36"/>
-      <c r="C68" s="36"/>
+      <c r="B68" s="37"/>
+      <c r="C68" s="37"/>
       <c r="D68" s="15" t="s">
         <v>101</v>
       </c>
@@ -6021,7 +6073,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A69" s="39"/>
-      <c r="B69" s="36"/>
+      <c r="B69" s="37"/>
       <c r="C69" s="35" t="s">
         <v>39</v>
       </c>
@@ -6034,8 +6086,8 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A70" s="39"/>
-      <c r="B70" s="36"/>
-      <c r="C70" s="36"/>
+      <c r="B70" s="37"/>
+      <c r="C70" s="37"/>
       <c r="D70" s="15" t="s">
         <v>75</v>
       </c>
@@ -6045,8 +6097,8 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A71" s="39"/>
-      <c r="B71" s="36"/>
-      <c r="C71" s="36"/>
+      <c r="B71" s="37"/>
+      <c r="C71" s="37"/>
       <c r="D71" s="15" t="s">
         <v>76</v>
       </c>
@@ -6056,7 +6108,7 @@
     </row>
     <row r="72" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="39"/>
-      <c r="B72" s="36"/>
+      <c r="B72" s="37"/>
       <c r="C72" s="35" t="s">
         <v>40</v>
       </c>
@@ -6069,8 +6121,8 @@
     </row>
     <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="39"/>
-      <c r="B73" s="36"/>
-      <c r="C73" s="36"/>
+      <c r="B73" s="37"/>
+      <c r="C73" s="37"/>
       <c r="D73" s="15" t="s">
         <v>104</v>
       </c>
@@ -6080,8 +6132,8 @@
     </row>
     <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="39"/>
-      <c r="B74" s="36"/>
-      <c r="C74" s="36"/>
+      <c r="B74" s="37"/>
+      <c r="C74" s="37"/>
       <c r="D74" s="15" t="s">
         <v>105</v>
       </c>
@@ -6091,8 +6143,8 @@
     </row>
     <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="39"/>
-      <c r="B75" s="36"/>
-      <c r="C75" s="36"/>
+      <c r="B75" s="37"/>
+      <c r="C75" s="37"/>
       <c r="D75" s="15" t="s">
         <v>106</v>
       </c>
@@ -6102,7 +6154,7 @@
     </row>
     <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="39"/>
-      <c r="B76" s="36"/>
+      <c r="B76" s="37"/>
       <c r="C76" s="35" t="s">
         <v>41</v>
       </c>
@@ -6115,8 +6167,8 @@
     </row>
     <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="39"/>
-      <c r="B77" s="36"/>
-      <c r="C77" s="36"/>
+      <c r="B77" s="37"/>
+      <c r="C77" s="37"/>
       <c r="D77" s="15" t="s">
         <v>115</v>
       </c>
@@ -6126,7 +6178,7 @@
     </row>
     <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="39"/>
-      <c r="B78" s="36"/>
+      <c r="B78" s="37"/>
       <c r="C78" s="35" t="s">
         <v>42</v>
       </c>
@@ -6139,8 +6191,8 @@
     </row>
     <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="39"/>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
+      <c r="B79" s="37"/>
+      <c r="C79" s="37"/>
       <c r="D79" s="15" t="s">
         <v>124</v>
       </c>
@@ -6165,8 +6217,8 @@
     </row>
     <row r="81" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="39"/>
-      <c r="B81" s="36"/>
-      <c r="C81" s="37"/>
+      <c r="B81" s="37"/>
+      <c r="C81" s="36"/>
       <c r="D81" s="15"/>
       <c r="E81" s="15"/>
       <c r="F81" s="15"/>
@@ -6174,7 +6226,7 @@
     </row>
     <row r="82" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="39"/>
-      <c r="B82" s="36"/>
+      <c r="B82" s="37"/>
       <c r="C82" s="35" t="s">
         <v>44</v>
       </c>
@@ -6187,8 +6239,8 @@
     </row>
     <row r="83" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="39"/>
-      <c r="B83" s="37"/>
-      <c r="C83" s="37"/>
+      <c r="B83" s="36"/>
+      <c r="C83" s="36"/>
       <c r="D83" s="15"/>
       <c r="E83" s="15"/>
       <c r="F83" s="15"/>
@@ -6211,8 +6263,8 @@
     </row>
     <row r="85" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="39"/>
-      <c r="B85" s="36"/>
-      <c r="C85" s="36"/>
+      <c r="B85" s="37"/>
+      <c r="C85" s="37"/>
       <c r="D85" s="15"/>
       <c r="E85" s="15"/>
       <c r="F85" s="15"/>
@@ -6220,8 +6272,8 @@
     </row>
     <row r="86" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="39"/>
-      <c r="B86" s="36"/>
-      <c r="C86" s="37"/>
+      <c r="B86" s="37"/>
+      <c r="C86" s="36"/>
       <c r="D86" s="15"/>
       <c r="E86" s="15"/>
       <c r="F86" s="15"/>
@@ -6229,7 +6281,7 @@
     </row>
     <row r="87" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="39"/>
-      <c r="B87" s="36"/>
+      <c r="B87" s="37"/>
       <c r="C87" s="35" t="s">
         <v>46</v>
       </c>
@@ -6242,8 +6294,8 @@
     </row>
     <row r="88" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="39"/>
-      <c r="B88" s="36"/>
-      <c r="C88" s="36"/>
+      <c r="B88" s="37"/>
+      <c r="C88" s="37"/>
       <c r="D88" s="15"/>
       <c r="E88" s="15"/>
       <c r="F88" s="15"/>
@@ -6251,7 +6303,7 @@
     </row>
     <row r="89" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="39"/>
-      <c r="B89" s="36"/>
+      <c r="B89" s="37"/>
       <c r="C89" s="35" t="s">
         <v>47</v>
       </c>
@@ -6264,8 +6316,8 @@
     </row>
     <row r="90" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="39"/>
-      <c r="B90" s="36"/>
-      <c r="C90" s="36"/>
+      <c r="B90" s="37"/>
+      <c r="C90" s="37"/>
       <c r="D90" s="15"/>
       <c r="E90" s="15"/>
       <c r="F90" s="15"/>
@@ -6273,7 +6325,7 @@
     </row>
     <row r="91" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="39"/>
-      <c r="B91" s="36"/>
+      <c r="B91" s="37"/>
       <c r="C91" s="35" t="s">
         <v>48</v>
       </c>
@@ -6286,8 +6338,8 @@
     </row>
     <row r="92" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="39"/>
-      <c r="B92" s="36"/>
-      <c r="C92" s="36"/>
+      <c r="B92" s="37"/>
+      <c r="C92" s="37"/>
       <c r="D92" s="15"/>
       <c r="E92" s="15"/>
       <c r="F92" s="15"/>
@@ -6295,7 +6347,7 @@
     </row>
     <row r="93" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="39"/>
-      <c r="B93" s="36"/>
+      <c r="B93" s="37"/>
       <c r="C93" s="35" t="s">
         <v>49</v>
       </c>
@@ -6308,8 +6360,8 @@
     </row>
     <row r="94" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="39"/>
-      <c r="B94" s="36"/>
-      <c r="C94" s="36"/>
+      <c r="B94" s="37"/>
+      <c r="C94" s="37"/>
       <c r="D94" s="15" t="s">
         <v>126</v>
       </c>
@@ -6319,8 +6371,8 @@
     </row>
     <row r="95" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="39"/>
-      <c r="B95" s="36"/>
-      <c r="C95" s="36"/>
+      <c r="B95" s="37"/>
+      <c r="C95" s="37"/>
       <c r="D95" s="15" t="s">
         <v>127</v>
       </c>
@@ -6330,8 +6382,8 @@
     </row>
     <row r="96" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="39"/>
-      <c r="B96" s="36"/>
-      <c r="C96" s="36"/>
+      <c r="B96" s="37"/>
+      <c r="C96" s="37"/>
       <c r="D96" s="15"/>
       <c r="E96" s="15"/>
       <c r="F96" s="15"/>
@@ -6339,8 +6391,8 @@
     </row>
     <row r="97" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="39"/>
-      <c r="B97" s="36"/>
-      <c r="C97" s="36"/>
+      <c r="B97" s="37"/>
+      <c r="C97" s="37"/>
       <c r="D97" s="15"/>
       <c r="E97" s="15"/>
       <c r="F97" s="15"/>
@@ -6363,8 +6415,8 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A99" s="39"/>
-      <c r="B99" s="36"/>
-      <c r="C99" s="36"/>
+      <c r="B99" s="37"/>
+      <c r="C99" s="37"/>
       <c r="D99" s="15" t="s">
         <v>71</v>
       </c>
@@ -6374,8 +6426,8 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A100" s="39"/>
-      <c r="B100" s="36"/>
-      <c r="C100" s="36"/>
+      <c r="B100" s="37"/>
+      <c r="C100" s="37"/>
       <c r="D100" s="15" t="s">
         <v>83</v>
       </c>
@@ -6385,7 +6437,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A101" s="39"/>
-      <c r="B101" s="36"/>
+      <c r="B101" s="37"/>
       <c r="C101" s="35" t="s">
         <v>51</v>
       </c>
@@ -6398,8 +6450,8 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A102" s="39"/>
-      <c r="B102" s="36"/>
-      <c r="C102" s="36"/>
+      <c r="B102" s="37"/>
+      <c r="C102" s="37"/>
       <c r="D102" s="15" t="s">
         <v>117</v>
       </c>
@@ -6409,8 +6461,8 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A103" s="39"/>
-      <c r="B103" s="36"/>
-      <c r="C103" s="36"/>
+      <c r="B103" s="37"/>
+      <c r="C103" s="37"/>
       <c r="D103" s="15" t="s">
         <v>118</v>
       </c>
@@ -6420,8 +6472,8 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A104" s="39"/>
-      <c r="B104" s="36"/>
-      <c r="C104" s="36"/>
+      <c r="B104" s="37"/>
+      <c r="C104" s="37"/>
       <c r="D104" s="15" t="s">
         <v>119</v>
       </c>
@@ -6431,7 +6483,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A105" s="39"/>
-      <c r="B105" s="36"/>
+      <c r="B105" s="37"/>
       <c r="C105" s="35" t="s">
         <v>52</v>
       </c>
@@ -6444,8 +6496,8 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A106" s="39"/>
-      <c r="B106" s="36"/>
-      <c r="C106" s="36"/>
+      <c r="B106" s="37"/>
+      <c r="C106" s="37"/>
       <c r="D106" s="15"/>
       <c r="E106" s="15"/>
       <c r="F106" s="15"/>
@@ -6453,7 +6505,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A107" s="39"/>
-      <c r="B107" s="36"/>
+      <c r="B107" s="37"/>
       <c r="C107" s="13" t="s">
         <v>53</v>
       </c>
@@ -6481,8 +6533,8 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A109" s="39"/>
-      <c r="B109" s="36"/>
-      <c r="C109" s="37"/>
+      <c r="B109" s="37"/>
+      <c r="C109" s="36"/>
       <c r="D109" s="15" t="s">
         <v>93</v>
       </c>
@@ -6492,7 +6544,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A110" s="39"/>
-      <c r="B110" s="36"/>
+      <c r="B110" s="37"/>
       <c r="C110" s="35" t="s">
         <v>55</v>
       </c>
@@ -6505,8 +6557,8 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A111" s="39"/>
-      <c r="B111" s="37"/>
-      <c r="C111" s="37"/>
+      <c r="B111" s="36"/>
+      <c r="C111" s="36"/>
       <c r="D111" s="15"/>
       <c r="E111" s="15"/>
       <c r="F111" s="15"/>
@@ -6552,7 +6604,7 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A116" s="39"/>
-      <c r="B116" s="41"/>
+      <c r="B116" s="42"/>
       <c r="C116" s="28"/>
       <c r="D116" s="19"/>
       <c r="E116" s="19"/>
@@ -6561,7 +6613,7 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117" s="39"/>
-      <c r="B117" s="42"/>
+      <c r="B117" s="43"/>
       <c r="C117" s="28"/>
       <c r="D117" s="19"/>
       <c r="E117" s="19"/>
@@ -6570,7 +6622,7 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118" s="39"/>
-      <c r="B118" s="43"/>
+      <c r="B118" s="41"/>
       <c r="C118" s="28"/>
       <c r="D118" s="19"/>
       <c r="E118" s="19"/>
@@ -6582,7 +6634,7 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119" s="39"/>
-      <c r="B119" s="41"/>
+      <c r="B119" s="42"/>
       <c r="C119" s="28"/>
       <c r="D119" s="19"/>
       <c r="E119" s="19"/>
@@ -6591,7 +6643,7 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" s="39"/>
-      <c r="B120" s="41"/>
+      <c r="B120" s="42"/>
       <c r="C120" s="28"/>
       <c r="D120" s="19"/>
       <c r="E120" s="19"/>
@@ -6600,7 +6652,7 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" s="39"/>
-      <c r="B121" s="41"/>
+      <c r="B121" s="42"/>
       <c r="C121" s="28"/>
       <c r="D121" s="19"/>
       <c r="E121" s="19"/>
@@ -6609,7 +6661,7 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122" s="39"/>
-      <c r="B122" s="41"/>
+      <c r="B122" s="42"/>
       <c r="C122" s="28"/>
       <c r="D122" s="19"/>
       <c r="E122" s="19"/>
@@ -6618,7 +6670,7 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" s="39"/>
-      <c r="B123" s="41"/>
+      <c r="B123" s="42"/>
       <c r="C123" s="28"/>
       <c r="D123" s="19"/>
       <c r="E123" s="19"/>
@@ -6627,7 +6679,7 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124" s="39"/>
-      <c r="B124" s="41"/>
+      <c r="B124" s="42"/>
       <c r="C124" s="28"/>
       <c r="D124" s="19"/>
       <c r="E124" s="19"/>
@@ -6636,7 +6688,7 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125" s="39"/>
-      <c r="B125" s="41"/>
+      <c r="B125" s="42"/>
       <c r="C125" s="28"/>
       <c r="D125" s="19"/>
       <c r="E125" s="19"/>
@@ -6645,7 +6697,7 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A126" s="39"/>
-      <c r="B126" s="41"/>
+      <c r="B126" s="42"/>
       <c r="C126" s="28"/>
       <c r="D126" s="19"/>
       <c r="E126" s="19"/>
@@ -6654,7 +6706,7 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A127" s="39"/>
-      <c r="B127" s="41"/>
+      <c r="B127" s="42"/>
       <c r="C127" s="28"/>
       <c r="D127" s="19"/>
       <c r="E127" s="19"/>
@@ -6663,7 +6715,7 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A128" s="39"/>
-      <c r="B128" s="41"/>
+      <c r="B128" s="42"/>
       <c r="C128" s="28"/>
       <c r="D128" s="19"/>
       <c r="E128" s="19"/>
@@ -6671,8 +6723,8 @@
       <c r="G128" s="19"/>
     </row>
     <row r="129" spans="1:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A129" s="47"/>
-      <c r="B129" s="48"/>
+      <c r="A129" s="44"/>
+      <c r="B129" s="45"/>
       <c r="C129" s="31"/>
       <c r="D129" s="32"/>
       <c r="E129" s="33"/>
@@ -6691,6 +6743,39 @@
   </sheetData>
   <autoFilter ref="A4:G115" xr:uid="{34DC90E1-7112-4806-ADC5-98CA8498E977}"/>
   <mergeCells count="49">
+    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="B26:B57"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="B58:B65"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="C60:C65"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="B66:B79"/>
+    <mergeCell ref="C66:C68"/>
+    <mergeCell ref="C69:C71"/>
+    <mergeCell ref="C72:C75"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B80:B83"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="B84:B97"/>
+    <mergeCell ref="C84:C86"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="C93:C97"/>
     <mergeCell ref="A116:A129"/>
     <mergeCell ref="B116:B117"/>
     <mergeCell ref="B118:B129"/>
@@ -6701,45 +6786,12 @@
     <mergeCell ref="B108:B111"/>
     <mergeCell ref="C108:C109"/>
     <mergeCell ref="C110:C111"/>
-    <mergeCell ref="B80:B83"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="B84:B97"/>
-    <mergeCell ref="C84:C86"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="C89:C90"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="C93:C97"/>
-    <mergeCell ref="B66:B79"/>
-    <mergeCell ref="C66:C68"/>
-    <mergeCell ref="C69:C71"/>
-    <mergeCell ref="C72:C75"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="C48:C50"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="B58:B65"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="C60:C65"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="C43:C45"/>
     <mergeCell ref="A5:A115"/>
     <mergeCell ref="B5:B11"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="B12:B25"/>
     <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C18:C21"/>
-    <mergeCell ref="C22:C25"/>
-    <mergeCell ref="B26:B57"/>
-    <mergeCell ref="C26:C28"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
